--- a/Financial Analysis/BBD.A.xlsx
+++ b/Financial Analysis/BBD.A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0854FBE1-C300-46F7-A6D3-AC3625713801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38440518-5D3A-4009-9AB0-3D60CA7EC133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{346DD61D-C15D-48A0-ADE2-5B9C576CD682}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>BBD</t>
   </si>
@@ -188,6 +188,15 @@
   </si>
   <si>
     <t>Backlog y/y</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
@@ -198,21 +207,21 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-1009]#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="0.000_)"/>
-    <numFmt numFmtId="174" formatCode="0.00_)"/>
-    <numFmt numFmtId="175" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0\ _K_č_-;\-* #,##0\ _K_č_-;_-* &quot;-&quot;\ _K_č_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00\ _K_č_-;\-* #,##0.00\ _K_č_-;_-* &quot;-&quot;??\ _K_č_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_ * #,##0.00_)\ &quot;$&quot;_ ;_ * \(#,##0.00\)\ &quot;$&quot;_ ;_ * &quot;-&quot;??_)\ &quot;$&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="187" formatCode="_-* #,##0.00\ _$_-;\-* #,##0.00\ _$_-;_-* &quot;-&quot;??\ _$_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.000_)"/>
+    <numFmt numFmtId="168" formatCode="0.00_)"/>
+    <numFmt numFmtId="169" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0\ _K_č_-;\-* #,##0\ _K_č_-;_-* &quot;-&quot;\ _K_č_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ _K_č_-;\-* #,##0.00\ _K_č_-;_-* &quot;-&quot;??\ _K_č_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_ * #,##0.00_)\ &quot;$&quot;_ ;_ * \(#,##0.00\)\ &quot;$&quot;_ ;_ * &quot;-&quot;??_)\ &quot;$&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="175" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ _$_-;\-* #,##0.00\ _$_-;_-* &quot;-&quot;??\ _$_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,6 +548,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1070,18 +1088,18 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center"/>
@@ -1095,12 +1113,12 @@
     <xf numFmtId="0" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1120,10 +1138,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="12" applyNumberFormat="0" applyAlignment="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="12" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -1331,8 +1349,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
@@ -1352,210 +1370,210 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="169" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="35" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="35" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="36" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="35" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="35" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="43" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="36" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="21" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="42" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="42" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="22" fillId="0" borderId="8">
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="8">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="39" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="40" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="41" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="42" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="45" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="169" fontId="39" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="41" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="42" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="43" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="45" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="14">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="14">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="14">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="14">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="14">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="14">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="14" fillId="22" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="14" fillId="22" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="16" fillId="34" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="16" fillId="34" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="16" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="16" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="27" fillId="36" borderId="0"/>
-    <xf numFmtId="175" fontId="28" fillId="36" borderId="0"/>
-    <xf numFmtId="175" fontId="29" fillId="36" borderId="17"/>
-    <xf numFmtId="175" fontId="29" fillId="36" borderId="0"/>
-    <xf numFmtId="175" fontId="27" fillId="20" borderId="17">
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="27" fillId="36" borderId="0"/>
+    <xf numFmtId="169" fontId="28" fillId="36" borderId="0"/>
+    <xf numFmtId="169" fontId="29" fillId="36" borderId="17"/>
+    <xf numFmtId="169" fontId="29" fillId="36" borderId="0"/>
+    <xf numFmtId="169" fontId="27" fillId="20" borderId="17">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="27" fillId="36" borderId="0"/>
-    <xf numFmtId="175" fontId="12" fillId="0" borderId="18"/>
-    <xf numFmtId="175" fontId="30" fillId="7" borderId="19">
+    <xf numFmtId="169" fontId="27" fillId="36" borderId="0"/>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="18"/>
+    <xf numFmtId="169" fontId="30" fillId="7" borderId="19">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="45" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="45" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="39" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="40" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="41" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="36" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="39" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="41" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="47" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="36" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -1569,10 +1587,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="12" applyNumberFormat="0" applyAlignment="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="12" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -1637,254 +1655,254 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="30" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="23" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="32" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="169" fontId="6" fillId="33" borderId="15" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="37" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
     <xf numFmtId="0" fontId="51" fillId="18" borderId="6" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
-    <xf numFmtId="183" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
+    <xf numFmtId="175" fontId="50" fillId="16" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1896,7 +1914,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1931,6 +1949,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="648" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="649">
     <cellStyle name="_Exec Summary FINAL" xfId="3" xr:uid="{19585BA9-F398-4EDE-A7B7-F00CFAAF7DC7}"/>
@@ -3033,7 +3053,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="4">
         <v>45967</v>
@@ -3108,7 +3128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D972C2C-CAC0-4237-B51D-27B3C5E485D0}">
-  <dimension ref="A2:AF37"/>
+  <dimension ref="A2:AF43"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3338,7 +3358,7 @@
         <v>590</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" ref="M6:N6" si="0">I6*1.05</f>
+        <f t="shared" ref="M6" si="0">I6*1.05</f>
         <v>554.4</v>
       </c>
       <c r="N6" s="18">
@@ -3404,43 +3424,43 @@
         <v>42</v>
       </c>
       <c r="E8" s="15">
-        <f>SUM(E5:E7)</f>
+        <f t="shared" ref="E8:N8" si="2">SUM(E5:E7)</f>
         <v>1856</v>
       </c>
       <c r="F8" s="15">
-        <f>SUM(F5:F7)</f>
+        <f t="shared" si="2"/>
         <v>3062</v>
       </c>
       <c r="G8" s="15">
-        <f>SUM(G5:G7)</f>
+        <f t="shared" si="2"/>
         <v>1281</v>
       </c>
       <c r="H8" s="15">
-        <f>SUM(H5:H7)</f>
+        <f t="shared" si="2"/>
         <v>2203</v>
       </c>
       <c r="I8" s="15">
-        <f>SUM(I5:I7)</f>
+        <f t="shared" si="2"/>
         <v>2073</v>
       </c>
       <c r="J8" s="15">
-        <f>SUM(J5:J7)</f>
+        <f t="shared" si="2"/>
         <v>3108</v>
       </c>
       <c r="K8" s="15">
-        <f>SUM(K5:K7)</f>
+        <f t="shared" si="2"/>
         <v>1522</v>
       </c>
       <c r="L8" s="15">
-        <f>SUM(L5:L7)</f>
+        <f t="shared" si="2"/>
         <v>2028</v>
       </c>
       <c r="M8" s="15">
-        <f>SUM(M5:M7)</f>
+        <f t="shared" si="2"/>
         <v>2164.65</v>
       </c>
       <c r="N8" s="15">
-        <f>SUM(N5:N7)</f>
+        <f t="shared" si="2"/>
         <v>3686.88</v>
       </c>
       <c r="U8" s="15">
@@ -3502,35 +3522,35 @@
         <v>38</v>
       </c>
       <c r="E10" s="15">
-        <f>E8-E9</f>
+        <f t="shared" ref="E10:L10" si="3">E8-E9</f>
         <v>383</v>
       </c>
       <c r="F10" s="15">
-        <f>F8-F9</f>
+        <f t="shared" si="3"/>
         <v>582</v>
       </c>
       <c r="G10" s="15">
-        <f>G8-G9</f>
+        <f t="shared" si="3"/>
         <v>285</v>
       </c>
       <c r="H10" s="15">
-        <f>H8-H9</f>
+        <f t="shared" si="3"/>
         <v>454</v>
       </c>
       <c r="I10" s="15">
-        <f>I8-I9</f>
+        <f t="shared" si="3"/>
         <v>416</v>
       </c>
       <c r="J10" s="15">
-        <f>J8-J9</f>
+        <f t="shared" si="3"/>
         <v>621</v>
       </c>
       <c r="K10" s="15">
-        <f>K8-K9</f>
+        <f t="shared" si="3"/>
         <v>281</v>
       </c>
       <c r="L10" s="15">
-        <f>L8-L9</f>
+        <f t="shared" si="3"/>
         <v>411</v>
       </c>
       <c r="M10" s="17">
@@ -3587,11 +3607,11 @@
         <v>139.05000000000001</v>
       </c>
       <c r="U11" s="18">
-        <f t="shared" ref="U11:V15" si="2">SUM(G11:J11)</f>
+        <f t="shared" ref="U11:U15" si="4">SUM(G11:J11)</f>
         <v>478</v>
       </c>
       <c r="V11" s="18">
-        <f t="shared" ref="V11:V15" si="3">SUM(K11:N11)</f>
+        <f t="shared" ref="V11:V15" si="5">SUM(K11:N11)</f>
         <v>477.56</v>
       </c>
     </row>
@@ -3632,11 +3652,11 @@
         <v>123.42</v>
       </c>
       <c r="U12" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>352</v>
       </c>
       <c r="V12" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>289.87</v>
       </c>
     </row>
@@ -3675,11 +3695,11 @@
         <v>15</v>
       </c>
       <c r="U13" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="V13" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
     </row>
@@ -3719,11 +3739,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="V14" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -3762,11 +3782,11 @@
         <v>0</v>
       </c>
       <c r="U15" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="V15" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -3775,43 +3795,43 @@
         <v>19</v>
       </c>
       <c r="E16" s="19">
-        <f>SUM(E11:E15)</f>
+        <f t="shared" ref="E16:N16" si="6">SUM(E11:E15)</f>
         <v>186</v>
       </c>
       <c r="F16" s="19">
-        <f>SUM(F11:F15)</f>
+        <f t="shared" si="6"/>
         <v>371</v>
       </c>
       <c r="G16" s="19">
-        <f>SUM(G11:G15)</f>
+        <f t="shared" si="6"/>
         <v>141</v>
       </c>
       <c r="H16" s="19">
-        <f>SUM(H11:H15)</f>
+        <f t="shared" si="6"/>
         <v>263</v>
       </c>
       <c r="I16" s="19">
-        <f>SUM(I11:I15)</f>
+        <f t="shared" si="6"/>
         <v>215</v>
       </c>
       <c r="J16" s="19">
-        <f>SUM(J11:J15)</f>
+        <f t="shared" si="6"/>
         <v>279</v>
       </c>
       <c r="K16" s="19">
-        <f>SUM(K11:K15)</f>
+        <f t="shared" si="6"/>
         <v>104</v>
       </c>
       <c r="L16" s="19">
-        <f>SUM(L11:L15)</f>
+        <f t="shared" si="6"/>
         <v>206</v>
       </c>
       <c r="M16" s="19">
-        <f>SUM(M11:M15)</f>
+        <f t="shared" si="6"/>
         <v>223.96</v>
       </c>
       <c r="N16" s="19">
-        <f>SUM(N11:N15)</f>
+        <f t="shared" si="6"/>
         <v>277.47000000000003</v>
       </c>
       <c r="U16" s="19">
@@ -3828,43 +3848,43 @@
         <v>20</v>
       </c>
       <c r="E17" s="15">
-        <f>E10-E16</f>
+        <f t="shared" ref="E17:N17" si="7">E10-E16</f>
         <v>197</v>
       </c>
       <c r="F17" s="15">
-        <f>F10-F16</f>
+        <f t="shared" si="7"/>
         <v>211</v>
       </c>
       <c r="G17" s="15">
-        <f>G10-G16</f>
+        <f t="shared" si="7"/>
         <v>144</v>
       </c>
       <c r="H17" s="15">
-        <f>H10-H16</f>
+        <f t="shared" si="7"/>
         <v>191</v>
       </c>
       <c r="I17" s="15">
-        <f>I10-I16</f>
+        <f t="shared" si="7"/>
         <v>201</v>
       </c>
       <c r="J17" s="15">
-        <f>J10-J16</f>
+        <f t="shared" si="7"/>
         <v>342</v>
       </c>
       <c r="K17" s="15">
-        <f>K10-K16</f>
+        <f t="shared" si="7"/>
         <v>177</v>
       </c>
       <c r="L17" s="15">
-        <f>L10-L16</f>
+        <f t="shared" si="7"/>
         <v>205</v>
       </c>
       <c r="M17" s="15">
-        <f>M10-M16</f>
+        <f t="shared" si="7"/>
         <v>208.97000000000006</v>
       </c>
       <c r="N17" s="15">
-        <f>N10-N16</f>
+        <f t="shared" si="7"/>
         <v>459.90600000000006</v>
       </c>
       <c r="U17" s="15">
@@ -3913,11 +3933,11 @@
         <v>305.91000000000003</v>
       </c>
       <c r="U18" s="18">
-        <f t="shared" ref="U18:V19" si="4">SUM(G18:J18)</f>
+        <f t="shared" ref="U18:U19" si="8">SUM(G18:J18)</f>
         <v>842</v>
       </c>
       <c r="V18" s="18">
-        <f t="shared" ref="V18:V19" si="5">SUM(K18:N18)</f>
+        <f t="shared" ref="V18:V19" si="9">SUM(K18:N18)</f>
         <v>758.05</v>
       </c>
     </row>
@@ -3950,19 +3970,19 @@
         <v>-134</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" ref="M19:N19" si="6">I19*1.03</f>
+        <f t="shared" ref="M19:N19" si="10">I19*1.03</f>
         <v>-52.53</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-6.18</v>
       </c>
       <c r="U19" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-220</v>
       </c>
       <c r="V19" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>-204.71</v>
       </c>
     </row>
@@ -3971,43 +3991,43 @@
         <v>23</v>
       </c>
       <c r="E20" s="15">
-        <f>E17-E18-E19</f>
+        <f t="shared" ref="E20:N20" si="11">E17-E18-E19</f>
         <v>-39</v>
       </c>
       <c r="F20" s="15">
-        <f>F17-F18-F19</f>
+        <f t="shared" si="11"/>
         <v>222</v>
       </c>
       <c r="G20" s="15">
-        <f>G17-G18-G19</f>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="H20" s="15">
-        <f>H17-H18-H19</f>
+        <f t="shared" si="11"/>
         <v>-3</v>
       </c>
       <c r="I20" s="15">
-        <f>I17-I18-I19</f>
+        <f t="shared" si="11"/>
         <v>114</v>
       </c>
       <c r="J20" s="15">
-        <f>J17-J18-J19</f>
+        <f t="shared" si="11"/>
         <v>51</v>
       </c>
       <c r="K20" s="15">
-        <f>K17-K18-K19</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
       <c r="L20" s="15">
-        <f>L17-L18-L19</f>
+        <f t="shared" si="11"/>
         <v>173</v>
       </c>
       <c r="M20" s="15">
-        <f>M17-M18-M19</f>
+        <f t="shared" si="11"/>
         <v>119.36000000000004</v>
       </c>
       <c r="N20" s="15">
-        <f>N17-N18-N19</f>
+        <f t="shared" si="11"/>
         <v>160.17600000000004</v>
       </c>
       <c r="U20" s="15">
@@ -4054,11 +4074,11 @@
         <v>0</v>
       </c>
       <c r="U21" s="18">
-        <f t="shared" ref="U21:V22" si="7">SUM(G21:J21)</f>
+        <f t="shared" ref="U21:U22" si="12">SUM(G21:J21)</f>
         <v>-114</v>
       </c>
       <c r="V21" s="18">
-        <f t="shared" ref="V21:V22" si="8">SUM(K21:N21)</f>
+        <f t="shared" ref="V21:V22" si="13">SUM(K21:N21)</f>
         <v>-19</v>
       </c>
     </row>
@@ -4097,11 +4117,11 @@
         <v>0</v>
       </c>
       <c r="U22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="V22" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
     </row>
@@ -4110,43 +4130,43 @@
         <v>13</v>
       </c>
       <c r="E23" s="15">
-        <f>E20-E21-E22</f>
+        <f t="shared" ref="E23:L23" si="14">E20-E21-E22</f>
         <v>-37</v>
       </c>
       <c r="F23" s="15">
-        <f>F20-F21-F22</f>
+        <f t="shared" si="14"/>
         <v>215</v>
       </c>
       <c r="G23" s="15">
-        <f>G20-G21-G22</f>
+        <f t="shared" si="14"/>
         <v>110</v>
       </c>
       <c r="H23" s="15">
-        <f>H20-H21-H22</f>
+        <f t="shared" si="14"/>
         <v>19</v>
       </c>
       <c r="I23" s="15">
-        <f>I20-I21-I22</f>
+        <f t="shared" si="14"/>
         <v>117</v>
       </c>
       <c r="J23" s="15">
-        <f>J20-J21-J22</f>
+        <f t="shared" si="14"/>
         <v>124</v>
       </c>
       <c r="K23" s="15">
-        <f>K20-K21-K22</f>
+        <f t="shared" si="14"/>
         <v>44</v>
       </c>
       <c r="L23" s="15">
-        <f>L20-L21-L22</f>
+        <f t="shared" si="14"/>
         <v>178</v>
       </c>
       <c r="M23" s="15">
-        <f t="shared" ref="M23:N23" si="9">M20-M21-M22</f>
+        <f t="shared" ref="M23:N23" si="15">M20-M21-M22</f>
         <v>119.36000000000004</v>
       </c>
       <c r="N23" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>160.17600000000004</v>
       </c>
       <c r="U23" s="15">
@@ -4163,43 +4183,43 @@
         <v>2</v>
       </c>
       <c r="E24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" ref="E24:L24" si="16">86.8+12.3</f>
         <v>99.1</v>
       </c>
       <c r="F24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="G24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="H24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="I24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="J24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="K24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="L24" s="6">
-        <f>86.8+12.3</f>
+        <f t="shared" si="16"/>
         <v>99.1</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" ref="M24:N24" si="10">86.8+12.3</f>
+        <f t="shared" ref="M24:N24" si="17">86.8+12.3</f>
         <v>99.1</v>
       </c>
       <c r="N24" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>99.1</v>
       </c>
       <c r="U24" s="6">
@@ -4216,43 +4236,43 @@
         <v>26</v>
       </c>
       <c r="E25" s="14">
-        <f>E23/E24</f>
+        <f t="shared" ref="E25:L25" si="18">E23/E24</f>
         <v>-0.37336024217961655</v>
       </c>
       <c r="F25" s="14">
-        <f>F23/F24</f>
+        <f t="shared" si="18"/>
         <v>2.1695257315842587</v>
       </c>
       <c r="G25" s="14">
-        <f>G23/G24</f>
+        <f t="shared" si="18"/>
         <v>1.109989909182644</v>
       </c>
       <c r="H25" s="14">
-        <f>H23/H24</f>
+        <f t="shared" si="18"/>
         <v>0.19172552976791121</v>
       </c>
       <c r="I25" s="14">
-        <f>I23/I24</f>
+        <f t="shared" si="18"/>
         <v>1.1806256306760847</v>
       </c>
       <c r="J25" s="14">
-        <f>J23/J24</f>
+        <f t="shared" si="18"/>
         <v>1.2512613521695257</v>
       </c>
       <c r="K25" s="14">
-        <f>K23/K24</f>
+        <f t="shared" si="18"/>
         <v>0.44399596367305755</v>
       </c>
       <c r="L25" s="14">
-        <f>L23/L24</f>
+        <f t="shared" si="18"/>
         <v>1.7961654894046419</v>
       </c>
       <c r="M25" s="14">
-        <f t="shared" ref="M25:N25" si="11">M23/M24</f>
+        <f t="shared" ref="M25:N25" si="19">M23/M24</f>
         <v>1.204439959636731</v>
       </c>
       <c r="N25" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>1.6163067608476291</v>
       </c>
       <c r="U25" s="14">
@@ -4298,27 +4318,27 @@
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
       <c r="I28" s="16">
-        <f>I5/E5-1</f>
+        <f t="shared" ref="I28:L31" si="20">I5/E5-1</f>
         <v>6.4200976971388712E-2</v>
       </c>
       <c r="J28" s="16">
-        <f>J5/F5-1</f>
+        <f t="shared" si="20"/>
         <v>1.555814858031912E-3</v>
       </c>
       <c r="K28" s="16">
-        <f>K5/G5-1</f>
+        <f t="shared" si="20"/>
         <v>0.28553459119496849</v>
       </c>
       <c r="L28" s="16">
-        <f>L5/H5-1</f>
+        <f t="shared" si="20"/>
         <v>-0.1513353115727003</v>
       </c>
       <c r="M28" s="16">
-        <f t="shared" ref="M27:M31" si="12">M5/I5-1</f>
+        <f t="shared" ref="M28:M31" si="21">M5/I5-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N28" s="16">
-        <f t="shared" ref="N27:N31" si="13">N5/J5-1</f>
+        <f t="shared" ref="N28:N31" si="22">N5/J5-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="V28" s="16">
@@ -4335,31 +4355,31 @@
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
       <c r="I29" s="16">
-        <f>I6/E6-1</f>
+        <f t="shared" si="20"/>
         <v>0.2753623188405796</v>
       </c>
       <c r="J29" s="16">
-        <f>J6/F6-1</f>
+        <f t="shared" si="20"/>
         <v>8.7136929460580825E-2</v>
       </c>
       <c r="K29" s="16">
-        <f>K6/G6-1</f>
+        <f t="shared" si="20"/>
         <v>3.7735849056603765E-2</v>
       </c>
       <c r="L29" s="16">
-        <f>L6/H6-1</f>
+        <f t="shared" si="20"/>
         <v>0.16370808678500981</v>
       </c>
       <c r="M29" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N29" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="V29" s="16">
-        <f t="shared" ref="V29:V31" si="14">V6/U6-1</f>
+        <f t="shared" ref="V29:V31" si="23">V6/U6-1</f>
         <v>9.3457760314342053E-2</v>
       </c>
     </row>
@@ -4372,31 +4392,31 @@
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
       <c r="I30" s="16">
-        <f>I7/E7-1</f>
+        <f t="shared" si="20"/>
         <v>1.2222222222222223</v>
       </c>
       <c r="J30" s="16">
-        <f>J7/F7-1</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K30" s="16">
-        <f>K7/G7-1</f>
+        <f t="shared" si="20"/>
         <v>-0.44444444444444442</v>
       </c>
       <c r="L30" s="16">
-        <f>L7/H7-1</f>
+        <f t="shared" si="20"/>
         <v>-0.27272727272727271</v>
       </c>
       <c r="M30" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>-0.55000000000000004</v>
       </c>
       <c r="N30" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="V30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>-0.34693877551020413</v>
       </c>
     </row>
@@ -4409,31 +4429,31 @@
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16">
-        <f>I8/E8-1</f>
+        <f t="shared" si="20"/>
         <v>0.1169181034482758</v>
       </c>
       <c r="J31" s="16">
-        <f>J8/F8-1</f>
+        <f t="shared" si="20"/>
         <v>1.5022860875244959E-2</v>
       </c>
       <c r="K31" s="16">
-        <f>K8/G8-1</f>
+        <f t="shared" si="20"/>
         <v>0.1881342701014832</v>
       </c>
       <c r="L31" s="16">
-        <f>L8/H8-1</f>
+        <f t="shared" si="20"/>
         <v>-7.9437131184748044E-2</v>
       </c>
       <c r="M31" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>4.4211287988422665E-2</v>
       </c>
       <c r="N31" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0.18625482625482626</v>
       </c>
       <c r="V31" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>8.5000577034045177E-2</v>
       </c>
     </row>
@@ -4442,31 +4462,31 @@
         <v>44</v>
       </c>
       <c r="E32" s="16">
-        <f t="shared" ref="E32:L32" si="15">E10/E8</f>
+        <f t="shared" ref="E32:K32" si="24">E10/E8</f>
         <v>0.20635775862068967</v>
       </c>
       <c r="F32" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>0.19007184846505551</v>
       </c>
       <c r="G32" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>0.22248243559718969</v>
       </c>
       <c r="H32" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>0.20608261461643212</v>
       </c>
       <c r="I32" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>0.20067534973468404</v>
       </c>
       <c r="J32" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>0.1998069498069498</v>
       </c>
       <c r="K32" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>0.18462549277266754</v>
       </c>
       <c r="L32" s="16">
@@ -4474,15 +4494,15 @@
         <v>0.20266272189349113</v>
       </c>
       <c r="M32" s="16">
-        <f t="shared" ref="M32:N32" si="16">M10/M8</f>
+        <f t="shared" ref="M32:N32" si="25">M10/M8</f>
         <v>0.2</v>
       </c>
       <c r="N32" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
       <c r="V32" s="16">
-        <f t="shared" ref="V32" si="17">V10/V8</f>
+        <f t="shared" ref="V32" si="26">V10/V8</f>
         <v>0.1980854180117492</v>
       </c>
     </row>
@@ -4495,31 +4515,31 @@
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
       <c r="I33" s="16">
-        <f>I11/E11-1</f>
+        <f t="shared" ref="I33:L34" si="27">I11/E11-1</f>
         <v>0.13592233009708732</v>
       </c>
       <c r="J33" s="16">
-        <f>J11/F11-1</f>
+        <f t="shared" si="27"/>
         <v>-1.4598540145985384E-2</v>
       </c>
       <c r="K33" s="16">
-        <f>K11/G11-1</f>
+        <f t="shared" si="27"/>
         <v>-0.1009174311926605</v>
       </c>
       <c r="L33" s="16">
-        <f>L11/H11-1</f>
+        <f t="shared" si="27"/>
         <v>2.564102564102555E-2</v>
       </c>
       <c r="M33" s="16">
-        <f t="shared" ref="M33:N33" si="18">M11/I11-1</f>
+        <f t="shared" ref="M33:N33" si="28">M11/I11-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="N33" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="V33" s="16" t="e">
-        <f t="shared" ref="V33:V34" si="19">V11/R11-1</f>
+        <f t="shared" ref="V33:V34" si="29">V11/R11-1</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4532,31 +4552,31 @@
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16">
-        <f>I12/E12-1</f>
+        <f t="shared" si="27"/>
         <v>9.8765432098765427E-2</v>
       </c>
       <c r="J34" s="16">
-        <f>J12/F12-1</f>
+        <f t="shared" si="27"/>
         <v>-0.23417721518987344</v>
       </c>
       <c r="K34" s="16">
-        <f>K12/G12-1</f>
+        <f t="shared" si="27"/>
         <v>-1.103448275862069</v>
       </c>
       <c r="L34" s="16">
-        <f>L12/H12-1</f>
+        <f t="shared" si="27"/>
         <v>-0.32743362831858402</v>
       </c>
       <c r="M34" s="16">
-        <f t="shared" ref="M34:N34" si="20">M12/I12-1</f>
+        <f t="shared" ref="M34:N34" si="30">M12/I12-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N34" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V34" s="16" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4565,31 +4585,31 @@
         <v>50</v>
       </c>
       <c r="E35" s="16">
-        <f t="shared" ref="E35:L35" si="21">E17/E8</f>
+        <f t="shared" ref="E35:K35" si="31">E17/E8</f>
         <v>0.10614224137931035</v>
       </c>
       <c r="F35" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>6.8909209666884394E-2</v>
       </c>
       <c r="G35" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>0.11241217798594848</v>
       </c>
       <c r="H35" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>8.6699954607353608E-2</v>
       </c>
       <c r="I35" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>9.6960926193921854E-2</v>
       </c>
       <c r="J35" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>0.11003861003861004</v>
       </c>
       <c r="K35" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>0.11629434954007885</v>
       </c>
       <c r="L35" s="16">
@@ -4597,15 +4617,15 @@
         <v>0.10108481262327416</v>
       </c>
       <c r="M35" s="16">
-        <f t="shared" ref="M35:N35" si="22">M17/M8</f>
+        <f t="shared" ref="M35:N35" si="32">M17/M8</f>
         <v>9.6537546485575054E-2</v>
       </c>
       <c r="N35" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>0.12474124462960554</v>
       </c>
       <c r="V35" s="16">
-        <f t="shared" ref="V35" si="23">V17/V8</f>
+        <f t="shared" ref="V35" si="33">V17/V8</f>
         <v>0.11177712563806108</v>
       </c>
     </row>
@@ -4614,31 +4634,31 @@
         <v>24</v>
       </c>
       <c r="E36" s="16">
-        <f t="shared" ref="E36:L36" si="24">E21/E20</f>
+        <f t="shared" ref="E36:K36" si="34">E21/E20</f>
         <v>5.128205128205128E-2</v>
       </c>
       <c r="F36" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3.1531531531531529E-2</v>
       </c>
       <c r="G36" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>-0.1702127659574468</v>
       </c>
       <c r="H36" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>7.333333333333333</v>
       </c>
       <c r="I36" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>-2.6315789473684209E-2</v>
       </c>
       <c r="J36" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>-1.4313725490196079</v>
       </c>
       <c r="K36" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="L36" s="16">
@@ -4646,15 +4666,15 @@
         <v>-0.11560693641618497</v>
       </c>
       <c r="M36" s="16">
-        <f t="shared" ref="M36:N36" si="25">M21/M20</f>
+        <f t="shared" ref="M36:N36" si="35">M21/M20</f>
         <v>0</v>
       </c>
       <c r="N36" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="V36" s="16">
-        <f t="shared" ref="V36" si="26">V21/V20</f>
+        <f t="shared" ref="V36" si="36">V21/V20</f>
         <v>-3.8188191407254914E-2</v>
       </c>
     </row>
@@ -4663,31 +4683,31 @@
         <v>51</v>
       </c>
       <c r="E37" s="16">
-        <f t="shared" ref="E37:L37" si="27">E23/E8</f>
+        <f t="shared" ref="E37:K37" si="37">E23/E8</f>
         <v>-1.9935344827586209E-2</v>
       </c>
       <c r="F37" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>7.0215545395166556E-2</v>
       </c>
       <c r="G37" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>8.5870413739266196E-2</v>
       </c>
       <c r="H37" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>8.6246028143440769E-3</v>
       </c>
       <c r="I37" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>5.6439942112879886E-2</v>
       </c>
       <c r="J37" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>3.9897039897039896E-2</v>
       </c>
       <c r="K37" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="37"/>
         <v>2.8909329829172142E-2</v>
       </c>
       <c r="L37" s="16">
@@ -4695,16 +4715,43 @@
         <v>8.7771203155818545E-2</v>
       </c>
       <c r="M37" s="16">
-        <f t="shared" ref="M37:N37" si="28">M23/M8</f>
+        <f t="shared" ref="M37:N37" si="38">M23/M8</f>
         <v>5.5140553900168636E-2</v>
       </c>
       <c r="N37" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>4.3444863950006518E-2</v>
       </c>
       <c r="V37" s="16">
-        <f t="shared" ref="V37" si="29">V23/V8</f>
+        <f t="shared" ref="V37" si="39">V23/V8</f>
         <v>5.334621066996547E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" s="20" customFormat="1">
+      <c r="B40" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" s="20">
+        <f>12864</f>
+        <v>12864</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22">
+      <c r="B42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L42" s="21">
+        <f>Main!D9/Model!L40</f>
+        <v>1.845136271766169</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22">
+      <c r="B43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L43" s="16">
+        <f>L40/Main!D9-1</f>
+        <v>-0.45803460952897668</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/BBD.A.xlsx
+++ b/Financial Analysis/BBD.A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38440518-5D3A-4009-9AB0-3D60CA7EC133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A820B79-EDCF-434F-B656-35A87FB8A767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{346DD61D-C15D-48A0-ADE2-5B9C576CD682}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>BBD</t>
   </si>
@@ -197,13 +197,43 @@
   </si>
   <si>
     <t>B/EV</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-1009]#,##0.00"/>
@@ -220,6 +250,7 @@
     <numFmt numFmtId="175" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ _$_-;\-* #,##0.00\ _$_-;_-* &quot;-&quot;??\ _$_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="0.0\x"/>
+    <numFmt numFmtId="178" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
   <fonts count="54">
     <font>
@@ -1914,7 +1945,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1951,6 +1982,8 @@
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="648" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="53" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="649">
     <cellStyle name="_Exec Summary FINAL" xfId="3" xr:uid="{19585BA9-F398-4EDE-A7B7-F00CFAAF7DC7}"/>
@@ -2628,7 +2661,7 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2678,8 +2711,8 @@
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2695,7 +2728,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13319760" y="7620"/>
-          <a:ext cx="0" cy="6134100"/>
+          <a:ext cx="0" cy="7399020"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3046,14 +3079,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>194.63</v>
+        <v>195.91</v>
       </c>
       <c r="E3" s="4">
-        <v>45926</v>
+        <v>45956</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45934</v>
+        <v>45956</v>
       </c>
       <c r="G3" s="4">
         <v>45967</v>
@@ -3077,7 +3110,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>19287.832999999999</v>
+        <v>19414.680999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -3118,7 +3151,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>23735.832999999999</v>
+        <v>23862.680999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3128,12 +3161,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D972C2C-CAC0-4237-B51D-27B3C5E485D0}">
-  <dimension ref="A2:AF43"/>
+  <dimension ref="A2:EI44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="33" width="8.88671875" style="1"/>
+    <col min="34" max="34" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:32">
@@ -3326,6 +3362,46 @@
         <f>SUM(K5:N5)</f>
         <v>7143.25</v>
       </c>
+      <c r="W5" s="6">
+        <f>V5*1.12</f>
+        <v>8000.4400000000005</v>
+      </c>
+      <c r="X5" s="6">
+        <f>W5*1.07</f>
+        <v>8560.470800000001</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>X5*1.04</f>
+        <v>8902.8896320000022</v>
+      </c>
+      <c r="Z5" s="6">
+        <f>Y5*1.03</f>
+        <v>9169.9763209600023</v>
+      </c>
+      <c r="AA5" s="6">
+        <f t="shared" ref="AA5:AF6" si="0">Z5*1.03</f>
+        <v>9445.0756105888031</v>
+      </c>
+      <c r="AB5" s="6">
+        <f t="shared" si="0"/>
+        <v>9728.4278789064683</v>
+      </c>
+      <c r="AC5" s="6">
+        <f t="shared" si="0"/>
+        <v>10020.280715273662</v>
+      </c>
+      <c r="AD5" s="6">
+        <f t="shared" si="0"/>
+        <v>10320.889136731872</v>
+      </c>
+      <c r="AE5" s="6">
+        <f t="shared" si="0"/>
+        <v>10630.515810833829</v>
+      </c>
+      <c r="AF5" s="6">
+        <f t="shared" si="0"/>
+        <v>10949.431285158844</v>
+      </c>
     </row>
     <row r="6" spans="1:32">
       <c r="B6" s="1" t="s">
@@ -3358,7 +3434,7 @@
         <v>590</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" ref="M6" si="0">I6*1.05</f>
+        <f t="shared" ref="M6" si="1">I6*1.05</f>
         <v>554.4</v>
       </c>
       <c r="N6" s="18">
@@ -3370,8 +3446,48 @@
         <v>2036</v>
       </c>
       <c r="V6" s="18">
-        <f t="shared" ref="V6:V7" si="1">SUM(K6:N6)</f>
+        <f t="shared" ref="V6:V7" si="2">SUM(K6:N6)</f>
         <v>2226.2800000000002</v>
+      </c>
+      <c r="W6" s="6">
+        <f>V6*1.1</f>
+        <v>2448.9080000000004</v>
+      </c>
+      <c r="X6" s="6">
+        <f>W6*1.07</f>
+        <v>2620.3315600000005</v>
+      </c>
+      <c r="Y6" s="6">
+        <f>X6*1.05</f>
+        <v>2751.3481380000007</v>
+      </c>
+      <c r="Z6" s="6">
+        <f>Y6*1.04</f>
+        <v>2861.4020635200009</v>
+      </c>
+      <c r="AA6" s="6">
+        <f>Z6*1.03</f>
+        <v>2947.2441254256009</v>
+      </c>
+      <c r="AB6" s="6">
+        <f t="shared" si="0"/>
+        <v>3035.6614491883693</v>
+      </c>
+      <c r="AC6" s="6">
+        <f t="shared" si="0"/>
+        <v>3126.7312926640202</v>
+      </c>
+      <c r="AD6" s="6">
+        <f t="shared" si="0"/>
+        <v>3220.5332314439411</v>
+      </c>
+      <c r="AE6" s="6">
+        <f t="shared" si="0"/>
+        <v>3317.1492283872594</v>
+      </c>
+      <c r="AF6" s="6">
+        <f t="shared" si="0"/>
+        <v>3416.6637052388774</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -3415,8 +3531,48 @@
         <v>49</v>
       </c>
       <c r="V7" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>32</v>
+      </c>
+      <c r="W7" s="6">
+        <f>V7*1.2</f>
+        <v>38.4</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" ref="X7:AF7" si="3">W7*1.2</f>
+        <v>46.08</v>
+      </c>
+      <c r="Y7" s="6">
+        <f t="shared" si="3"/>
+        <v>55.295999999999999</v>
+      </c>
+      <c r="Z7" s="6">
+        <f t="shared" si="3"/>
+        <v>66.355199999999996</v>
+      </c>
+      <c r="AA7" s="6">
+        <f t="shared" si="3"/>
+        <v>79.626239999999996</v>
+      </c>
+      <c r="AB7" s="6">
+        <f t="shared" si="3"/>
+        <v>95.551487999999992</v>
+      </c>
+      <c r="AC7" s="6">
+        <f t="shared" si="3"/>
+        <v>114.66178559999999</v>
+      </c>
+      <c r="AD7" s="6">
+        <f t="shared" si="3"/>
+        <v>137.59414271999998</v>
+      </c>
+      <c r="AE7" s="6">
+        <f t="shared" si="3"/>
+        <v>165.11297126399998</v>
+      </c>
+      <c r="AF7" s="6">
+        <f t="shared" si="3"/>
+        <v>198.13556551679997</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="2" customFormat="1">
@@ -3424,43 +3580,43 @@
         <v>42</v>
       </c>
       <c r="E8" s="15">
-        <f t="shared" ref="E8:N8" si="2">SUM(E5:E7)</f>
+        <f t="shared" ref="E8:N8" si="4">SUM(E5:E7)</f>
         <v>1856</v>
       </c>
       <c r="F8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3062</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1281</v>
       </c>
       <c r="H8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2203</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2073</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3108</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1522</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2164.65</v>
       </c>
       <c r="N8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3686.88</v>
       </c>
       <c r="U8" s="15">
@@ -3470,6 +3626,46 @@
       <c r="V8" s="15">
         <f>SUM(V5:V7)</f>
         <v>9401.5300000000007</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" ref="W8:AF8" si="5">SUM(W5:W7)</f>
+        <v>10487.748000000001</v>
+      </c>
+      <c r="X8" s="15">
+        <f t="shared" si="5"/>
+        <v>11226.882360000001</v>
+      </c>
+      <c r="Y8" s="15">
+        <f t="shared" si="5"/>
+        <v>11709.533770000004</v>
+      </c>
+      <c r="Z8" s="15">
+        <f t="shared" si="5"/>
+        <v>12097.733584480004</v>
+      </c>
+      <c r="AA8" s="15">
+        <f t="shared" si="5"/>
+        <v>12471.945976014404</v>
+      </c>
+      <c r="AB8" s="15">
+        <f t="shared" si="5"/>
+        <v>12859.640816094836</v>
+      </c>
+      <c r="AC8" s="15">
+        <f t="shared" si="5"/>
+        <v>13261.673793537682</v>
+      </c>
+      <c r="AD8" s="15">
+        <f t="shared" si="5"/>
+        <v>13679.016510895812</v>
+      </c>
+      <c r="AE8" s="15">
+        <f t="shared" si="5"/>
+        <v>14112.778010485088</v>
+      </c>
+      <c r="AF8" s="15">
+        <f t="shared" si="5"/>
+        <v>14564.230555914522</v>
       </c>
     </row>
     <row r="9" spans="1:32">
@@ -3516,41 +3712,81 @@
         <f>SUM(K9:N9)</f>
         <v>7539.2240000000002</v>
       </c>
+      <c r="W9" s="6">
+        <f>W8-W10</f>
+        <v>8390.1984000000011</v>
+      </c>
+      <c r="X9" s="6">
+        <f t="shared" ref="X9:AF9" si="6">X8-X10</f>
+        <v>8981.5058880000015</v>
+      </c>
+      <c r="Y9" s="6">
+        <f t="shared" si="6"/>
+        <v>9367.6270160000022</v>
+      </c>
+      <c r="Z9" s="6">
+        <f t="shared" si="6"/>
+        <v>9678.1868675840033</v>
+      </c>
+      <c r="AA9" s="6">
+        <f t="shared" si="6"/>
+        <v>9977.5567808115229</v>
+      </c>
+      <c r="AB9" s="6">
+        <f t="shared" si="6"/>
+        <v>10287.712652875869</v>
+      </c>
+      <c r="AC9" s="6">
+        <f t="shared" si="6"/>
+        <v>10609.339034830145</v>
+      </c>
+      <c r="AD9" s="6">
+        <f t="shared" si="6"/>
+        <v>10943.21320871665</v>
+      </c>
+      <c r="AE9" s="6">
+        <f t="shared" si="6"/>
+        <v>11290.22240838807</v>
+      </c>
+      <c r="AF9" s="6">
+        <f t="shared" si="6"/>
+        <v>11651.384444731619</v>
+      </c>
     </row>
     <row r="10" spans="1:32" s="2" customFormat="1">
       <c r="B10" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="15">
-        <f t="shared" ref="E10:L10" si="3">E8-E9</f>
+        <f t="shared" ref="E10:L10" si="7">E8-E9</f>
         <v>383</v>
       </c>
       <c r="F10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>582</v>
       </c>
       <c r="G10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>285</v>
       </c>
       <c r="H10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>454</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>416</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>621</v>
       </c>
       <c r="K10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>281</v>
       </c>
       <c r="L10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>411</v>
       </c>
       <c r="M10" s="17">
@@ -3568,6 +3804,46 @@
       <c r="V10" s="15">
         <f>V8-V9</f>
         <v>1862.3060000000005</v>
+      </c>
+      <c r="W10" s="17">
+        <f>W8*0.2</f>
+        <v>2097.5496000000003</v>
+      </c>
+      <c r="X10" s="17">
+        <f t="shared" ref="X10:AF10" si="8">X8*0.2</f>
+        <v>2245.3764720000004</v>
+      </c>
+      <c r="Y10" s="17">
+        <f t="shared" si="8"/>
+        <v>2341.906754000001</v>
+      </c>
+      <c r="Z10" s="17">
+        <f t="shared" si="8"/>
+        <v>2419.5467168960008</v>
+      </c>
+      <c r="AA10" s="17">
+        <f t="shared" si="8"/>
+        <v>2494.3891952028807</v>
+      </c>
+      <c r="AB10" s="17">
+        <f t="shared" si="8"/>
+        <v>2571.9281632189673</v>
+      </c>
+      <c r="AC10" s="17">
+        <f t="shared" si="8"/>
+        <v>2652.3347587075368</v>
+      </c>
+      <c r="AD10" s="17">
+        <f t="shared" si="8"/>
+        <v>2735.8033021791625</v>
+      </c>
+      <c r="AE10" s="17">
+        <f t="shared" si="8"/>
+        <v>2822.555602097018</v>
+      </c>
+      <c r="AF10" s="17">
+        <f t="shared" si="8"/>
+        <v>2912.8461111829047</v>
       </c>
     </row>
     <row r="11" spans="1:32">
@@ -3607,12 +3883,52 @@
         <v>139.05000000000001</v>
       </c>
       <c r="U11" s="18">
-        <f t="shared" ref="U11:U15" si="4">SUM(G11:J11)</f>
+        <f t="shared" ref="U11:U15" si="9">SUM(G11:J11)</f>
         <v>478</v>
       </c>
       <c r="V11" s="18">
-        <f t="shared" ref="V11:V15" si="5">SUM(K11:N11)</f>
+        <f t="shared" ref="V11:V15" si="10">SUM(K11:N11)</f>
         <v>477.56</v>
+      </c>
+      <c r="W11" s="6">
+        <f>V11*1.01</f>
+        <v>482.3356</v>
+      </c>
+      <c r="X11" s="6">
+        <f t="shared" ref="X11:Y11" si="11">W11*1.01</f>
+        <v>487.15895599999999</v>
+      </c>
+      <c r="Y11" s="6">
+        <f t="shared" si="11"/>
+        <v>492.03054556000001</v>
+      </c>
+      <c r="Z11" s="6">
+        <f t="shared" ref="Z11:AF11" si="12">Y11*1.01</f>
+        <v>496.95085101559999</v>
+      </c>
+      <c r="AA11" s="6">
+        <f t="shared" si="12"/>
+        <v>501.920359525756</v>
+      </c>
+      <c r="AB11" s="6">
+        <f t="shared" si="12"/>
+        <v>506.93956312101358</v>
+      </c>
+      <c r="AC11" s="6">
+        <f t="shared" si="12"/>
+        <v>512.00895875222375</v>
+      </c>
+      <c r="AD11" s="6">
+        <f t="shared" si="12"/>
+        <v>517.12904833974596</v>
+      </c>
+      <c r="AE11" s="6">
+        <f t="shared" si="12"/>
+        <v>522.30033882314342</v>
+      </c>
+      <c r="AF11" s="6">
+        <f t="shared" si="12"/>
+        <v>527.52334221137482</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -3652,12 +3968,52 @@
         <v>123.42</v>
       </c>
       <c r="U12" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>352</v>
       </c>
       <c r="V12" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>289.87</v>
+      </c>
+      <c r="W12" s="6">
+        <f>V12*1.05</f>
+        <v>304.36350000000004</v>
+      </c>
+      <c r="X12" s="6">
+        <f>W12*1.03</f>
+        <v>313.49440500000003</v>
+      </c>
+      <c r="Y12" s="6">
+        <f>X12*1.02</f>
+        <v>319.76429310000003</v>
+      </c>
+      <c r="Z12" s="6">
+        <f t="shared" ref="Z12:AF12" si="13">Y12*1.02</f>
+        <v>326.15957896200001</v>
+      </c>
+      <c r="AA12" s="6">
+        <f t="shared" si="13"/>
+        <v>332.68277054124002</v>
+      </c>
+      <c r="AB12" s="6">
+        <f t="shared" si="13"/>
+        <v>339.33642595206481</v>
+      </c>
+      <c r="AC12" s="6">
+        <f t="shared" si="13"/>
+        <v>346.12315447110609</v>
+      </c>
+      <c r="AD12" s="6">
+        <f t="shared" si="13"/>
+        <v>353.04561756052823</v>
+      </c>
+      <c r="AE12" s="6">
+        <f t="shared" si="13"/>
+        <v>360.10652991173879</v>
+      </c>
+      <c r="AF12" s="6">
+        <f t="shared" si="13"/>
+        <v>367.30866050997355</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -3695,12 +4051,52 @@
         <v>15</v>
       </c>
       <c r="U13" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>63</v>
       </c>
       <c r="V13" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>44</v>
+      </c>
+      <c r="W13" s="6">
+        <f>V13*1.05</f>
+        <v>46.2</v>
+      </c>
+      <c r="X13" s="6">
+        <f t="shared" ref="X13:AF13" si="14">W13*1.05</f>
+        <v>48.510000000000005</v>
+      </c>
+      <c r="Y13" s="6">
+        <f t="shared" si="14"/>
+        <v>50.935500000000005</v>
+      </c>
+      <c r="Z13" s="6">
+        <f t="shared" si="14"/>
+        <v>53.482275000000008</v>
+      </c>
+      <c r="AA13" s="6">
+        <f t="shared" si="14"/>
+        <v>56.156388750000012</v>
+      </c>
+      <c r="AB13" s="6">
+        <f t="shared" si="14"/>
+        <v>58.964208187500013</v>
+      </c>
+      <c r="AC13" s="6">
+        <f t="shared" si="14"/>
+        <v>61.912418596875014</v>
+      </c>
+      <c r="AD13" s="6">
+        <f t="shared" si="14"/>
+        <v>65.008039526718761</v>
+      </c>
+      <c r="AE13" s="6">
+        <f t="shared" si="14"/>
+        <v>68.258441503054698</v>
+      </c>
+      <c r="AF13" s="6">
+        <f t="shared" si="14"/>
+        <v>71.671363578207433</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -3739,11 +4135,41 @@
         <v>0</v>
       </c>
       <c r="U14" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="V14" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="6">
+        <v>0</v>
+      </c>
+      <c r="X14" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3782,11 +4208,41 @@
         <v>0</v>
       </c>
       <c r="U15" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="V15" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="6">
+        <v>0</v>
+      </c>
+      <c r="X15" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3795,43 +4251,43 @@
         <v>19</v>
       </c>
       <c r="E16" s="19">
-        <f t="shared" ref="E16:N16" si="6">SUM(E11:E15)</f>
+        <f t="shared" ref="E16:N16" si="15">SUM(E11:E15)</f>
         <v>186</v>
       </c>
       <c r="F16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>371</v>
       </c>
       <c r="G16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>141</v>
       </c>
       <c r="H16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>263</v>
       </c>
       <c r="I16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="J16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>279</v>
       </c>
       <c r="K16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>104</v>
       </c>
       <c r="L16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>206</v>
       </c>
       <c r="M16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>223.96</v>
       </c>
       <c r="N16" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>277.47000000000003</v>
       </c>
       <c r="U16" s="19">
@@ -3842,49 +4298,89 @@
         <f>SUM(V11:V15)</f>
         <v>811.43000000000006</v>
       </c>
+      <c r="W16" s="19">
+        <f>SUM(W11:W15)</f>
+        <v>832.89910000000009</v>
+      </c>
+      <c r="X16" s="19">
+        <f t="shared" ref="X16:AF16" si="16">SUM(X11:X15)</f>
+        <v>849.16336100000001</v>
+      </c>
+      <c r="Y16" s="19">
+        <f t="shared" si="16"/>
+        <v>862.73033866000014</v>
+      </c>
+      <c r="Z16" s="19">
+        <f t="shared" si="16"/>
+        <v>876.59270497759996</v>
+      </c>
+      <c r="AA16" s="19">
+        <f t="shared" si="16"/>
+        <v>890.75951881699609</v>
+      </c>
+      <c r="AB16" s="19">
+        <f t="shared" si="16"/>
+        <v>905.24019726057838</v>
+      </c>
+      <c r="AC16" s="19">
+        <f t="shared" si="16"/>
+        <v>920.04453182020484</v>
+      </c>
+      <c r="AD16" s="19">
+        <f t="shared" si="16"/>
+        <v>935.18270542699304</v>
+      </c>
+      <c r="AE16" s="19">
+        <f t="shared" si="16"/>
+        <v>950.66531023793686</v>
+      </c>
+      <c r="AF16" s="19">
+        <f t="shared" si="16"/>
+        <v>966.50336629955575</v>
+      </c>
     </row>
-    <row r="17" spans="2:22" s="2" customFormat="1">
+    <row r="17" spans="2:139" s="2" customFormat="1">
       <c r="B17" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="15">
-        <f t="shared" ref="E17:N17" si="7">E10-E16</f>
+        <f t="shared" ref="E17:N17" si="17">E10-E16</f>
         <v>197</v>
       </c>
       <c r="F17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>211</v>
       </c>
       <c r="G17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>144</v>
       </c>
       <c r="H17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>191</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>201</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>342</v>
       </c>
       <c r="K17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>177</v>
       </c>
       <c r="L17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>205</v>
       </c>
       <c r="M17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>208.97000000000006</v>
       </c>
       <c r="N17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>459.90600000000006</v>
       </c>
       <c r="U17" s="15">
@@ -3895,8 +4391,48 @@
         <f>V10-V16</f>
         <v>1050.8760000000004</v>
       </c>
+      <c r="W17" s="15">
+        <f>W10-W16</f>
+        <v>1264.6505000000002</v>
+      </c>
+      <c r="X17" s="15">
+        <f t="shared" ref="X17:AF17" si="18">X10-X16</f>
+        <v>1396.2131110000005</v>
+      </c>
+      <c r="Y17" s="15">
+        <f t="shared" si="18"/>
+        <v>1479.1764153400009</v>
+      </c>
+      <c r="Z17" s="15">
+        <f t="shared" si="18"/>
+        <v>1542.9540119184007</v>
+      </c>
+      <c r="AA17" s="15">
+        <f t="shared" si="18"/>
+        <v>1603.6296763858845</v>
+      </c>
+      <c r="AB17" s="15">
+        <f t="shared" si="18"/>
+        <v>1666.6879659583888</v>
+      </c>
+      <c r="AC17" s="15">
+        <f t="shared" si="18"/>
+        <v>1732.290226887332</v>
+      </c>
+      <c r="AD17" s="15">
+        <f t="shared" si="18"/>
+        <v>1800.6205967521696</v>
+      </c>
+      <c r="AE17" s="15">
+        <f t="shared" si="18"/>
+        <v>1871.8902918590811</v>
+      </c>
+      <c r="AF17" s="15">
+        <f t="shared" si="18"/>
+        <v>1946.342744883349</v>
+      </c>
     </row>
-    <row r="18" spans="2:22">
+    <row r="18" spans="2:139">
       <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
@@ -3933,15 +4469,55 @@
         <v>305.91000000000003</v>
       </c>
       <c r="U18" s="18">
-        <f t="shared" ref="U18:U19" si="8">SUM(G18:J18)</f>
+        <f t="shared" ref="U18:U19" si="19">SUM(G18:J18)</f>
         <v>842</v>
       </c>
       <c r="V18" s="18">
-        <f t="shared" ref="V18:V19" si="9">SUM(K18:N18)</f>
+        <f t="shared" ref="V18:V19" si="20">SUM(K18:N18)</f>
         <v>758.05</v>
       </c>
+      <c r="W18" s="6">
+        <f>V18*1.03</f>
+        <v>780.79149999999993</v>
+      </c>
+      <c r="X18" s="6">
+        <f t="shared" ref="X18:AF18" si="21">W18*1.03</f>
+        <v>804.21524499999998</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="21"/>
+        <v>828.34170234999999</v>
+      </c>
+      <c r="Z18" s="6">
+        <f t="shared" si="21"/>
+        <v>853.1919534205</v>
+      </c>
+      <c r="AA18" s="6">
+        <f t="shared" si="21"/>
+        <v>878.78771202311498</v>
+      </c>
+      <c r="AB18" s="6">
+        <f t="shared" si="21"/>
+        <v>905.15134338380847</v>
+      </c>
+      <c r="AC18" s="6">
+        <f t="shared" si="21"/>
+        <v>932.30588368532278</v>
+      </c>
+      <c r="AD18" s="6">
+        <f t="shared" si="21"/>
+        <v>960.27506019588247</v>
+      </c>
+      <c r="AE18" s="6">
+        <f t="shared" si="21"/>
+        <v>989.08331200175894</v>
+      </c>
+      <c r="AF18" s="6">
+        <f t="shared" si="21"/>
+        <v>1018.7558113618118</v>
+      </c>
     </row>
-    <row r="19" spans="2:22">
+    <row r="19" spans="2:139">
       <c r="B19" s="8" t="s">
         <v>22</v>
       </c>
@@ -3970,64 +4546,104 @@
         <v>-134</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" ref="M19:N19" si="10">I19*1.03</f>
+        <f t="shared" ref="M19:N19" si="22">I19*1.03</f>
         <v>-52.53</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>-6.18</v>
       </c>
       <c r="U19" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="19"/>
         <v>-220</v>
       </c>
       <c r="V19" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>-204.71</v>
       </c>
+      <c r="W19" s="6">
+        <f>V19*1.03</f>
+        <v>-210.85130000000001</v>
+      </c>
+      <c r="X19" s="6">
+        <f t="shared" ref="X19:AF19" si="23">W19*1.03</f>
+        <v>-217.176839</v>
+      </c>
+      <c r="Y19" s="6">
+        <f t="shared" si="23"/>
+        <v>-223.69214417000001</v>
+      </c>
+      <c r="Z19" s="6">
+        <f t="shared" si="23"/>
+        <v>-230.40290849510001</v>
+      </c>
+      <c r="AA19" s="6">
+        <f t="shared" si="23"/>
+        <v>-237.31499574995303</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="23"/>
+        <v>-244.43444562245162</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="23"/>
+        <v>-251.76747899112519</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="23"/>
+        <v>-259.32050336085894</v>
+      </c>
+      <c r="AE19" s="6">
+        <f t="shared" si="23"/>
+        <v>-267.1001184616847</v>
+      </c>
+      <c r="AF19" s="6">
+        <f t="shared" si="23"/>
+        <v>-275.11312201553523</v>
+      </c>
     </row>
-    <row r="20" spans="2:22" s="2" customFormat="1">
+    <row r="20" spans="2:139" s="2" customFormat="1">
       <c r="B20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="15">
-        <f t="shared" ref="E20:N20" si="11">E17-E18-E19</f>
+        <f t="shared" ref="E20:N20" si="24">E17-E18-E19</f>
         <v>-39</v>
       </c>
       <c r="F20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>222</v>
       </c>
       <c r="G20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>94</v>
       </c>
       <c r="H20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>-3</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>114</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>51</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>45</v>
       </c>
       <c r="L20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>173</v>
       </c>
       <c r="M20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>119.36000000000004</v>
       </c>
       <c r="N20" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="24"/>
         <v>160.17600000000004</v>
       </c>
       <c r="U20" s="15">
@@ -4038,8 +4654,48 @@
         <f>V17-V18-V19</f>
         <v>497.53600000000051</v>
       </c>
+      <c r="W20" s="15">
+        <f>W17-W18-W19</f>
+        <v>694.7103000000003</v>
+      </c>
+      <c r="X20" s="15">
+        <f t="shared" ref="X20:AF20" si="25">X17-X18-X19</f>
+        <v>809.17470500000047</v>
+      </c>
+      <c r="Y20" s="15">
+        <f t="shared" si="25"/>
+        <v>874.52685716000087</v>
+      </c>
+      <c r="Z20" s="15">
+        <f t="shared" si="25"/>
+        <v>920.16496699300069</v>
+      </c>
+      <c r="AA20" s="15">
+        <f t="shared" si="25"/>
+        <v>962.15696011272257</v>
+      </c>
+      <c r="AB20" s="15">
+        <f t="shared" si="25"/>
+        <v>1005.9710681970319</v>
+      </c>
+      <c r="AC20" s="15">
+        <f t="shared" si="25"/>
+        <v>1051.7518221931343</v>
+      </c>
+      <c r="AD20" s="15">
+        <f t="shared" si="25"/>
+        <v>1099.666039917146</v>
+      </c>
+      <c r="AE20" s="15">
+        <f t="shared" si="25"/>
+        <v>1149.9070983190068</v>
+      </c>
+      <c r="AF20" s="15">
+        <f t="shared" si="25"/>
+        <v>1202.7000555370726</v>
+      </c>
     </row>
-    <row r="21" spans="2:22">
+    <row r="21" spans="2:139">
       <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
@@ -4074,15 +4730,55 @@
         <v>0</v>
       </c>
       <c r="U21" s="18">
-        <f t="shared" ref="U21:U22" si="12">SUM(G21:J21)</f>
+        <f t="shared" ref="U21:U22" si="26">SUM(G21:J21)</f>
         <v>-114</v>
       </c>
       <c r="V21" s="18">
-        <f t="shared" ref="V21:V22" si="13">SUM(K21:N21)</f>
+        <f t="shared" ref="V21:V22" si="27">SUM(K21:N21)</f>
         <v>-19</v>
       </c>
+      <c r="W21" s="6">
+        <f>W20*0.15</f>
+        <v>104.20654500000005</v>
+      </c>
+      <c r="X21" s="6">
+        <f t="shared" ref="X21:AF21" si="28">X20*0.15</f>
+        <v>121.37620575000007</v>
+      </c>
+      <c r="Y21" s="6">
+        <f t="shared" si="28"/>
+        <v>131.17902857400011</v>
+      </c>
+      <c r="Z21" s="6">
+        <f t="shared" si="28"/>
+        <v>138.02474504895011</v>
+      </c>
+      <c r="AA21" s="6">
+        <f t="shared" si="28"/>
+        <v>144.32354401690839</v>
+      </c>
+      <c r="AB21" s="6">
+        <f t="shared" si="28"/>
+        <v>150.89566022955478</v>
+      </c>
+      <c r="AC21" s="6">
+        <f t="shared" si="28"/>
+        <v>157.76277332897016</v>
+      </c>
+      <c r="AD21" s="6">
+        <f t="shared" si="28"/>
+        <v>164.9499059875719</v>
+      </c>
+      <c r="AE21" s="6">
+        <f t="shared" si="28"/>
+        <v>172.486064747851</v>
+      </c>
+      <c r="AF21" s="6">
+        <f t="shared" si="28"/>
+        <v>180.40500833056089</v>
+      </c>
     </row>
-    <row r="22" spans="2:22">
+    <row r="22" spans="2:139">
       <c r="B22" s="11" t="s">
         <v>25</v>
       </c>
@@ -4117,56 +4813,96 @@
         <v>0</v>
       </c>
       <c r="U22" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="V22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="27"/>
         <v>15</v>
       </c>
+      <c r="W22" s="6">
+        <f>V22*1.03</f>
+        <v>15.450000000000001</v>
+      </c>
+      <c r="X22" s="6">
+        <f t="shared" ref="X22:AF22" si="29">W22*1.03</f>
+        <v>15.913500000000001</v>
+      </c>
+      <c r="Y22" s="6">
+        <f t="shared" si="29"/>
+        <v>16.390905</v>
+      </c>
+      <c r="Z22" s="6">
+        <f t="shared" si="29"/>
+        <v>16.882632149999999</v>
+      </c>
+      <c r="AA22" s="6">
+        <f t="shared" si="29"/>
+        <v>17.3891111145</v>
+      </c>
+      <c r="AB22" s="6">
+        <f t="shared" si="29"/>
+        <v>17.910784447935001</v>
+      </c>
+      <c r="AC22" s="6">
+        <f t="shared" si="29"/>
+        <v>18.448107981373052</v>
+      </c>
+      <c r="AD22" s="6">
+        <f t="shared" si="29"/>
+        <v>19.001551220814246</v>
+      </c>
+      <c r="AE22" s="6">
+        <f t="shared" si="29"/>
+        <v>19.571597757438674</v>
+      </c>
+      <c r="AF22" s="6">
+        <f t="shared" si="29"/>
+        <v>20.158745690161833</v>
+      </c>
     </row>
-    <row r="23" spans="2:22" s="2" customFormat="1">
+    <row r="23" spans="2:139" s="2" customFormat="1">
       <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="15">
-        <f t="shared" ref="E23:L23" si="14">E20-E21-E22</f>
+        <f t="shared" ref="E23:L23" si="30">E20-E21-E22</f>
         <v>-37</v>
       </c>
       <c r="F23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>215</v>
       </c>
       <c r="G23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>110</v>
       </c>
       <c r="H23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>19</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>117</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>124</v>
       </c>
       <c r="K23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>44</v>
       </c>
       <c r="L23" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="30"/>
         <v>178</v>
       </c>
       <c r="M23" s="15">
-        <f t="shared" ref="M23:N23" si="15">M20-M21-M22</f>
+        <f t="shared" ref="M23:N23" si="31">M20-M21-M22</f>
         <v>119.36000000000004</v>
       </c>
       <c r="N23" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="31"/>
         <v>160.17600000000004</v>
       </c>
       <c r="U23" s="15">
@@ -4177,49 +4913,517 @@
         <f>V20-V21-V22</f>
         <v>501.53600000000051</v>
       </c>
+      <c r="W23" s="15">
+        <f>W20-W21-W22</f>
+        <v>575.05375500000025</v>
+      </c>
+      <c r="X23" s="15">
+        <f t="shared" ref="X23:AF23" si="32">X20-X21-X22</f>
+        <v>671.88499925000042</v>
+      </c>
+      <c r="Y23" s="15">
+        <f t="shared" si="32"/>
+        <v>726.95692358600081</v>
+      </c>
+      <c r="Z23" s="15">
+        <f t="shared" si="32"/>
+        <v>765.25758979405066</v>
+      </c>
+      <c r="AA23" s="15">
+        <f t="shared" si="32"/>
+        <v>800.44430498131419</v>
+      </c>
+      <c r="AB23" s="15">
+        <f t="shared" si="32"/>
+        <v>837.16462351954203</v>
+      </c>
+      <c r="AC23" s="15">
+        <f t="shared" si="32"/>
+        <v>875.54094088279112</v>
+      </c>
+      <c r="AD23" s="15">
+        <f t="shared" si="32"/>
+        <v>915.71458270875985</v>
+      </c>
+      <c r="AE23" s="15">
+        <f t="shared" si="32"/>
+        <v>957.84943581371704</v>
+      </c>
+      <c r="AF23" s="15">
+        <f t="shared" si="32"/>
+        <v>1002.1363015163498</v>
+      </c>
+      <c r="AG23" s="2">
+        <f>AF23*(1+$AI$31)</f>
+        <v>992.11493850118632</v>
+      </c>
+      <c r="AH23" s="2">
+        <f t="shared" ref="AH23:CS23" si="33">AG23*(1+$AI$31)</f>
+        <v>982.19378911617446</v>
+      </c>
+      <c r="AI23" s="2">
+        <f t="shared" si="33"/>
+        <v>972.37185122501273</v>
+      </c>
+      <c r="AJ23" s="2">
+        <f t="shared" si="33"/>
+        <v>962.64813271276262</v>
+      </c>
+      <c r="AK23" s="2">
+        <f t="shared" si="33"/>
+        <v>953.02165138563498</v>
+      </c>
+      <c r="AL23" s="2">
+        <f t="shared" si="33"/>
+        <v>943.49143487177867</v>
+      </c>
+      <c r="AM23" s="2">
+        <f t="shared" si="33"/>
+        <v>934.05652052306084</v>
+      </c>
+      <c r="AN23" s="2">
+        <f t="shared" si="33"/>
+        <v>924.71595531783021</v>
+      </c>
+      <c r="AO23" s="2">
+        <f t="shared" si="33"/>
+        <v>915.46879576465187</v>
+      </c>
+      <c r="AP23" s="2">
+        <f t="shared" si="33"/>
+        <v>906.31410780700537</v>
+      </c>
+      <c r="AQ23" s="2">
+        <f t="shared" si="33"/>
+        <v>897.25096672893528</v>
+      </c>
+      <c r="AR23" s="2">
+        <f t="shared" si="33"/>
+        <v>888.2784570616459</v>
+      </c>
+      <c r="AS23" s="2">
+        <f t="shared" si="33"/>
+        <v>879.39567249102947</v>
+      </c>
+      <c r="AT23" s="2">
+        <f t="shared" si="33"/>
+        <v>870.60171576611913</v>
+      </c>
+      <c r="AU23" s="2">
+        <f t="shared" si="33"/>
+        <v>861.89569860845791</v>
+      </c>
+      <c r="AV23" s="2">
+        <f t="shared" si="33"/>
+        <v>853.27674162237327</v>
+      </c>
+      <c r="AW23" s="2">
+        <f t="shared" si="33"/>
+        <v>844.74397420614957</v>
+      </c>
+      <c r="AX23" s="2">
+        <f t="shared" si="33"/>
+        <v>836.29653446408804</v>
+      </c>
+      <c r="AY23" s="2">
+        <f t="shared" si="33"/>
+        <v>827.93356911944716</v>
+      </c>
+      <c r="AZ23" s="2">
+        <f t="shared" si="33"/>
+        <v>819.65423342825272</v>
+      </c>
+      <c r="BA23" s="2">
+        <f t="shared" si="33"/>
+        <v>811.4576910939702</v>
+      </c>
+      <c r="BB23" s="2">
+        <f t="shared" si="33"/>
+        <v>803.34311418303048</v>
+      </c>
+      <c r="BC23" s="2">
+        <f t="shared" si="33"/>
+        <v>795.30968304120017</v>
+      </c>
+      <c r="BD23" s="2">
+        <f t="shared" si="33"/>
+        <v>787.35658621078812</v>
+      </c>
+      <c r="BE23" s="2">
+        <f t="shared" si="33"/>
+        <v>779.48302034868027</v>
+      </c>
+      <c r="BF23" s="2">
+        <f t="shared" si="33"/>
+        <v>771.68819014519352</v>
+      </c>
+      <c r="BG23" s="2">
+        <f t="shared" si="33"/>
+        <v>763.97130824374153</v>
+      </c>
+      <c r="BH23" s="2">
+        <f t="shared" si="33"/>
+        <v>756.33159516130411</v>
+      </c>
+      <c r="BI23" s="2">
+        <f t="shared" si="33"/>
+        <v>748.76827920969106</v>
+      </c>
+      <c r="BJ23" s="2">
+        <f t="shared" si="33"/>
+        <v>741.2805964175941</v>
+      </c>
+      <c r="BK23" s="2">
+        <f t="shared" si="33"/>
+        <v>733.86779045341814</v>
+      </c>
+      <c r="BL23" s="2">
+        <f t="shared" si="33"/>
+        <v>726.52911254888397</v>
+      </c>
+      <c r="BM23" s="2">
+        <f t="shared" si="33"/>
+        <v>719.26382142339514</v>
+      </c>
+      <c r="BN23" s="2">
+        <f t="shared" si="33"/>
+        <v>712.07118320916118</v>
+      </c>
+      <c r="BO23" s="2">
+        <f t="shared" si="33"/>
+        <v>704.95047137706956</v>
+      </c>
+      <c r="BP23" s="2">
+        <f t="shared" si="33"/>
+        <v>697.90096666329885</v>
+      </c>
+      <c r="BQ23" s="2">
+        <f t="shared" si="33"/>
+        <v>690.92195699666581</v>
+      </c>
+      <c r="BR23" s="2">
+        <f t="shared" si="33"/>
+        <v>684.01273742669912</v>
+      </c>
+      <c r="BS23" s="2">
+        <f t="shared" si="33"/>
+        <v>677.17261005243211</v>
+      </c>
+      <c r="BT23" s="2">
+        <f t="shared" si="33"/>
+        <v>670.40088395190776</v>
+      </c>
+      <c r="BU23" s="2">
+        <f t="shared" si="33"/>
+        <v>663.69687511238862</v>
+      </c>
+      <c r="BV23" s="2">
+        <f t="shared" si="33"/>
+        <v>657.05990636126478</v>
+      </c>
+      <c r="BW23" s="2">
+        <f t="shared" si="33"/>
+        <v>650.48930729765209</v>
+      </c>
+      <c r="BX23" s="2">
+        <f t="shared" si="33"/>
+        <v>643.98441422467556</v>
+      </c>
+      <c r="BY23" s="2">
+        <f t="shared" si="33"/>
+        <v>637.54457008242878</v>
+      </c>
+      <c r="BZ23" s="2">
+        <f t="shared" si="33"/>
+        <v>631.16912438160443</v>
+      </c>
+      <c r="CA23" s="2">
+        <f t="shared" si="33"/>
+        <v>624.85743313778835</v>
+      </c>
+      <c r="CB23" s="2">
+        <f t="shared" si="33"/>
+        <v>618.60885880641047</v>
+      </c>
+      <c r="CC23" s="2">
+        <f t="shared" si="33"/>
+        <v>612.42277021834639</v>
+      </c>
+      <c r="CD23" s="2">
+        <f t="shared" si="33"/>
+        <v>606.29854251616291</v>
+      </c>
+      <c r="CE23" s="2">
+        <f t="shared" si="33"/>
+        <v>600.23555709100128</v>
+      </c>
+      <c r="CF23" s="2">
+        <f t="shared" si="33"/>
+        <v>594.23320152009126</v>
+      </c>
+      <c r="CG23" s="2">
+        <f t="shared" si="33"/>
+        <v>588.29086950489034</v>
+      </c>
+      <c r="CH23" s="2">
+        <f t="shared" si="33"/>
+        <v>582.40796080984148</v>
+      </c>
+      <c r="CI23" s="2">
+        <f t="shared" si="33"/>
+        <v>576.58388120174311</v>
+      </c>
+      <c r="CJ23" s="2">
+        <f t="shared" si="33"/>
+        <v>570.81804238972563</v>
+      </c>
+      <c r="CK23" s="2">
+        <f t="shared" si="33"/>
+        <v>565.10986196582837</v>
+      </c>
+      <c r="CL23" s="2">
+        <f t="shared" si="33"/>
+        <v>559.45876334617003</v>
+      </c>
+      <c r="CM23" s="2">
+        <f t="shared" si="33"/>
+        <v>553.86417571270829</v>
+      </c>
+      <c r="CN23" s="2">
+        <f t="shared" si="33"/>
+        <v>548.32553395558125</v>
+      </c>
+      <c r="CO23" s="2">
+        <f t="shared" si="33"/>
+        <v>542.8422786160254</v>
+      </c>
+      <c r="CP23" s="2">
+        <f t="shared" si="33"/>
+        <v>537.41385582986516</v>
+      </c>
+      <c r="CQ23" s="2">
+        <f t="shared" si="33"/>
+        <v>532.03971727156647</v>
+      </c>
+      <c r="CR23" s="2">
+        <f t="shared" si="33"/>
+        <v>526.71932009885086</v>
+      </c>
+      <c r="CS23" s="2">
+        <f t="shared" si="33"/>
+        <v>521.4521268978624</v>
+      </c>
+      <c r="CT23" s="2">
+        <f t="shared" ref="CT23:EI23" si="34">CS23*(1+$AI$31)</f>
+        <v>516.23760562888378</v>
+      </c>
+      <c r="CU23" s="2">
+        <f t="shared" si="34"/>
+        <v>511.07522957259494</v>
+      </c>
+      <c r="CV23" s="2">
+        <f t="shared" si="34"/>
+        <v>505.96447727686899</v>
+      </c>
+      <c r="CW23" s="2">
+        <f t="shared" si="34"/>
+        <v>500.90483250410028</v>
+      </c>
+      <c r="CX23" s="2">
+        <f t="shared" si="34"/>
+        <v>495.89578417905926</v>
+      </c>
+      <c r="CY23" s="2">
+        <f t="shared" si="34"/>
+        <v>490.93682633726866</v>
+      </c>
+      <c r="CZ23" s="2">
+        <f t="shared" si="34"/>
+        <v>486.02745807389596</v>
+      </c>
+      <c r="DA23" s="2">
+        <f t="shared" si="34"/>
+        <v>481.16718349315698</v>
+      </c>
+      <c r="DB23" s="2">
+        <f t="shared" si="34"/>
+        <v>476.3555116582254</v>
+      </c>
+      <c r="DC23" s="2">
+        <f t="shared" si="34"/>
+        <v>471.59195654164313</v>
+      </c>
+      <c r="DD23" s="2">
+        <f t="shared" si="34"/>
+        <v>466.87603697622671</v>
+      </c>
+      <c r="DE23" s="2">
+        <f t="shared" si="34"/>
+        <v>462.20727660646446</v>
+      </c>
+      <c r="DF23" s="2">
+        <f t="shared" si="34"/>
+        <v>457.5852038403998</v>
+      </c>
+      <c r="DG23" s="2">
+        <f t="shared" si="34"/>
+        <v>453.00935180199582</v>
+      </c>
+      <c r="DH23" s="2">
+        <f t="shared" si="34"/>
+        <v>448.47925828397587</v>
+      </c>
+      <c r="DI23" s="2">
+        <f t="shared" si="34"/>
+        <v>443.99446570113611</v>
+      </c>
+      <c r="DJ23" s="2">
+        <f t="shared" si="34"/>
+        <v>439.55452104412473</v>
+      </c>
+      <c r="DK23" s="2">
+        <f t="shared" si="34"/>
+        <v>435.15897583368348</v>
+      </c>
+      <c r="DL23" s="2">
+        <f t="shared" si="34"/>
+        <v>430.80738607534664</v>
+      </c>
+      <c r="DM23" s="2">
+        <f t="shared" si="34"/>
+        <v>426.49931221459315</v>
+      </c>
+      <c r="DN23" s="2">
+        <f t="shared" si="34"/>
+        <v>422.23431909244721</v>
+      </c>
+      <c r="DO23" s="2">
+        <f t="shared" si="34"/>
+        <v>418.01197590152276</v>
+      </c>
+      <c r="DP23" s="2">
+        <f t="shared" si="34"/>
+        <v>413.83185614250755</v>
+      </c>
+      <c r="DQ23" s="2">
+        <f t="shared" si="34"/>
+        <v>409.69353758108247</v>
+      </c>
+      <c r="DR23" s="2">
+        <f t="shared" si="34"/>
+        <v>405.59660220527167</v>
+      </c>
+      <c r="DS23" s="2">
+        <f t="shared" si="34"/>
+        <v>401.54063618321896</v>
+      </c>
+      <c r="DT23" s="2">
+        <f t="shared" si="34"/>
+        <v>397.52522982138674</v>
+      </c>
+      <c r="DU23" s="2">
+        <f t="shared" si="34"/>
+        <v>393.54997752317286</v>
+      </c>
+      <c r="DV23" s="2">
+        <f t="shared" si="34"/>
+        <v>389.61447774794112</v>
+      </c>
+      <c r="DW23" s="2">
+        <f t="shared" si="34"/>
+        <v>385.71833297046169</v>
+      </c>
+      <c r="DX23" s="2">
+        <f t="shared" si="34"/>
+        <v>381.86114964075705</v>
+      </c>
+      <c r="DY23" s="2">
+        <f t="shared" si="34"/>
+        <v>378.04253814434946</v>
+      </c>
+      <c r="DZ23" s="2">
+        <f t="shared" si="34"/>
+        <v>374.26211276290599</v>
+      </c>
+      <c r="EA23" s="2">
+        <f t="shared" si="34"/>
+        <v>370.51949163527695</v>
+      </c>
+      <c r="EB23" s="2">
+        <f t="shared" si="34"/>
+        <v>366.8142967189242</v>
+      </c>
+      <c r="EC23" s="2">
+        <f t="shared" si="34"/>
+        <v>363.14615375173497</v>
+      </c>
+      <c r="ED23" s="2">
+        <f t="shared" si="34"/>
+        <v>359.51469221421763</v>
+      </c>
+      <c r="EE23" s="2">
+        <f t="shared" si="34"/>
+        <v>355.91954529207544</v>
+      </c>
+      <c r="EF23" s="2">
+        <f t="shared" si="34"/>
+        <v>352.36034983915471</v>
+      </c>
+      <c r="EG23" s="2">
+        <f t="shared" si="34"/>
+        <v>348.83674634076317</v>
+      </c>
+      <c r="EH23" s="2">
+        <f t="shared" si="34"/>
+        <v>345.34837887735551</v>
+      </c>
+      <c r="EI23" s="2">
+        <f t="shared" si="34"/>
+        <v>341.89489508858196</v>
+      </c>
     </row>
-    <row r="24" spans="2:22">
+    <row r="24" spans="2:139">
       <c r="B24" s="11" t="s">
         <v>2</v>
       </c>
       <c r="E24" s="6">
-        <f t="shared" ref="E24:L24" si="16">86.8+12.3</f>
+        <f t="shared" ref="E24:L24" si="35">86.8+12.3</f>
         <v>99.1</v>
       </c>
       <c r="F24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="H24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="I24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="J24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="K24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="L24" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="35"/>
         <v>99.1</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" ref="M24:N24" si="17">86.8+12.3</f>
+        <f t="shared" ref="M24:N24" si="36">86.8+12.3</f>
         <v>99.1</v>
       </c>
       <c r="N24" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="36"/>
         <v>99.1</v>
       </c>
       <c r="U24" s="6">
@@ -4230,49 +5434,89 @@
         <f>86.8+12.3</f>
         <v>99.1</v>
       </c>
+      <c r="W24" s="6">
+        <f>86.8+12.3</f>
+        <v>99.1</v>
+      </c>
+      <c r="X24" s="6">
+        <f t="shared" ref="X24:AF24" si="37">86.8+12.3</f>
+        <v>99.1</v>
+      </c>
+      <c r="Y24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="Z24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="AA24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="AB24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="AC24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="AD24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="AE24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
+      <c r="AF24" s="6">
+        <f t="shared" si="37"/>
+        <v>99.1</v>
+      </c>
     </row>
-    <row r="25" spans="2:22">
+    <row r="25" spans="2:139">
       <c r="B25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="14">
-        <f t="shared" ref="E25:L25" si="18">E23/E24</f>
+        <f t="shared" ref="E25:L25" si="38">E23/E24</f>
         <v>-0.37336024217961655</v>
       </c>
       <c r="F25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>2.1695257315842587</v>
       </c>
       <c r="G25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>1.109989909182644</v>
       </c>
       <c r="H25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>0.19172552976791121</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>1.1806256306760847</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>1.2512613521695257</v>
       </c>
       <c r="K25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>0.44399596367305755</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="38"/>
         <v>1.7961654894046419</v>
       </c>
       <c r="M25" s="14">
-        <f t="shared" ref="M25:N25" si="19">M23/M24</f>
+        <f t="shared" ref="M25:N25" si="39">M23/M24</f>
         <v>1.204439959636731</v>
       </c>
       <c r="N25" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="39"/>
         <v>1.6163067608476291</v>
       </c>
       <c r="U25" s="14">
@@ -4283,8 +5527,48 @@
         <f>V23/V24</f>
         <v>5.0609081735620638</v>
       </c>
+      <c r="W25" s="14">
+        <f>W23/W24</f>
+        <v>5.8027624117053511</v>
+      </c>
+      <c r="X25" s="14">
+        <f t="shared" ref="X25:AF25" si="40">X23/X24</f>
+        <v>6.7798688118062609</v>
+      </c>
+      <c r="Y25" s="14">
+        <f t="shared" si="40"/>
+        <v>7.3355895417356294</v>
+      </c>
+      <c r="Z25" s="14">
+        <f t="shared" si="40"/>
+        <v>7.722074569062066</v>
+      </c>
+      <c r="AA25" s="14">
+        <f t="shared" si="40"/>
+        <v>8.0771372853815766</v>
+      </c>
+      <c r="AB25" s="14">
+        <f t="shared" si="40"/>
+        <v>8.4476753130125335</v>
+      </c>
+      <c r="AC25" s="14">
+        <f t="shared" si="40"/>
+        <v>8.8349237223288721</v>
+      </c>
+      <c r="AD25" s="14">
+        <f t="shared" si="40"/>
+        <v>9.2403086045283533</v>
+      </c>
+      <c r="AE25" s="14">
+        <f t="shared" si="40"/>
+        <v>9.6654837115410395</v>
+      </c>
+      <c r="AF25" s="14">
+        <f t="shared" si="40"/>
+        <v>10.112374384625126</v>
+      </c>
     </row>
-    <row r="27" spans="2:22">
+    <row r="27" spans="2:139">
       <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
@@ -4309,449 +5593,943 @@
         <v>0.11805555555555558</v>
       </c>
     </row>
-    <row r="28" spans="2:22">
-      <c r="B28" s="1" t="s">
+    <row r="28" spans="2:139">
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+    </row>
+    <row r="29" spans="2:139">
+      <c r="B29" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16">
-        <f t="shared" ref="I28:L31" si="20">I5/E5-1</f>
-        <v>6.4200976971388712E-2</v>
-      </c>
-      <c r="J28" s="16">
-        <f t="shared" si="20"/>
-        <v>1.555814858031912E-3</v>
-      </c>
-      <c r="K28" s="16">
-        <f t="shared" si="20"/>
-        <v>0.28553459119496849</v>
-      </c>
-      <c r="L28" s="16">
-        <f t="shared" si="20"/>
-        <v>-0.1513353115727003</v>
-      </c>
-      <c r="M28" s="16">
-        <f t="shared" ref="M28:M31" si="21">M5/I5-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N28" s="16">
-        <f t="shared" ref="N28:N31" si="22">N5/J5-1</f>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="V28" s="16">
-        <f>V5/U5-1</f>
-        <v>8.5600303951367751E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:22">
-      <c r="B29" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
       <c r="I29" s="16">
-        <f t="shared" si="20"/>
-        <v>0.2753623188405796</v>
+        <f t="shared" ref="I29:L32" si="41">I5/E5-1</f>
+        <v>6.4200976971388712E-2</v>
       </c>
       <c r="J29" s="16">
-        <f t="shared" si="20"/>
-        <v>8.7136929460580825E-2</v>
+        <f t="shared" si="41"/>
+        <v>1.555814858031912E-3</v>
       </c>
       <c r="K29" s="16">
-        <f t="shared" si="20"/>
-        <v>3.7735849056603765E-2</v>
+        <f t="shared" si="41"/>
+        <v>0.28553459119496849</v>
       </c>
       <c r="L29" s="16">
-        <f t="shared" si="20"/>
-        <v>0.16370808678500981</v>
+        <f t="shared" si="41"/>
+        <v>-0.1513353115727003</v>
       </c>
       <c r="M29" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="M29:M32" si="42">M5/I5-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N29" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="N29:N32" si="43">N5/J5-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16">
+        <f>V5/U5-1</f>
+        <v>8.5600303951367751E-2</v>
+      </c>
+      <c r="W29" s="16">
+        <f t="shared" ref="W29:AF32" si="44">W5/V5-1</f>
         <v>0.12000000000000011</v>
       </c>
-      <c r="V29" s="16">
-        <f t="shared" ref="V29:V31" si="23">V6/U6-1</f>
-        <v>9.3457760314342053E-2</v>
+      <c r="X29" s="16">
+        <f t="shared" si="44"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="Y29" s="16">
+        <f t="shared" si="44"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="Z29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AA29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AB29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF29" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:22">
+    <row r="30" spans="2:139">
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
       <c r="I30" s="16">
-        <f t="shared" si="20"/>
-        <v>1.2222222222222223</v>
+        <f t="shared" si="41"/>
+        <v>0.2753623188405796</v>
       </c>
       <c r="J30" s="16">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>8.7136929460580825E-2</v>
       </c>
       <c r="K30" s="16">
-        <f t="shared" si="20"/>
-        <v>-0.44444444444444442</v>
+        <f t="shared" si="41"/>
+        <v>3.7735849056603765E-2</v>
       </c>
       <c r="L30" s="16">
-        <f t="shared" si="20"/>
-        <v>-0.27272727272727271</v>
+        <f t="shared" si="41"/>
+        <v>0.16370808678500981</v>
       </c>
       <c r="M30" s="16">
-        <f t="shared" si="21"/>
-        <v>-0.55000000000000004</v>
+        <f t="shared" si="42"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="N30" s="16">
-        <f t="shared" si="22"/>
-        <v>0.11111111111111116</v>
-      </c>
+        <f t="shared" si="43"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="U30" s="16"/>
       <c r="V30" s="16">
-        <f t="shared" si="23"/>
-        <v>-0.34693877551020413</v>
+        <f t="shared" ref="U30:V34" si="45">V6/U6-1</f>
+        <v>9.3457760314342053E-2</v>
+      </c>
+      <c r="W30" s="16">
+        <f t="shared" si="44"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="X30" s="16">
+        <f t="shared" si="44"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="Y30" s="16">
+        <f t="shared" si="44"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="Z30" s="16">
+        <f t="shared" si="44"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AA30" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AB30" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC30" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD30" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE30" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF30" s="16">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:22">
+    <row r="31" spans="2:139">
       <c r="B31" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="41"/>
+        <v>1.2222222222222223</v>
+      </c>
+      <c r="J31" s="16">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="16">
+        <f t="shared" si="41"/>
+        <v>-0.44444444444444442</v>
+      </c>
+      <c r="L31" s="16">
+        <f t="shared" si="41"/>
+        <v>-0.27272727272727271</v>
+      </c>
+      <c r="M31" s="16">
+        <f t="shared" si="42"/>
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="N31" s="16">
+        <f t="shared" si="43"/>
+        <v>0.11111111111111116</v>
+      </c>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16">
+        <f t="shared" si="45"/>
+        <v>-0.34693877551020413</v>
+      </c>
+      <c r="W31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="X31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="Y31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="Z31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AA31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AB31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AC31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AD31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AE31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AF31" s="16">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AH31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI31" s="16">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="32" spans="2:139">
+      <c r="B32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16">
+        <f t="shared" si="41"/>
         <v>0.1169181034482758</v>
       </c>
-      <c r="J31" s="16">
-        <f t="shared" si="20"/>
+      <c r="J32" s="16">
+        <f t="shared" si="41"/>
         <v>1.5022860875244959E-2</v>
       </c>
-      <c r="K31" s="16">
-        <f t="shared" si="20"/>
+      <c r="K32" s="16">
+        <f t="shared" si="41"/>
         <v>0.1881342701014832</v>
       </c>
-      <c r="L31" s="16">
-        <f t="shared" si="20"/>
+      <c r="L32" s="16">
+        <f t="shared" si="41"/>
         <v>-7.9437131184748044E-2</v>
       </c>
-      <c r="M31" s="16">
-        <f t="shared" si="21"/>
+      <c r="M32" s="16">
+        <f t="shared" si="42"/>
         <v>4.4211287988422665E-2</v>
       </c>
-      <c r="N31" s="16">
-        <f t="shared" si="22"/>
+      <c r="N32" s="16">
+        <f t="shared" si="43"/>
         <v>0.18625482625482626</v>
       </c>
-      <c r="V31" s="16">
-        <f t="shared" si="23"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16">
+        <f t="shared" si="45"/>
         <v>8.5000577034045177E-2</v>
       </c>
+      <c r="W32" s="16">
+        <f t="shared" si="44"/>
+        <v>0.11553630100632573</v>
+      </c>
+      <c r="X32" s="16">
+        <f t="shared" si="44"/>
+        <v>7.0475983976731715E-2</v>
+      </c>
+      <c r="Y32" s="16">
+        <f t="shared" si="44"/>
+        <v>4.2990689180072872E-2</v>
+      </c>
+      <c r="Z32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.3152456972674216E-2</v>
+      </c>
+      <c r="AA32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.093243779268473E-2</v>
+      </c>
+      <c r="AB32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.1085352744955275E-2</v>
+      </c>
+      <c r="AC32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.1263157594547453E-2</v>
+      </c>
+      <c r="AD32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.1469837356540742E-2</v>
+      </c>
+      <c r="AE32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.1709991668170678E-2</v>
+      </c>
+      <c r="AF32" s="16">
+        <f t="shared" si="44"/>
+        <v>3.1988921323216957E-2</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI32" s="16">
+        <v>0.08</v>
+      </c>
     </row>
-    <row r="32" spans="2:22">
-      <c r="B32" s="1" t="s">
+    <row r="33" spans="2:35">
+      <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="16">
-        <f t="shared" ref="E32:K32" si="24">E10/E8</f>
+      <c r="E33" s="16">
+        <f t="shared" ref="E33:K33" si="46">E10/E8</f>
         <v>0.20635775862068967</v>
       </c>
-      <c r="F32" s="16">
-        <f t="shared" si="24"/>
+      <c r="F33" s="16">
+        <f t="shared" si="46"/>
         <v>0.19007184846505551</v>
       </c>
-      <c r="G32" s="16">
-        <f t="shared" si="24"/>
+      <c r="G33" s="16">
+        <f t="shared" si="46"/>
         <v>0.22248243559718969</v>
       </c>
-      <c r="H32" s="16">
-        <f t="shared" si="24"/>
+      <c r="H33" s="16">
+        <f t="shared" si="46"/>
         <v>0.20608261461643212</v>
       </c>
-      <c r="I32" s="16">
-        <f t="shared" si="24"/>
+      <c r="I33" s="16">
+        <f t="shared" si="46"/>
         <v>0.20067534973468404</v>
       </c>
-      <c r="J32" s="16">
-        <f t="shared" si="24"/>
+      <c r="J33" s="16">
+        <f t="shared" si="46"/>
         <v>0.1998069498069498</v>
       </c>
-      <c r="K32" s="16">
-        <f t="shared" si="24"/>
+      <c r="K33" s="16">
+        <f t="shared" si="46"/>
         <v>0.18462549277266754</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L33" s="16">
         <f>L10/L8</f>
         <v>0.20266272189349113</v>
       </c>
-      <c r="M32" s="16">
-        <f t="shared" ref="M32:N32" si="25">M10/M8</f>
+      <c r="M33" s="16">
+        <f t="shared" ref="M33:N33" si="47">M10/M8</f>
         <v>0.2</v>
       </c>
-      <c r="N32" s="16">
-        <f t="shared" si="25"/>
+      <c r="N33" s="16">
+        <f t="shared" si="47"/>
         <v>0.2</v>
       </c>
-      <c r="V32" s="16">
-        <f t="shared" ref="V32" si="26">V10/V8</f>
+      <c r="U33" s="16">
+        <f t="shared" ref="U33" si="48">U10/U8</f>
+        <v>0.20496249278707443</v>
+      </c>
+      <c r="V33" s="16">
+        <f t="shared" ref="V33:AF33" si="49">V10/V8</f>
         <v>0.1980854180117492</v>
       </c>
+      <c r="W33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="X33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="Z33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="AA33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="AB33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="AC33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AD33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="AE33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AF33" s="16">
+        <f t="shared" si="49"/>
+        <v>0.2</v>
+      </c>
+      <c r="AH33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI33" s="6">
+        <f>NPV(AI32,V23:EI23)</f>
+        <v>10070.758342822548</v>
+      </c>
     </row>
-    <row r="33" spans="2:22">
-      <c r="B33" s="1" t="s">
+    <row r="34" spans="2:35">
+      <c r="B34" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16">
-        <f t="shared" ref="I33:L34" si="27">I11/E11-1</f>
-        <v>0.13592233009708732</v>
-      </c>
-      <c r="J33" s="16">
-        <f t="shared" si="27"/>
-        <v>-1.4598540145985384E-2</v>
-      </c>
-      <c r="K33" s="16">
-        <f t="shared" si="27"/>
-        <v>-0.1009174311926605</v>
-      </c>
-      <c r="L33" s="16">
-        <f t="shared" si="27"/>
-        <v>2.564102564102555E-2</v>
-      </c>
-      <c r="M33" s="16">
-        <f t="shared" ref="M33:N33" si="28">M11/I11-1</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="N33" s="16">
-        <f t="shared" si="28"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="V33" s="16" t="e">
-        <f t="shared" ref="V33:V34" si="29">V11/R11-1</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22">
-      <c r="B34" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E34" s="16"/>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="I34:L35" si="50">I11/E11-1</f>
+        <v>0.13592233009708732</v>
+      </c>
+      <c r="J34" s="16">
+        <f t="shared" si="50"/>
+        <v>-1.4598540145985384E-2</v>
+      </c>
+      <c r="K34" s="16">
+        <f t="shared" si="50"/>
+        <v>-0.1009174311926605</v>
+      </c>
+      <c r="L34" s="16">
+        <f t="shared" si="50"/>
+        <v>2.564102564102555E-2</v>
+      </c>
+      <c r="M34" s="16">
+        <f t="shared" ref="M34:N34" si="51">M11/I11-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="N34" s="16">
+        <f t="shared" si="51"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16">
+        <f>V11/U11-1</f>
+        <v>-9.2050209205019051E-4</v>
+      </c>
+      <c r="W34" s="16">
+        <f t="shared" ref="W34:AF34" si="52">W11/V11-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="X34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="Y34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="Z34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AA34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AB34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AC34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AD34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AE34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF34" s="16">
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI34" s="6">
+        <f>Main!D8</f>
+        <v>-4448</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35">
+      <c r="B35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16">
+        <f t="shared" si="50"/>
         <v>9.8765432098765427E-2</v>
       </c>
-      <c r="J34" s="16">
-        <f t="shared" si="27"/>
+      <c r="J35" s="16">
+        <f t="shared" si="50"/>
         <v>-0.23417721518987344</v>
       </c>
-      <c r="K34" s="16">
-        <f t="shared" si="27"/>
+      <c r="K35" s="16">
+        <f t="shared" si="50"/>
         <v>-1.103448275862069</v>
       </c>
-      <c r="L34" s="16">
-        <f t="shared" si="27"/>
+      <c r="L35" s="16">
+        <f t="shared" si="50"/>
         <v>-0.32743362831858402</v>
       </c>
-      <c r="M34" s="16">
-        <f t="shared" ref="M34:N34" si="30">M12/I12-1</f>
+      <c r="M35" s="16">
+        <f t="shared" ref="M35:N35" si="53">M12/I12-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="N34" s="16">
-        <f t="shared" si="30"/>
+      <c r="N35" s="16">
+        <f t="shared" si="53"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="V34" s="16" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16">
+        <f>V12/U12-1</f>
+        <v>-0.17650568181818183</v>
+      </c>
+      <c r="W35" s="16">
+        <f t="shared" ref="W35:AF35" si="54">W12/V12-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="X35" s="16">
+        <f t="shared" si="54"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="Y35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="Z35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AA35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AB35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AC35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF35" s="16">
+        <f t="shared" si="54"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI35" s="6">
+        <f>AI33+AI34</f>
+        <v>5622.758342822548</v>
       </c>
     </row>
-    <row r="35" spans="2:22">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:35">
+      <c r="B36" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="16">
-        <f t="shared" ref="E35:K35" si="31">E17/E8</f>
+      <c r="E36" s="16">
+        <f t="shared" ref="E36:K36" si="55">E17/E8</f>
         <v>0.10614224137931035</v>
       </c>
-      <c r="F35" s="16">
-        <f t="shared" si="31"/>
+      <c r="F36" s="16">
+        <f t="shared" si="55"/>
         <v>6.8909209666884394E-2</v>
       </c>
-      <c r="G35" s="16">
-        <f t="shared" si="31"/>
+      <c r="G36" s="16">
+        <f t="shared" si="55"/>
         <v>0.11241217798594848</v>
       </c>
-      <c r="H35" s="16">
-        <f t="shared" si="31"/>
+      <c r="H36" s="16">
+        <f t="shared" si="55"/>
         <v>8.6699954607353608E-2</v>
       </c>
-      <c r="I35" s="16">
-        <f t="shared" si="31"/>
+      <c r="I36" s="16">
+        <f t="shared" si="55"/>
         <v>9.6960926193921854E-2</v>
       </c>
-      <c r="J35" s="16">
-        <f t="shared" si="31"/>
+      <c r="J36" s="16">
+        <f t="shared" si="55"/>
         <v>0.11003861003861004</v>
       </c>
-      <c r="K35" s="16">
-        <f t="shared" si="31"/>
+      <c r="K36" s="16">
+        <f t="shared" si="55"/>
         <v>0.11629434954007885</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L36" s="16">
         <f>L17/L8</f>
         <v>0.10108481262327416</v>
       </c>
-      <c r="M35" s="16">
-        <f t="shared" ref="M35:N35" si="32">M17/M8</f>
+      <c r="M36" s="16">
+        <f t="shared" ref="M36:N36" si="56">M17/M8</f>
         <v>9.6537546485575054E-2</v>
       </c>
-      <c r="N35" s="16">
-        <f t="shared" si="32"/>
+      <c r="N36" s="16">
+        <f t="shared" si="56"/>
         <v>0.12474124462960554</v>
       </c>
-      <c r="V35" s="16">
-        <f t="shared" ref="V35" si="33">V17/V8</f>
+      <c r="U36" s="16">
+        <f t="shared" ref="U36" si="57">U17/U8</f>
+        <v>0.10132717830351991</v>
+      </c>
+      <c r="V36" s="16">
+        <f t="shared" ref="V36:AF36" si="58">V17/V8</f>
         <v>0.11177712563806108</v>
       </c>
+      <c r="W36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.12058360860691923</v>
+      </c>
+      <c r="X36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.12436338657778545</v>
+      </c>
+      <c r="Y36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.12632240056642327</v>
+      </c>
+      <c r="Z36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.12754074977298496</v>
+      </c>
+      <c r="AA36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.12857894665916025</v>
+      </c>
+      <c r="AB36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.12960610562873573</v>
+      </c>
+      <c r="AC36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.13062380012178135</v>
+      </c>
+      <c r="AD36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.13163377610648491</v>
+      </c>
+      <c r="AE36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.13263797464031252</v>
+      </c>
+      <c r="AF36" s="16">
+        <f t="shared" si="58"/>
+        <v>0.13363855628424812</v>
+      </c>
+      <c r="AH36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI36" s="23">
+        <f>AI35/AF24</f>
+        <v>56.738227475505028</v>
+      </c>
     </row>
-    <row r="36" spans="2:22">
-      <c r="B36" s="1" t="s">
+    <row r="37" spans="2:35">
+      <c r="B37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="16">
-        <f t="shared" ref="E36:K36" si="34">E21/E20</f>
+      <c r="E37" s="16">
+        <f t="shared" ref="E37:K37" si="59">E21/E20</f>
         <v>5.128205128205128E-2</v>
       </c>
-      <c r="F36" s="16">
-        <f t="shared" si="34"/>
+      <c r="F37" s="16">
+        <f t="shared" si="59"/>
         <v>3.1531531531531529E-2</v>
       </c>
-      <c r="G36" s="16">
-        <f t="shared" si="34"/>
+      <c r="G37" s="16">
+        <f t="shared" si="59"/>
         <v>-0.1702127659574468</v>
       </c>
-      <c r="H36" s="16">
-        <f t="shared" si="34"/>
+      <c r="H37" s="16">
+        <f t="shared" si="59"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="I36" s="16">
-        <f t="shared" si="34"/>
+      <c r="I37" s="16">
+        <f t="shared" si="59"/>
         <v>-2.6315789473684209E-2</v>
       </c>
-      <c r="J36" s="16">
-        <f t="shared" si="34"/>
+      <c r="J37" s="16">
+        <f t="shared" si="59"/>
         <v>-1.4313725490196079</v>
       </c>
-      <c r="K36" s="16">
-        <f t="shared" si="34"/>
+      <c r="K37" s="16">
+        <f t="shared" si="59"/>
         <v>2.2222222222222223E-2</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L37" s="16">
         <f>L21/L20</f>
         <v>-0.11560693641618497</v>
       </c>
-      <c r="M36" s="16">
-        <f t="shared" ref="M36:N36" si="35">M21/M20</f>
+      <c r="M37" s="16">
+        <f t="shared" ref="M37:N37" si="60">M21/M20</f>
         <v>0</v>
       </c>
-      <c r="N36" s="16">
-        <f t="shared" si="35"/>
+      <c r="N37" s="16">
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="V36" s="16">
-        <f t="shared" ref="V36" si="36">V21/V20</f>
+      <c r="U37" s="16">
+        <f t="shared" ref="U37" si="61">U21/U20</f>
+        <v>-0.4453125</v>
+      </c>
+      <c r="V37" s="16">
+        <f t="shared" ref="V37:AF37" si="62">V21/V20</f>
         <v>-3.8188191407254914E-2</v>
       </c>
+      <c r="W37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="X37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="Y37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="Z37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AA37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AB37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AC37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AD37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AE37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AF37" s="16">
+        <f t="shared" si="62"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI37" s="23">
+        <f>Main!D3</f>
+        <v>195.91</v>
+      </c>
     </row>
-    <row r="37" spans="2:22">
-      <c r="B37" s="1" t="s">
+    <row r="38" spans="2:35">
+      <c r="B38" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="16">
-        <f t="shared" ref="E37:K37" si="37">E23/E8</f>
+      <c r="E38" s="16">
+        <f t="shared" ref="E38:K38" si="63">E23/E8</f>
         <v>-1.9935344827586209E-2</v>
       </c>
-      <c r="F37" s="16">
-        <f t="shared" si="37"/>
+      <c r="F38" s="16">
+        <f t="shared" si="63"/>
         <v>7.0215545395166556E-2</v>
       </c>
-      <c r="G37" s="16">
-        <f t="shared" si="37"/>
+      <c r="G38" s="16">
+        <f t="shared" si="63"/>
         <v>8.5870413739266196E-2</v>
       </c>
-      <c r="H37" s="16">
-        <f t="shared" si="37"/>
+      <c r="H38" s="16">
+        <f t="shared" si="63"/>
         <v>8.6246028143440769E-3</v>
       </c>
-      <c r="I37" s="16">
-        <f t="shared" si="37"/>
+      <c r="I38" s="16">
+        <f t="shared" si="63"/>
         <v>5.6439942112879886E-2</v>
       </c>
-      <c r="J37" s="16">
-        <f t="shared" si="37"/>
+      <c r="J38" s="16">
+        <f t="shared" si="63"/>
         <v>3.9897039897039896E-2</v>
       </c>
-      <c r="K37" s="16">
-        <f t="shared" si="37"/>
+      <c r="K38" s="16">
+        <f t="shared" si="63"/>
         <v>2.8909329829172142E-2</v>
       </c>
-      <c r="L37" s="16">
+      <c r="L38" s="16">
         <f>L23/L8</f>
         <v>8.7771203155818545E-2</v>
       </c>
-      <c r="M37" s="16">
-        <f t="shared" ref="M37:N37" si="38">M23/M8</f>
+      <c r="M38" s="16">
+        <f t="shared" ref="M38:N38" si="64">M23/M8</f>
         <v>5.5140553900168636E-2</v>
       </c>
-      <c r="N37" s="16">
-        <f t="shared" si="38"/>
+      <c r="N38" s="16">
+        <f t="shared" si="64"/>
         <v>4.3444863950006518E-2</v>
       </c>
-      <c r="V37" s="16">
-        <f t="shared" ref="V37" si="39">V23/V8</f>
+      <c r="U38" s="16">
+        <f t="shared" ref="U38" si="65">U23/U8</f>
+        <v>4.2700519330640507E-2</v>
+      </c>
+      <c r="V38" s="16">
+        <f t="shared" ref="V38:AF38" si="66">V23/V8</f>
         <v>5.334621066996547E-2</v>
       </c>
+      <c r="W38" s="16">
+        <f t="shared" si="66"/>
+        <v>5.4831004234655541E-2</v>
+      </c>
+      <c r="X38" s="16">
+        <f t="shared" si="66"/>
+        <v>5.9846088852221688E-2</v>
+      </c>
+      <c r="Y38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.2082482348569251E-2</v>
+      </c>
+      <c r="Z38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.3256277256410059E-2</v>
+      </c>
+      <c r="AA38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.417958404572148E-2</v>
+      </c>
+      <c r="AB38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.5100156022380173E-2</v>
+      </c>
+      <c r="AC38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.6020394899883289E-2</v>
+      </c>
+      <c r="AD38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.6943013189534592E-2</v>
+      </c>
+      <c r="AE38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.7871076488419418E-2</v>
+      </c>
+      <c r="AF38" s="16">
+        <f t="shared" si="66"/>
+        <v>6.8808049808672042E-2</v>
+      </c>
+      <c r="AH38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI38" s="22">
+        <f>AI36/AI37-1</f>
+        <v>-0.710386261673702</v>
+      </c>
     </row>
-    <row r="40" spans="2:22" s="20" customFormat="1">
-      <c r="B40" s="20" t="s">
+    <row r="39" spans="2:35">
+      <c r="AH39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI39" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="2:35" s="20" customFormat="1">
+      <c r="B41" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="L40" s="20">
+      <c r="L41" s="20">
         <f>12864</f>
         <v>12864</v>
       </c>
     </row>
-    <row r="42" spans="2:22">
-      <c r="B42" s="1" t="s">
+    <row r="43" spans="2:35">
+      <c r="B43" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L42" s="21">
-        <f>Main!D9/Model!L40</f>
-        <v>1.845136271766169</v>
+      <c r="L43" s="21">
+        <f>Main!D9/Model!L41</f>
+        <v>1.8549969682835818</v>
       </c>
     </row>
-    <row r="43" spans="2:22">
-      <c r="B43" s="1" t="s">
+    <row r="44" spans="2:35">
+      <c r="B44" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L43" s="16">
-        <f>L40/Main!D9-1</f>
-        <v>-0.45803460952897668</v>
+      <c r="L44" s="16">
+        <f>L41/Main!D9-1</f>
+        <v>-0.46091556099668762</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/BBD.A.xlsx
+++ b/Financial Analysis/BBD.A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A820B79-EDCF-434F-B656-35A87FB8A767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F30132-8B08-4A88-A40C-462C5902DCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{346DD61D-C15D-48A0-ADE2-5B9C576CD682}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
   <si>
     <t>BBD</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>USD/CAD</t>
+  </si>
+  <si>
+    <t>CAD$</t>
   </si>
 </sst>
 </file>
@@ -1945,7 +1951,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1984,6 +1990,7 @@
     <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="53" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="649">
     <cellStyle name="_Exec Summary FINAL" xfId="3" xr:uid="{19585BA9-F398-4EDE-A7B7-F00CFAAF7DC7}"/>
@@ -2653,15 +2660,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2677,8 +2684,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7726680" y="7620"/>
-          <a:ext cx="0" cy="6134100"/>
+          <a:off x="8435340" y="7620"/>
+          <a:ext cx="0" cy="9974580"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2711,8 +2718,8 @@
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2728,7 +2735,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13319760" y="7620"/>
-          <a:ext cx="0" cy="7399020"/>
+          <a:ext cx="0" cy="9974580"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3051,7 +3058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7E10EC-689A-4374-B136-FA4060CA2AA7}">
-  <dimension ref="B2:G9"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="1"/>
@@ -3079,17 +3086,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>195.91</v>
+        <f>D12*D13</f>
+        <v>162.50479999999999</v>
       </c>
       <c r="E3" s="4">
-        <v>45956</v>
+        <v>45988</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45956</v>
+        <v>45988</v>
       </c>
       <c r="G3" s="4">
-        <v>45967</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -3097,11 +3105,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>86.8+12.3</f>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -3110,7 +3118,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>19414.680999999997</v>
+        <v>16120.47616</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -3118,10 +3126,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <v>811</v>
+        <f>1182</f>
+        <v>1182</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -3129,11 +3138,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>184+5075</f>
-        <v>5259</v>
+        <f>250+5253</f>
+        <v>5503</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -3142,7 +3151,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-4448</v>
+        <v>-4321</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -3151,7 +3160,23 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>23862.680999999997</v>
+        <v>20441.476159999998</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="C12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="1">
+        <v>228.88</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="C13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -3286,11 +3311,11 @@
       <c r="L3" s="18">
         <v>16100</v>
       </c>
-      <c r="M3" s="13">
-        <v>16100</v>
+      <c r="M3" s="18">
+        <v>16600</v>
       </c>
       <c r="N3" s="13">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="T3" s="18">
         <v>14200</v>
@@ -3298,8 +3323,8 @@
       <c r="U3" s="6">
         <v>14400</v>
       </c>
-      <c r="V3" s="13">
-        <v>16100</v>
+      <c r="V3" s="18">
+        <v>16600</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -3347,8 +3372,7 @@
         <v>1430</v>
       </c>
       <c r="M5" s="18">
-        <f>I5*1.05</f>
-        <v>1601.25</v>
+        <v>1711</v>
       </c>
       <c r="N5" s="18">
         <f>J5*1.2</f>
@@ -3360,47 +3384,47 @@
       </c>
       <c r="V5" s="18">
         <f>SUM(K5:N5)</f>
-        <v>7143.25</v>
+        <v>7253</v>
       </c>
       <c r="W5" s="6">
-        <f>V5*1.12</f>
-        <v>8000.4400000000005</v>
+        <f>V5*1.14</f>
+        <v>8268.42</v>
       </c>
       <c r="X5" s="6">
         <f>W5*1.07</f>
-        <v>8560.470800000001</v>
+        <v>8847.2093999999997</v>
       </c>
       <c r="Y5" s="6">
         <f>X5*1.04</f>
-        <v>8902.8896320000022</v>
+        <v>9201.0977760000005</v>
       </c>
       <c r="Z5" s="6">
         <f>Y5*1.03</f>
-        <v>9169.9763209600023</v>
+        <v>9477.1307092800016</v>
       </c>
       <c r="AA5" s="6">
         <f t="shared" ref="AA5:AF6" si="0">Z5*1.03</f>
-        <v>9445.0756105888031</v>
+        <v>9761.4446305584024</v>
       </c>
       <c r="AB5" s="6">
         <f t="shared" si="0"/>
-        <v>9728.4278789064683</v>
+        <v>10054.287969475155</v>
       </c>
       <c r="AC5" s="6">
         <f t="shared" si="0"/>
-        <v>10020.280715273662</v>
+        <v>10355.91660855941</v>
       </c>
       <c r="AD5" s="6">
         <f t="shared" si="0"/>
-        <v>10320.889136731872</v>
+        <v>10666.594106816192</v>
       </c>
       <c r="AE5" s="6">
         <f t="shared" si="0"/>
-        <v>10630.515810833829</v>
+        <v>10986.591930020679</v>
       </c>
       <c r="AF5" s="6">
         <f t="shared" si="0"/>
-        <v>10949.431285158844</v>
+        <v>11316.1896879213</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -3434,8 +3458,7 @@
         <v>590</v>
       </c>
       <c r="M6" s="18">
-        <f t="shared" ref="M6" si="1">I6*1.05</f>
-        <v>554.4</v>
+        <v>590</v>
       </c>
       <c r="N6" s="18">
         <f>J6*1.12</f>
@@ -3446,48 +3469,48 @@
         <v>2036</v>
       </c>
       <c r="V6" s="18">
-        <f t="shared" ref="V6:V7" si="2">SUM(K6:N6)</f>
-        <v>2226.2800000000002</v>
+        <f t="shared" ref="V6:V7" si="1">SUM(K6:N6)</f>
+        <v>2261.88</v>
       </c>
       <c r="W6" s="6">
         <f>V6*1.1</f>
-        <v>2448.9080000000004</v>
+        <v>2488.0680000000002</v>
       </c>
       <c r="X6" s="6">
         <f>W6*1.07</f>
-        <v>2620.3315600000005</v>
+        <v>2662.2327600000003</v>
       </c>
       <c r="Y6" s="6">
         <f>X6*1.05</f>
-        <v>2751.3481380000007</v>
+        <v>2795.3443980000006</v>
       </c>
       <c r="Z6" s="6">
         <f>Y6*1.04</f>
-        <v>2861.4020635200009</v>
+        <v>2907.1581739200005</v>
       </c>
       <c r="AA6" s="6">
         <f>Z6*1.03</f>
-        <v>2947.2441254256009</v>
+        <v>2994.3729191376005</v>
       </c>
       <c r="AB6" s="6">
         <f t="shared" si="0"/>
-        <v>3035.6614491883693</v>
+        <v>3084.2041067117289</v>
       </c>
       <c r="AC6" s="6">
         <f t="shared" si="0"/>
-        <v>3126.7312926640202</v>
+        <v>3176.7302299130806</v>
       </c>
       <c r="AD6" s="6">
         <f t="shared" si="0"/>
-        <v>3220.5332314439411</v>
+        <v>3272.0321368104733</v>
       </c>
       <c r="AE6" s="6">
         <f t="shared" si="0"/>
-        <v>3317.1492283872594</v>
+        <v>3370.1931009147875</v>
       </c>
       <c r="AF6" s="6">
         <f t="shared" si="0"/>
-        <v>3416.6637052388774</v>
+        <v>3471.2988939422312</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -3521,7 +3544,7 @@
         <v>8</v>
       </c>
       <c r="M7" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N7" s="12">
         <v>10</v>
@@ -3531,48 +3554,48 @@
         <v>49</v>
       </c>
       <c r="V7" s="18">
-        <f t="shared" si="2"/>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
       <c r="W7" s="6">
         <f>V7*1.2</f>
-        <v>38.4</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="X7" s="6">
-        <f t="shared" ref="X7:AF7" si="3">W7*1.2</f>
-        <v>46.08</v>
+        <f t="shared" ref="X7:AF7" si="2">W7*1.2</f>
+        <v>41.76</v>
       </c>
       <c r="Y7" s="6">
-        <f t="shared" si="3"/>
-        <v>55.295999999999999</v>
+        <f t="shared" si="2"/>
+        <v>50.111999999999995</v>
       </c>
       <c r="Z7" s="6">
-        <f t="shared" si="3"/>
-        <v>66.355199999999996</v>
+        <f t="shared" si="2"/>
+        <v>60.134399999999992</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" si="3"/>
-        <v>79.626239999999996</v>
+        <f t="shared" si="2"/>
+        <v>72.161279999999991</v>
       </c>
       <c r="AB7" s="6">
-        <f t="shared" si="3"/>
-        <v>95.551487999999992</v>
+        <f t="shared" si="2"/>
+        <v>86.593535999999986</v>
       </c>
       <c r="AC7" s="6">
-        <f t="shared" si="3"/>
-        <v>114.66178559999999</v>
+        <f t="shared" si="2"/>
+        <v>103.91224319999998</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="3"/>
-        <v>137.59414271999998</v>
+        <f t="shared" si="2"/>
+        <v>124.69469183999996</v>
       </c>
       <c r="AE7" s="6">
-        <f t="shared" si="3"/>
-        <v>165.11297126399998</v>
+        <f t="shared" si="2"/>
+        <v>149.63363020799994</v>
       </c>
       <c r="AF7" s="6">
-        <f t="shared" si="3"/>
-        <v>198.13556551679997</v>
+        <f t="shared" si="2"/>
+        <v>179.56035624959992</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="2" customFormat="1">
@@ -3580,43 +3603,43 @@
         <v>42</v>
       </c>
       <c r="E8" s="15">
-        <f t="shared" ref="E8:N8" si="4">SUM(E5:E7)</f>
+        <f t="shared" ref="E8:N8" si="3">SUM(E5:E7)</f>
         <v>1856</v>
       </c>
       <c r="F8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3062</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1281</v>
       </c>
       <c r="H8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2203</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2073</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3108</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1522</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2028</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" si="4"/>
-        <v>2164.65</v>
+        <f>SUM(M5:M7)</f>
+        <v>2307</v>
       </c>
       <c r="N8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3686.88</v>
       </c>
       <c r="U8" s="15">
@@ -3625,47 +3648,47 @@
       </c>
       <c r="V8" s="15">
         <f>SUM(V5:V7)</f>
-        <v>9401.5300000000007</v>
+        <v>9543.880000000001</v>
       </c>
       <c r="W8" s="15">
-        <f t="shared" ref="W8:AF8" si="5">SUM(W5:W7)</f>
-        <v>10487.748000000001</v>
+        <f t="shared" ref="W8:AF8" si="4">SUM(W5:W7)</f>
+        <v>10791.288</v>
       </c>
       <c r="X8" s="15">
-        <f t="shared" si="5"/>
-        <v>11226.882360000001</v>
+        <f t="shared" si="4"/>
+        <v>11551.202160000001</v>
       </c>
       <c r="Y8" s="15">
-        <f t="shared" si="5"/>
-        <v>11709.533770000004</v>
+        <f t="shared" si="4"/>
+        <v>12046.554174000001</v>
       </c>
       <c r="Z8" s="15">
-        <f t="shared" si="5"/>
-        <v>12097.733584480004</v>
+        <f t="shared" si="4"/>
+        <v>12444.423283200003</v>
       </c>
       <c r="AA8" s="15">
-        <f t="shared" si="5"/>
-        <v>12471.945976014404</v>
+        <f t="shared" si="4"/>
+        <v>12827.978829696003</v>
       </c>
       <c r="AB8" s="15">
-        <f t="shared" si="5"/>
-        <v>12859.640816094836</v>
+        <f t="shared" si="4"/>
+        <v>13225.085612186886</v>
       </c>
       <c r="AC8" s="15">
-        <f t="shared" si="5"/>
-        <v>13261.673793537682</v>
+        <f t="shared" si="4"/>
+        <v>13636.559081672491</v>
       </c>
       <c r="AD8" s="15">
-        <f t="shared" si="5"/>
-        <v>13679.016510895812</v>
+        <f t="shared" si="4"/>
+        <v>14063.320935466667</v>
       </c>
       <c r="AE8" s="15">
-        <f t="shared" si="5"/>
-        <v>14112.778010485088</v>
+        <f t="shared" si="4"/>
+        <v>14506.418661143465</v>
       </c>
       <c r="AF8" s="15">
-        <f t="shared" si="5"/>
-        <v>14564.230555914522</v>
+        <f t="shared" si="4"/>
+        <v>14967.04893811313</v>
       </c>
     </row>
     <row r="9" spans="1:32">
@@ -3697,8 +3720,7 @@
         <v>1617</v>
       </c>
       <c r="M9" s="6">
-        <f>M8-M10</f>
-        <v>1731.72</v>
+        <v>1843</v>
       </c>
       <c r="N9" s="6">
         <f>N8-N10</f>
@@ -3710,47 +3732,47 @@
       </c>
       <c r="V9" s="18">
         <f>SUM(K9:N9)</f>
-        <v>7539.2240000000002</v>
+        <v>7650.5039999999999</v>
       </c>
       <c r="W9" s="6">
         <f>W8-W10</f>
-        <v>8390.1984000000011</v>
+        <v>8525.1175199999998</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" ref="X9:AF9" si="6">X8-X10</f>
-        <v>8981.5058880000015</v>
+        <f t="shared" ref="X9:AF9" si="5">X8-X10</f>
+        <v>9125.4497064000007</v>
       </c>
       <c r="Y9" s="6">
-        <f t="shared" si="6"/>
-        <v>9367.6270160000022</v>
+        <f t="shared" si="5"/>
+        <v>9516.7777974600012</v>
       </c>
       <c r="Z9" s="6">
-        <f t="shared" si="6"/>
-        <v>9678.1868675840033</v>
+        <f t="shared" si="5"/>
+        <v>9831.0943937280026</v>
       </c>
       <c r="AA9" s="6">
-        <f t="shared" si="6"/>
-        <v>9977.5567808115229</v>
+        <f t="shared" si="5"/>
+        <v>10134.103275459842</v>
       </c>
       <c r="AB9" s="6">
-        <f t="shared" si="6"/>
-        <v>10287.712652875869</v>
+        <f t="shared" si="5"/>
+        <v>10447.817633627639</v>
       </c>
       <c r="AC9" s="6">
-        <f t="shared" si="6"/>
-        <v>10609.339034830145</v>
+        <f t="shared" si="5"/>
+        <v>10772.881674521268</v>
       </c>
       <c r="AD9" s="6">
-        <f t="shared" si="6"/>
-        <v>10943.21320871665</v>
+        <f t="shared" si="5"/>
+        <v>11110.023539018668</v>
       </c>
       <c r="AE9" s="6">
-        <f t="shared" si="6"/>
-        <v>11290.22240838807</v>
+        <f t="shared" si="5"/>
+        <v>11460.070742303338</v>
       </c>
       <c r="AF9" s="6">
-        <f t="shared" si="6"/>
-        <v>11651.384444731619</v>
+        <f t="shared" si="5"/>
+        <v>11823.968661109373</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="2" customFormat="1">
@@ -3758,40 +3780,40 @@
         <v>38</v>
       </c>
       <c r="E10" s="15">
-        <f t="shared" ref="E10:L10" si="7">E8-E9</f>
+        <f t="shared" ref="E10:M10" si="6">E8-E9</f>
         <v>383</v>
       </c>
       <c r="F10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>582</v>
       </c>
       <c r="G10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>285</v>
       </c>
       <c r="H10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>454</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>416</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>621</v>
       </c>
       <c r="K10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>281</v>
       </c>
       <c r="L10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>411</v>
       </c>
-      <c r="M10" s="17">
-        <f>M8*0.2</f>
-        <v>432.93000000000006</v>
+      <c r="M10" s="15">
+        <f t="shared" si="6"/>
+        <v>464</v>
       </c>
       <c r="N10" s="17">
         <f>N8*0.2</f>
@@ -3803,47 +3825,47 @@
       </c>
       <c r="V10" s="15">
         <f>V8-V9</f>
-        <v>1862.3060000000005</v>
+        <v>1893.3760000000011</v>
       </c>
       <c r="W10" s="17">
-        <f>W8*0.2</f>
-        <v>2097.5496000000003</v>
+        <f>W8*0.21</f>
+        <v>2266.1704800000002</v>
       </c>
       <c r="X10" s="17">
-        <f t="shared" ref="X10:AF10" si="8">X8*0.2</f>
-        <v>2245.3764720000004</v>
+        <f t="shared" ref="X10:AF10" si="7">X8*0.21</f>
+        <v>2425.7524536000001</v>
       </c>
       <c r="Y10" s="17">
-        <f t="shared" si="8"/>
-        <v>2341.906754000001</v>
+        <f t="shared" si="7"/>
+        <v>2529.77637654</v>
       </c>
       <c r="Z10" s="17">
-        <f t="shared" si="8"/>
-        <v>2419.5467168960008</v>
+        <f t="shared" si="7"/>
+        <v>2613.3288894720008</v>
       </c>
       <c r="AA10" s="17">
-        <f t="shared" si="8"/>
-        <v>2494.3891952028807</v>
+        <f t="shared" si="7"/>
+        <v>2693.8755542361605</v>
       </c>
       <c r="AB10" s="17">
-        <f t="shared" si="8"/>
-        <v>2571.9281632189673</v>
+        <f t="shared" si="7"/>
+        <v>2777.2679785592459</v>
       </c>
       <c r="AC10" s="17">
-        <f t="shared" si="8"/>
-        <v>2652.3347587075368</v>
+        <f t="shared" si="7"/>
+        <v>2863.6774071512227</v>
       </c>
       <c r="AD10" s="17">
-        <f t="shared" si="8"/>
-        <v>2735.8033021791625</v>
+        <f t="shared" si="7"/>
+        <v>2953.2973964479997</v>
       </c>
       <c r="AE10" s="17">
-        <f t="shared" si="8"/>
-        <v>2822.555602097018</v>
+        <f t="shared" si="7"/>
+        <v>3046.3479188401275</v>
       </c>
       <c r="AF10" s="17">
-        <f t="shared" si="8"/>
-        <v>2912.8461111829047</v>
+        <f t="shared" si="7"/>
+        <v>3143.0802770037571</v>
       </c>
     </row>
     <row r="11" spans="1:32">
@@ -3875,60 +3897,59 @@
         <v>120</v>
       </c>
       <c r="M11" s="6">
-        <f>I11*1.03</f>
-        <v>120.51</v>
+        <v>124</v>
       </c>
       <c r="N11" s="6">
         <f>J11*1.03</f>
         <v>139.05000000000001</v>
       </c>
       <c r="U11" s="18">
-        <f t="shared" ref="U11:U15" si="9">SUM(G11:J11)</f>
+        <f t="shared" ref="U11:U15" si="8">SUM(G11:J11)</f>
         <v>478</v>
       </c>
       <c r="V11" s="18">
-        <f t="shared" ref="V11:V15" si="10">SUM(K11:N11)</f>
-        <v>477.56</v>
+        <f t="shared" ref="V11:V15" si="9">SUM(K11:N11)</f>
+        <v>481.05</v>
       </c>
       <c r="W11" s="6">
         <f>V11*1.01</f>
-        <v>482.3356</v>
+        <v>485.8605</v>
       </c>
       <c r="X11" s="6">
-        <f t="shared" ref="X11:Y11" si="11">W11*1.01</f>
-        <v>487.15895599999999</v>
+        <f t="shared" ref="X11:Y11" si="10">W11*1.01</f>
+        <v>490.71910500000001</v>
       </c>
       <c r="Y11" s="6">
+        <f t="shared" si="10"/>
+        <v>495.62629605000001</v>
+      </c>
+      <c r="Z11" s="6">
+        <f t="shared" ref="Z11:AF11" si="11">Y11*1.01</f>
+        <v>500.58255901050001</v>
+      </c>
+      <c r="AA11" s="6">
         <f t="shared" si="11"/>
-        <v>492.03054556000001</v>
-      </c>
-      <c r="Z11" s="6">
-        <f t="shared" ref="Z11:AF11" si="12">Y11*1.01</f>
-        <v>496.95085101559999</v>
-      </c>
-      <c r="AA11" s="6">
-        <f t="shared" si="12"/>
-        <v>501.920359525756</v>
+        <v>505.58838460060502</v>
       </c>
       <c r="AB11" s="6">
-        <f t="shared" si="12"/>
-        <v>506.93956312101358</v>
+        <f t="shared" si="11"/>
+        <v>510.64426844661108</v>
       </c>
       <c r="AC11" s="6">
-        <f t="shared" si="12"/>
-        <v>512.00895875222375</v>
+        <f t="shared" si="11"/>
+        <v>515.7507111310772</v>
       </c>
       <c r="AD11" s="6">
-        <f t="shared" si="12"/>
-        <v>517.12904833974596</v>
+        <f t="shared" si="11"/>
+        <v>520.90821824238799</v>
       </c>
       <c r="AE11" s="6">
-        <f t="shared" si="12"/>
-        <v>522.30033882314342</v>
+        <f t="shared" si="11"/>
+        <v>526.1173004248119</v>
       </c>
       <c r="AF11" s="6">
-        <f t="shared" si="12"/>
-        <v>527.52334221137482</v>
+        <f t="shared" si="11"/>
+        <v>531.37847342906002</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -3960,60 +3981,59 @@
         <v>76</v>
       </c>
       <c r="M12" s="6">
-        <f>I12*1.05</f>
-        <v>93.45</v>
+        <v>103</v>
       </c>
       <c r="N12" s="6">
         <f>J12*1.02</f>
         <v>123.42</v>
       </c>
       <c r="U12" s="18">
+        <f t="shared" si="8"/>
+        <v>352</v>
+      </c>
+      <c r="V12" s="18">
         <f t="shared" si="9"/>
-        <v>352</v>
-      </c>
-      <c r="V12" s="18">
-        <f t="shared" si="10"/>
-        <v>289.87</v>
+        <v>299.42</v>
       </c>
       <c r="W12" s="6">
         <f>V12*1.05</f>
-        <v>304.36350000000004</v>
+        <v>314.39100000000002</v>
       </c>
       <c r="X12" s="6">
         <f>W12*1.03</f>
-        <v>313.49440500000003</v>
+        <v>323.82273000000004</v>
       </c>
       <c r="Y12" s="6">
         <f>X12*1.02</f>
-        <v>319.76429310000003</v>
+        <v>330.29918460000005</v>
       </c>
       <c r="Z12" s="6">
-        <f t="shared" ref="Z12:AF12" si="13">Y12*1.02</f>
-        <v>326.15957896200001</v>
+        <f t="shared" ref="Z12:AF12" si="12">Y12*1.02</f>
+        <v>336.90516829200004</v>
       </c>
       <c r="AA12" s="6">
-        <f t="shared" si="13"/>
-        <v>332.68277054124002</v>
+        <f t="shared" si="12"/>
+        <v>343.64327165784005</v>
       </c>
       <c r="AB12" s="6">
-        <f t="shared" si="13"/>
-        <v>339.33642595206481</v>
+        <f t="shared" si="12"/>
+        <v>350.51613709099684</v>
       </c>
       <c r="AC12" s="6">
-        <f t="shared" si="13"/>
-        <v>346.12315447110609</v>
+        <f t="shared" si="12"/>
+        <v>357.52645983281678</v>
       </c>
       <c r="AD12" s="6">
-        <f t="shared" si="13"/>
-        <v>353.04561756052823</v>
+        <f t="shared" si="12"/>
+        <v>364.67698902947313</v>
       </c>
       <c r="AE12" s="6">
-        <f t="shared" si="13"/>
-        <v>360.10652991173879</v>
+        <f t="shared" si="12"/>
+        <v>371.9705288100626</v>
       </c>
       <c r="AF12" s="6">
-        <f t="shared" si="13"/>
-        <v>367.30866050997355</v>
+        <f t="shared" si="12"/>
+        <v>379.40993938626389</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -4051,11 +4071,11 @@
         <v>15</v>
       </c>
       <c r="U13" s="18">
+        <f t="shared" si="8"/>
+        <v>63</v>
+      </c>
+      <c r="V13" s="18">
         <f t="shared" si="9"/>
-        <v>63</v>
-      </c>
-      <c r="V13" s="18">
-        <f t="shared" si="10"/>
         <v>44</v>
       </c>
       <c r="W13" s="6">
@@ -4063,39 +4083,39 @@
         <v>46.2</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" ref="X13:AF13" si="14">W13*1.05</f>
+        <f t="shared" ref="X13:AF13" si="13">W13*1.05</f>
         <v>48.510000000000005</v>
       </c>
       <c r="Y13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>50.935500000000005</v>
       </c>
       <c r="Z13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>53.482275000000008</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>56.156388750000012</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>58.964208187500013</v>
       </c>
       <c r="AC13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>61.912418596875014</v>
       </c>
       <c r="AD13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>65.008039526718761</v>
       </c>
       <c r="AE13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>68.258441503054698</v>
       </c>
       <c r="AF13" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>71.671363578207433</v>
       </c>
     </row>
@@ -4135,11 +4155,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="18">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="V14" s="18">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="V14" s="18">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="W14" s="6">
@@ -4208,11 +4228,11 @@
         <v>0</v>
       </c>
       <c r="U15" s="18">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="V15" s="18">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="V15" s="18">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="W15" s="6">
@@ -4251,43 +4271,43 @@
         <v>19</v>
       </c>
       <c r="E16" s="19">
-        <f t="shared" ref="E16:N16" si="15">SUM(E11:E15)</f>
+        <f t="shared" ref="E16:N16" si="14">SUM(E11:E15)</f>
         <v>186</v>
       </c>
       <c r="F16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>371</v>
       </c>
       <c r="G16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>141</v>
       </c>
       <c r="H16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>263</v>
       </c>
       <c r="I16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>215</v>
       </c>
       <c r="J16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>279</v>
       </c>
       <c r="K16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>104</v>
       </c>
       <c r="L16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>206</v>
       </c>
       <c r="M16" s="19">
-        <f t="shared" si="15"/>
-        <v>223.96</v>
+        <f t="shared" si="14"/>
+        <v>237</v>
       </c>
       <c r="N16" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>277.47000000000003</v>
       </c>
       <c r="U16" s="19">
@@ -4296,47 +4316,47 @@
       </c>
       <c r="V16" s="19">
         <f>SUM(V11:V15)</f>
-        <v>811.43000000000006</v>
+        <v>824.47</v>
       </c>
       <c r="W16" s="19">
         <f>SUM(W11:W15)</f>
-        <v>832.89910000000009</v>
+        <v>846.45150000000012</v>
       </c>
       <c r="X16" s="19">
-        <f t="shared" ref="X16:AF16" si="16">SUM(X11:X15)</f>
-        <v>849.16336100000001</v>
+        <f t="shared" ref="X16:AF16" si="15">SUM(X11:X15)</f>
+        <v>863.05183499999998</v>
       </c>
       <c r="Y16" s="19">
-        <f t="shared" si="16"/>
-        <v>862.73033866000014</v>
+        <f t="shared" si="15"/>
+        <v>876.8609806500001</v>
       </c>
       <c r="Z16" s="19">
-        <f t="shared" si="16"/>
-        <v>876.59270497759996</v>
+        <f t="shared" si="15"/>
+        <v>890.97000230250001</v>
       </c>
       <c r="AA16" s="19">
-        <f t="shared" si="16"/>
-        <v>890.75951881699609</v>
+        <f t="shared" si="15"/>
+        <v>905.38804500844515</v>
       </c>
       <c r="AB16" s="19">
-        <f t="shared" si="16"/>
-        <v>905.24019726057838</v>
+        <f t="shared" si="15"/>
+        <v>920.12461372510791</v>
       </c>
       <c r="AC16" s="19">
-        <f t="shared" si="16"/>
-        <v>920.04453182020484</v>
+        <f t="shared" si="15"/>
+        <v>935.18958956076892</v>
       </c>
       <c r="AD16" s="19">
-        <f t="shared" si="16"/>
-        <v>935.18270542699304</v>
+        <f t="shared" si="15"/>
+        <v>950.59324679857991</v>
       </c>
       <c r="AE16" s="19">
-        <f t="shared" si="16"/>
-        <v>950.66531023793686</v>
+        <f t="shared" si="15"/>
+        <v>966.34627073792922</v>
       </c>
       <c r="AF16" s="19">
-        <f t="shared" si="16"/>
-        <v>966.50336629955575</v>
+        <f t="shared" si="15"/>
+        <v>982.45977639353134</v>
       </c>
     </row>
     <row r="17" spans="2:139" s="2" customFormat="1">
@@ -4344,43 +4364,43 @@
         <v>20</v>
       </c>
       <c r="E17" s="15">
-        <f t="shared" ref="E17:N17" si="17">E10-E16</f>
+        <f t="shared" ref="E17:N17" si="16">E10-E16</f>
         <v>197</v>
       </c>
       <c r="F17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>211</v>
       </c>
       <c r="G17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>144</v>
       </c>
       <c r="H17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>191</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>201</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>342</v>
       </c>
       <c r="K17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>177</v>
       </c>
       <c r="L17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>205</v>
       </c>
       <c r="M17" s="15">
-        <f t="shared" si="17"/>
-        <v>208.97000000000006</v>
+        <f t="shared" si="16"/>
+        <v>227</v>
       </c>
       <c r="N17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>459.90600000000006</v>
       </c>
       <c r="U17" s="15">
@@ -4389,47 +4409,47 @@
       </c>
       <c r="V17" s="15">
         <f>V10-V16</f>
-        <v>1050.8760000000004</v>
+        <v>1068.9060000000011</v>
       </c>
       <c r="W17" s="15">
         <f>W10-W16</f>
-        <v>1264.6505000000002</v>
+        <v>1419.7189800000001</v>
       </c>
       <c r="X17" s="15">
-        <f t="shared" ref="X17:AF17" si="18">X10-X16</f>
-        <v>1396.2131110000005</v>
+        <f t="shared" ref="X17:AF17" si="17">X10-X16</f>
+        <v>1562.7006186000001</v>
       </c>
       <c r="Y17" s="15">
-        <f t="shared" si="18"/>
-        <v>1479.1764153400009</v>
+        <f t="shared" si="17"/>
+        <v>1652.9153958899999</v>
       </c>
       <c r="Z17" s="15">
-        <f t="shared" si="18"/>
-        <v>1542.9540119184007</v>
+        <f t="shared" si="17"/>
+        <v>1722.3588871695008</v>
       </c>
       <c r="AA17" s="15">
-        <f t="shared" si="18"/>
-        <v>1603.6296763858845</v>
+        <f t="shared" si="17"/>
+        <v>1788.4875092277152</v>
       </c>
       <c r="AB17" s="15">
-        <f t="shared" si="18"/>
-        <v>1666.6879659583888</v>
+        <f t="shared" si="17"/>
+        <v>1857.1433648341381</v>
       </c>
       <c r="AC17" s="15">
-        <f t="shared" si="18"/>
-        <v>1732.290226887332</v>
+        <f t="shared" si="17"/>
+        <v>1928.4878175904537</v>
       </c>
       <c r="AD17" s="15">
-        <f t="shared" si="18"/>
-        <v>1800.6205967521696</v>
+        <f t="shared" si="17"/>
+        <v>2002.7041496494198</v>
       </c>
       <c r="AE17" s="15">
-        <f t="shared" si="18"/>
-        <v>1871.8902918590811</v>
+        <f t="shared" si="17"/>
+        <v>2080.0016481021985</v>
       </c>
       <c r="AF17" s="15">
-        <f t="shared" si="18"/>
-        <v>1946.342744883349</v>
+        <f t="shared" si="17"/>
+        <v>2160.6205006102259</v>
       </c>
     </row>
     <row r="18" spans="2:139">
@@ -4461,60 +4481,59 @@
         <v>166</v>
       </c>
       <c r="M18" s="6">
-        <f>I18*1.03</f>
-        <v>142.14000000000001</v>
+        <v>159</v>
       </c>
       <c r="N18" s="6">
         <f>J18*1.03</f>
         <v>305.91000000000003</v>
       </c>
       <c r="U18" s="18">
-        <f t="shared" ref="U18:U19" si="19">SUM(G18:J18)</f>
+        <f t="shared" ref="U18:U19" si="18">SUM(G18:J18)</f>
         <v>842</v>
       </c>
       <c r="V18" s="18">
-        <f t="shared" ref="V18:V19" si="20">SUM(K18:N18)</f>
-        <v>758.05</v>
+        <f t="shared" ref="V18:V19" si="19">SUM(K18:N18)</f>
+        <v>774.91000000000008</v>
       </c>
       <c r="W18" s="6">
         <f>V18*1.03</f>
-        <v>780.79149999999993</v>
+        <v>798.15730000000008</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" ref="X18:AF18" si="21">W18*1.03</f>
-        <v>804.21524499999998</v>
+        <f t="shared" ref="X18:AF18" si="20">W18*1.03</f>
+        <v>822.10201900000015</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="21"/>
-        <v>828.34170234999999</v>
+        <f t="shared" si="20"/>
+        <v>846.76507957000013</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="21"/>
-        <v>853.1919534205</v>
+        <f t="shared" si="20"/>
+        <v>872.1680319571002</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="21"/>
-        <v>878.78771202311498</v>
+        <f t="shared" si="20"/>
+        <v>898.3330729158132</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="21"/>
-        <v>905.15134338380847</v>
+        <f t="shared" si="20"/>
+        <v>925.28306510328764</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="21"/>
-        <v>932.30588368532278</v>
+        <f t="shared" si="20"/>
+        <v>953.0415570563863</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" si="21"/>
-        <v>960.27506019588247</v>
+        <f t="shared" si="20"/>
+        <v>981.63280376807791</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="21"/>
-        <v>989.08331200175894</v>
+        <f t="shared" si="20"/>
+        <v>1011.0817878811202</v>
       </c>
       <c r="AF18" s="6">
-        <f t="shared" si="21"/>
-        <v>1018.7558113618118</v>
+        <f t="shared" si="20"/>
+        <v>1041.4142415175538</v>
       </c>
     </row>
     <row r="19" spans="2:139">
@@ -4546,60 +4565,59 @@
         <v>-134</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" ref="M19:N19" si="22">I19*1.03</f>
-        <v>-52.53</v>
+        <v>-6</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="M19:N19" si="21">J19*1.03</f>
         <v>-6.18</v>
       </c>
       <c r="U19" s="18">
+        <f t="shared" si="18"/>
+        <v>-220</v>
+      </c>
+      <c r="V19" s="18">
         <f t="shared" si="19"/>
-        <v>-220</v>
-      </c>
-      <c r="V19" s="18">
-        <f t="shared" si="20"/>
-        <v>-204.71</v>
+        <v>-158.18</v>
       </c>
       <c r="W19" s="6">
         <f>V19*1.03</f>
-        <v>-210.85130000000001</v>
+        <v>-162.92540000000002</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" ref="X19:AF19" si="23">W19*1.03</f>
-        <v>-217.176839</v>
+        <f t="shared" ref="X19:AF19" si="22">W19*1.03</f>
+        <v>-167.81316200000003</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="23"/>
-        <v>-223.69214417000001</v>
+        <f t="shared" si="22"/>
+        <v>-172.84755686000003</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="23"/>
-        <v>-230.40290849510001</v>
+        <f t="shared" si="22"/>
+        <v>-178.03298356580004</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="23"/>
-        <v>-237.31499574995303</v>
+        <f t="shared" si="22"/>
+        <v>-183.37397307277405</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="23"/>
-        <v>-244.43444562245162</v>
+        <f t="shared" si="22"/>
+        <v>-188.87519226495726</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="23"/>
-        <v>-251.76747899112519</v>
+        <f t="shared" si="22"/>
+        <v>-194.54144803290598</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="23"/>
-        <v>-259.32050336085894</v>
+        <f t="shared" si="22"/>
+        <v>-200.37769147389315</v>
       </c>
       <c r="AE19" s="6">
-        <f t="shared" si="23"/>
-        <v>-267.1001184616847</v>
+        <f t="shared" si="22"/>
+        <v>-206.38902221810994</v>
       </c>
       <c r="AF19" s="6">
-        <f t="shared" si="23"/>
-        <v>-275.11312201553523</v>
+        <f t="shared" si="22"/>
+        <v>-212.58069288465325</v>
       </c>
     </row>
     <row r="20" spans="2:139" s="2" customFormat="1">
@@ -4607,43 +4625,43 @@
         <v>23</v>
       </c>
       <c r="E20" s="15">
-        <f t="shared" ref="E20:N20" si="24">E17-E18-E19</f>
+        <f t="shared" ref="E20:N20" si="23">E17-E18-E19</f>
         <v>-39</v>
       </c>
       <c r="F20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>222</v>
       </c>
       <c r="G20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>94</v>
       </c>
       <c r="H20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-3</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>114</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>51</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>45</v>
       </c>
       <c r="L20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>173</v>
       </c>
       <c r="M20" s="15">
-        <f t="shared" si="24"/>
-        <v>119.36000000000004</v>
+        <f t="shared" si="23"/>
+        <v>74</v>
       </c>
       <c r="N20" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>160.17600000000004</v>
       </c>
       <c r="U20" s="15">
@@ -4652,47 +4670,47 @@
       </c>
       <c r="V20" s="15">
         <f>V17-V18-V19</f>
-        <v>497.53600000000051</v>
+        <v>452.17600000000101</v>
       </c>
       <c r="W20" s="15">
         <f>W17-W18-W19</f>
-        <v>694.7103000000003</v>
+        <v>784.48708000000011</v>
       </c>
       <c r="X20" s="15">
-        <f t="shared" ref="X20:AF20" si="25">X17-X18-X19</f>
-        <v>809.17470500000047</v>
+        <f t="shared" ref="X20:AF20" si="24">X17-X18-X19</f>
+        <v>908.41176159999998</v>
       </c>
       <c r="Y20" s="15">
-        <f t="shared" si="25"/>
-        <v>874.52685716000087</v>
+        <f t="shared" si="24"/>
+        <v>978.99787317999983</v>
       </c>
       <c r="Z20" s="15">
-        <f t="shared" si="25"/>
-        <v>920.16496699300069</v>
+        <f t="shared" si="24"/>
+        <v>1028.2238387782006</v>
       </c>
       <c r="AA20" s="15">
-        <f t="shared" si="25"/>
-        <v>962.15696011272257</v>
+        <f t="shared" si="24"/>
+        <v>1073.528409384676</v>
       </c>
       <c r="AB20" s="15">
-        <f t="shared" si="25"/>
-        <v>1005.9710681970319</v>
+        <f t="shared" si="24"/>
+        <v>1120.7354919958077</v>
       </c>
       <c r="AC20" s="15">
-        <f t="shared" si="25"/>
-        <v>1051.7518221931343</v>
+        <f t="shared" si="24"/>
+        <v>1169.9877085669734</v>
       </c>
       <c r="AD20" s="15">
-        <f t="shared" si="25"/>
-        <v>1099.666039917146</v>
+        <f t="shared" si="24"/>
+        <v>1221.4490373552351</v>
       </c>
       <c r="AE20" s="15">
-        <f t="shared" si="25"/>
-        <v>1149.9070983190068</v>
+        <f t="shared" si="24"/>
+        <v>1275.308882439188</v>
       </c>
       <c r="AF20" s="15">
-        <f t="shared" si="25"/>
-        <v>1202.7000555370726</v>
+        <f t="shared" si="24"/>
+        <v>1331.7869519773253</v>
       </c>
     </row>
     <row r="21" spans="2:139">
@@ -4724,58 +4742,58 @@
         <v>-20</v>
       </c>
       <c r="M21" s="6">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="N21" s="6">
         <v>0</v>
       </c>
       <c r="U21" s="18">
-        <f t="shared" ref="U21:U22" si="26">SUM(G21:J21)</f>
+        <f t="shared" ref="U21:U22" si="25">SUM(G21:J21)</f>
         <v>-114</v>
       </c>
       <c r="V21" s="18">
-        <f t="shared" ref="V21:V22" si="27">SUM(K21:N21)</f>
-        <v>-19</v>
+        <f t="shared" ref="V21:V22" si="26">SUM(K21:N21)</f>
+        <v>-30</v>
       </c>
       <c r="W21" s="6">
         <f>W20*0.15</f>
-        <v>104.20654500000005</v>
+        <v>117.67306200000002</v>
       </c>
       <c r="X21" s="6">
-        <f t="shared" ref="X21:AF21" si="28">X20*0.15</f>
-        <v>121.37620575000007</v>
+        <f t="shared" ref="X21:AF21" si="27">X20*0.15</f>
+        <v>136.26176423999999</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" si="28"/>
-        <v>131.17902857400011</v>
+        <f t="shared" si="27"/>
+        <v>146.84968097699996</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" si="28"/>
-        <v>138.02474504895011</v>
+        <f t="shared" si="27"/>
+        <v>154.23357581673008</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" si="28"/>
-        <v>144.32354401690839</v>
+        <f t="shared" si="27"/>
+        <v>161.0292614077014</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="28"/>
-        <v>150.89566022955478</v>
+        <f t="shared" si="27"/>
+        <v>168.11032379937114</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="28"/>
-        <v>157.76277332897016</v>
+        <f t="shared" si="27"/>
+        <v>175.49815628504601</v>
       </c>
       <c r="AD21" s="6">
-        <f t="shared" si="28"/>
-        <v>164.9499059875719</v>
+        <f t="shared" si="27"/>
+        <v>183.21735560328526</v>
       </c>
       <c r="AE21" s="6">
-        <f t="shared" si="28"/>
-        <v>172.486064747851</v>
+        <f t="shared" si="27"/>
+        <v>191.29633236587819</v>
       </c>
       <c r="AF21" s="6">
-        <f t="shared" si="28"/>
-        <v>180.40500833056089</v>
+        <f t="shared" si="27"/>
+        <v>199.76804279659879</v>
       </c>
     </row>
     <row r="22" spans="2:139">
@@ -4807,58 +4825,49 @@
         <v>15</v>
       </c>
       <c r="M22" s="6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="18">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="18">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="18">
-        <f t="shared" si="27"/>
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="W22" s="6">
         <f>V22*1.03</f>
-        <v>15.450000000000001</v>
+        <v>48.410000000000004</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" ref="X22:AF22" si="29">W22*1.03</f>
-        <v>15.913500000000001</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="29"/>
-        <v>16.390905</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="29"/>
-        <v>16.882632149999999</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="29"/>
-        <v>17.3891111145</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="29"/>
-        <v>17.910784447935001</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="29"/>
-        <v>18.448107981373052</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="29"/>
-        <v>19.001551220814246</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="6">
-        <f t="shared" si="29"/>
-        <v>19.571597757438674</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" si="29"/>
-        <v>20.158745690161833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:139" s="2" customFormat="1">
@@ -4866,43 +4875,43 @@
         <v>13</v>
       </c>
       <c r="E23" s="15">
-        <f t="shared" ref="E23:L23" si="30">E20-E21-E22</f>
+        <f t="shared" ref="E23:L23" si="28">E20-E21-E22</f>
         <v>-37</v>
       </c>
       <c r="F23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>215</v>
       </c>
       <c r="G23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>110</v>
       </c>
       <c r="H23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>19</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>117</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>124</v>
       </c>
       <c r="K23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>44</v>
       </c>
       <c r="L23" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>178</v>
       </c>
       <c r="M23" s="15">
-        <f t="shared" ref="M23:N23" si="31">M20-M21-M22</f>
-        <v>119.36000000000004</v>
+        <f t="shared" ref="M23:N23" si="29">M20-M21-M22</f>
+        <v>53</v>
       </c>
       <c r="N23" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>160.17600000000004</v>
       </c>
       <c r="U23" s="15">
@@ -4911,475 +4920,475 @@
       </c>
       <c r="V23" s="15">
         <f>V20-V21-V22</f>
-        <v>501.53600000000051</v>
+        <v>435.17600000000101</v>
       </c>
       <c r="W23" s="15">
         <f>W20-W21-W22</f>
-        <v>575.05375500000025</v>
+        <v>618.40401800000006</v>
       </c>
       <c r="X23" s="15">
-        <f t="shared" ref="X23:AF23" si="32">X20-X21-X22</f>
-        <v>671.88499925000042</v>
+        <f t="shared" ref="X23:AF23" si="30">X20-X21-X22</f>
+        <v>772.14999736000004</v>
       </c>
       <c r="Y23" s="15">
-        <f t="shared" si="32"/>
-        <v>726.95692358600081</v>
+        <f t="shared" si="30"/>
+        <v>832.14819220299989</v>
       </c>
       <c r="Z23" s="15">
-        <f t="shared" si="32"/>
-        <v>765.25758979405066</v>
+        <f t="shared" si="30"/>
+        <v>873.99026296147053</v>
       </c>
       <c r="AA23" s="15">
-        <f t="shared" si="32"/>
-        <v>800.44430498131419</v>
+        <f t="shared" si="30"/>
+        <v>912.49914797697465</v>
       </c>
       <c r="AB23" s="15">
-        <f t="shared" si="32"/>
-        <v>837.16462351954203</v>
+        <f t="shared" si="30"/>
+        <v>952.62516819643656</v>
       </c>
       <c r="AC23" s="15">
-        <f t="shared" si="32"/>
-        <v>875.54094088279112</v>
+        <f t="shared" si="30"/>
+        <v>994.48955228192744</v>
       </c>
       <c r="AD23" s="15">
-        <f t="shared" si="32"/>
-        <v>915.71458270875985</v>
+        <f t="shared" si="30"/>
+        <v>1038.2316817519497</v>
       </c>
       <c r="AE23" s="15">
-        <f t="shared" si="32"/>
-        <v>957.84943581371704</v>
+        <f t="shared" si="30"/>
+        <v>1084.0125500733097</v>
       </c>
       <c r="AF23" s="15">
-        <f t="shared" si="32"/>
-        <v>1002.1363015163498</v>
+        <f t="shared" si="30"/>
+        <v>1132.0189091807265</v>
       </c>
       <c r="AG23" s="2">
         <f>AF23*(1+$AI$31)</f>
-        <v>992.11493850118632</v>
+        <v>1120.6987200889191</v>
       </c>
       <c r="AH23" s="2">
-        <f t="shared" ref="AH23:CS23" si="33">AG23*(1+$AI$31)</f>
-        <v>982.19378911617446</v>
+        <f t="shared" ref="AH23:CS23" si="31">AG23*(1+$AI$31)</f>
+        <v>1109.4917328880299</v>
       </c>
       <c r="AI23" s="2">
-        <f t="shared" si="33"/>
-        <v>972.37185122501273</v>
+        <f t="shared" si="31"/>
+        <v>1098.3968155591497</v>
       </c>
       <c r="AJ23" s="2">
-        <f t="shared" si="33"/>
-        <v>962.64813271276262</v>
+        <f t="shared" si="31"/>
+        <v>1087.4128474035581</v>
       </c>
       <c r="AK23" s="2">
-        <f t="shared" si="33"/>
-        <v>953.02165138563498</v>
+        <f t="shared" si="31"/>
+        <v>1076.5387189295225</v>
       </c>
       <c r="AL23" s="2">
-        <f t="shared" si="33"/>
-        <v>943.49143487177867</v>
+        <f t="shared" si="31"/>
+        <v>1065.7733317402271</v>
       </c>
       <c r="AM23" s="2">
-        <f t="shared" si="33"/>
-        <v>934.05652052306084</v>
+        <f t="shared" si="31"/>
+        <v>1055.1155984228249</v>
       </c>
       <c r="AN23" s="2">
-        <f t="shared" si="33"/>
-        <v>924.71595531783021</v>
+        <f t="shared" si="31"/>
+        <v>1044.5644424385966</v>
       </c>
       <c r="AO23" s="2">
-        <f t="shared" si="33"/>
-        <v>915.46879576465187</v>
+        <f t="shared" si="31"/>
+        <v>1034.1187980142106</v>
       </c>
       <c r="AP23" s="2">
-        <f t="shared" si="33"/>
-        <v>906.31410780700537</v>
+        <f t="shared" si="31"/>
+        <v>1023.7776100340685</v>
       </c>
       <c r="AQ23" s="2">
-        <f t="shared" si="33"/>
-        <v>897.25096672893528</v>
+        <f t="shared" si="31"/>
+        <v>1013.5398339337278</v>
       </c>
       <c r="AR23" s="2">
-        <f t="shared" si="33"/>
-        <v>888.2784570616459</v>
+        <f t="shared" si="31"/>
+        <v>1003.4044355943905</v>
       </c>
       <c r="AS23" s="2">
-        <f t="shared" si="33"/>
-        <v>879.39567249102947</v>
+        <f t="shared" si="31"/>
+        <v>993.37039123844659</v>
       </c>
       <c r="AT23" s="2">
-        <f t="shared" si="33"/>
-        <v>870.60171576611913</v>
+        <f t="shared" si="31"/>
+        <v>983.43668732606216</v>
       </c>
       <c r="AU23" s="2">
-        <f t="shared" si="33"/>
-        <v>861.89569860845791</v>
+        <f t="shared" si="31"/>
+        <v>973.60232045280156</v>
       </c>
       <c r="AV23" s="2">
-        <f t="shared" si="33"/>
-        <v>853.27674162237327</v>
+        <f t="shared" si="31"/>
+        <v>963.86629724827355</v>
       </c>
       <c r="AW23" s="2">
-        <f t="shared" si="33"/>
-        <v>844.74397420614957</v>
+        <f t="shared" si="31"/>
+        <v>954.22763427579082</v>
       </c>
       <c r="AX23" s="2">
-        <f t="shared" si="33"/>
-        <v>836.29653446408804</v>
+        <f t="shared" si="31"/>
+        <v>944.68535793303295</v>
       </c>
       <c r="AY23" s="2">
-        <f t="shared" si="33"/>
-        <v>827.93356911944716</v>
+        <f t="shared" si="31"/>
+        <v>935.23850435370264</v>
       </c>
       <c r="AZ23" s="2">
-        <f t="shared" si="33"/>
-        <v>819.65423342825272</v>
+        <f t="shared" si="31"/>
+        <v>925.88611931016555</v>
       </c>
       <c r="BA23" s="2">
-        <f t="shared" si="33"/>
-        <v>811.4576910939702</v>
+        <f t="shared" si="31"/>
+        <v>916.62725811706389</v>
       </c>
       <c r="BB23" s="2">
-        <f t="shared" si="33"/>
-        <v>803.34311418303048</v>
+        <f t="shared" si="31"/>
+        <v>907.4609855358932</v>
       </c>
       <c r="BC23" s="2">
-        <f t="shared" si="33"/>
-        <v>795.30968304120017</v>
+        <f t="shared" si="31"/>
+        <v>898.38637568053423</v>
       </c>
       <c r="BD23" s="2">
-        <f t="shared" si="33"/>
-        <v>787.35658621078812</v>
+        <f t="shared" si="31"/>
+        <v>889.40251192372887</v>
       </c>
       <c r="BE23" s="2">
-        <f t="shared" si="33"/>
-        <v>779.48302034868027</v>
+        <f t="shared" si="31"/>
+        <v>880.50848680449155</v>
       </c>
       <c r="BF23" s="2">
-        <f t="shared" si="33"/>
-        <v>771.68819014519352</v>
+        <f t="shared" si="31"/>
+        <v>871.70340193644665</v>
       </c>
       <c r="BG23" s="2">
-        <f t="shared" si="33"/>
-        <v>763.97130824374153</v>
+        <f t="shared" si="31"/>
+        <v>862.98636791708213</v>
       </c>
       <c r="BH23" s="2">
-        <f t="shared" si="33"/>
-        <v>756.33159516130411</v>
+        <f t="shared" si="31"/>
+        <v>854.35650423791128</v>
       </c>
       <c r="BI23" s="2">
-        <f t="shared" si="33"/>
-        <v>748.76827920969106</v>
+        <f t="shared" si="31"/>
+        <v>845.81293919553218</v>
       </c>
       <c r="BJ23" s="2">
-        <f t="shared" si="33"/>
-        <v>741.2805964175941</v>
+        <f t="shared" si="31"/>
+        <v>837.35480980357681</v>
       </c>
       <c r="BK23" s="2">
-        <f t="shared" si="33"/>
-        <v>733.86779045341814</v>
+        <f t="shared" si="31"/>
+        <v>828.98126170554099</v>
       </c>
       <c r="BL23" s="2">
-        <f t="shared" si="33"/>
-        <v>726.52911254888397</v>
+        <f t="shared" si="31"/>
+        <v>820.69144908848557</v>
       </c>
       <c r="BM23" s="2">
-        <f t="shared" si="33"/>
-        <v>719.26382142339514</v>
+        <f t="shared" si="31"/>
+        <v>812.48453459760071</v>
       </c>
       <c r="BN23" s="2">
-        <f t="shared" si="33"/>
-        <v>712.07118320916118</v>
+        <f t="shared" si="31"/>
+        <v>804.35968925162467</v>
       </c>
       <c r="BO23" s="2">
-        <f t="shared" si="33"/>
-        <v>704.95047137706956</v>
+        <f t="shared" si="31"/>
+        <v>796.31609235910844</v>
       </c>
       <c r="BP23" s="2">
-        <f t="shared" si="33"/>
-        <v>697.90096666329885</v>
+        <f t="shared" si="31"/>
+        <v>788.35293143551735</v>
       </c>
       <c r="BQ23" s="2">
-        <f t="shared" si="33"/>
-        <v>690.92195699666581</v>
+        <f t="shared" si="31"/>
+        <v>780.46940212116215</v>
       </c>
       <c r="BR23" s="2">
-        <f t="shared" si="33"/>
-        <v>684.01273742669912</v>
+        <f t="shared" si="31"/>
+        <v>772.66470809995053</v>
       </c>
       <c r="BS23" s="2">
-        <f t="shared" si="33"/>
-        <v>677.17261005243211</v>
+        <f t="shared" si="31"/>
+        <v>764.93806101895098</v>
       </c>
       <c r="BT23" s="2">
-        <f t="shared" si="33"/>
-        <v>670.40088395190776</v>
+        <f t="shared" si="31"/>
+        <v>757.28868040876148</v>
       </c>
       <c r="BU23" s="2">
-        <f t="shared" si="33"/>
-        <v>663.69687511238862</v>
+        <f t="shared" si="31"/>
+        <v>749.71579360467388</v>
       </c>
       <c r="BV23" s="2">
-        <f t="shared" si="33"/>
-        <v>657.05990636126478</v>
+        <f t="shared" si="31"/>
+        <v>742.21863566862714</v>
       </c>
       <c r="BW23" s="2">
-        <f t="shared" si="33"/>
-        <v>650.48930729765209</v>
+        <f t="shared" si="31"/>
+        <v>734.79644931194082</v>
       </c>
       <c r="BX23" s="2">
-        <f t="shared" si="33"/>
-        <v>643.98441422467556</v>
+        <f t="shared" si="31"/>
+        <v>727.44848481882138</v>
       </c>
       <c r="BY23" s="2">
-        <f t="shared" si="33"/>
-        <v>637.54457008242878</v>
+        <f t="shared" si="31"/>
+        <v>720.17399997063319</v>
       </c>
       <c r="BZ23" s="2">
-        <f t="shared" si="33"/>
-        <v>631.16912438160443</v>
+        <f t="shared" si="31"/>
+        <v>712.97225997092687</v>
       </c>
       <c r="CA23" s="2">
-        <f t="shared" si="33"/>
-        <v>624.85743313778835</v>
+        <f t="shared" si="31"/>
+        <v>705.84253737121765</v>
       </c>
       <c r="CB23" s="2">
-        <f t="shared" si="33"/>
-        <v>618.60885880641047</v>
+        <f t="shared" si="31"/>
+        <v>698.78411199750542</v>
       </c>
       <c r="CC23" s="2">
-        <f t="shared" si="33"/>
-        <v>612.42277021834639</v>
+        <f t="shared" si="31"/>
+        <v>691.79627087753033</v>
       </c>
       <c r="CD23" s="2">
-        <f t="shared" si="33"/>
-        <v>606.29854251616291</v>
+        <f t="shared" si="31"/>
+        <v>684.87830816875498</v>
       </c>
       <c r="CE23" s="2">
-        <f t="shared" si="33"/>
-        <v>600.23555709100128</v>
+        <f t="shared" si="31"/>
+        <v>678.02952508706744</v>
       </c>
       <c r="CF23" s="2">
-        <f t="shared" si="33"/>
-        <v>594.23320152009126</v>
+        <f t="shared" si="31"/>
+        <v>671.24922983619672</v>
       </c>
       <c r="CG23" s="2">
-        <f t="shared" si="33"/>
-        <v>588.29086950489034</v>
+        <f t="shared" si="31"/>
+        <v>664.53673753783471</v>
       </c>
       <c r="CH23" s="2">
-        <f t="shared" si="33"/>
-        <v>582.40796080984148</v>
+        <f t="shared" si="31"/>
+        <v>657.89137016245638</v>
       </c>
       <c r="CI23" s="2">
-        <f t="shared" si="33"/>
-        <v>576.58388120174311</v>
+        <f t="shared" si="31"/>
+        <v>651.31245646083187</v>
       </c>
       <c r="CJ23" s="2">
-        <f t="shared" si="33"/>
-        <v>570.81804238972563</v>
+        <f t="shared" si="31"/>
+        <v>644.79933189622352</v>
       </c>
       <c r="CK23" s="2">
-        <f t="shared" si="33"/>
-        <v>565.10986196582837</v>
+        <f t="shared" si="31"/>
+        <v>638.35133857726123</v>
       </c>
       <c r="CL23" s="2">
-        <f t="shared" si="33"/>
-        <v>559.45876334617003</v>
+        <f t="shared" si="31"/>
+        <v>631.9678251914886</v>
       </c>
       <c r="CM23" s="2">
-        <f t="shared" si="33"/>
-        <v>553.86417571270829</v>
+        <f t="shared" si="31"/>
+        <v>625.64814693957373</v>
       </c>
       <c r="CN23" s="2">
-        <f t="shared" si="33"/>
-        <v>548.32553395558125</v>
+        <f t="shared" si="31"/>
+        <v>619.39166547017794</v>
       </c>
       <c r="CO23" s="2">
-        <f t="shared" si="33"/>
-        <v>542.8422786160254</v>
+        <f t="shared" si="31"/>
+        <v>613.19774881547619</v>
       </c>
       <c r="CP23" s="2">
-        <f t="shared" si="33"/>
-        <v>537.41385582986516</v>
+        <f t="shared" si="31"/>
+        <v>607.06577132732139</v>
       </c>
       <c r="CQ23" s="2">
-        <f t="shared" si="33"/>
-        <v>532.03971727156647</v>
+        <f t="shared" si="31"/>
+        <v>600.99511361404814</v>
       </c>
       <c r="CR23" s="2">
-        <f t="shared" si="33"/>
-        <v>526.71932009885086</v>
+        <f t="shared" si="31"/>
+        <v>594.98516247790769</v>
       </c>
       <c r="CS23" s="2">
-        <f t="shared" si="33"/>
-        <v>521.4521268978624</v>
+        <f t="shared" si="31"/>
+        <v>589.03531085312864</v>
       </c>
       <c r="CT23" s="2">
-        <f t="shared" ref="CT23:EI23" si="34">CS23*(1+$AI$31)</f>
-        <v>516.23760562888378</v>
+        <f t="shared" ref="CT23:EI23" si="32">CS23*(1+$AI$31)</f>
+        <v>583.14495774459738</v>
       </c>
       <c r="CU23" s="2">
-        <f t="shared" si="34"/>
-        <v>511.07522957259494</v>
+        <f t="shared" si="32"/>
+        <v>577.31350816715144</v>
       </c>
       <c r="CV23" s="2">
-        <f t="shared" si="34"/>
-        <v>505.96447727686899</v>
+        <f t="shared" si="32"/>
+        <v>571.54037308547993</v>
       </c>
       <c r="CW23" s="2">
-        <f t="shared" si="34"/>
-        <v>500.90483250410028</v>
+        <f t="shared" si="32"/>
+        <v>565.82496935462507</v>
       </c>
       <c r="CX23" s="2">
-        <f t="shared" si="34"/>
-        <v>495.89578417905926</v>
+        <f t="shared" si="32"/>
+        <v>560.16671966107879</v>
       </c>
       <c r="CY23" s="2">
-        <f t="shared" si="34"/>
-        <v>490.93682633726866</v>
+        <f t="shared" si="32"/>
+        <v>554.56505246446795</v>
       </c>
       <c r="CZ23" s="2">
-        <f t="shared" si="34"/>
-        <v>486.02745807389596</v>
+        <f t="shared" si="32"/>
+        <v>549.0194019398233</v>
       </c>
       <c r="DA23" s="2">
-        <f t="shared" si="34"/>
-        <v>481.16718349315698</v>
+        <f t="shared" si="32"/>
+        <v>543.52920792042505</v>
       </c>
       <c r="DB23" s="2">
-        <f t="shared" si="34"/>
-        <v>476.3555116582254</v>
+        <f t="shared" si="32"/>
+        <v>538.09391584122079</v>
       </c>
       <c r="DC23" s="2">
-        <f t="shared" si="34"/>
-        <v>471.59195654164313</v>
+        <f t="shared" si="32"/>
+        <v>532.71297668280863</v>
       </c>
       <c r="DD23" s="2">
-        <f t="shared" si="34"/>
-        <v>466.87603697622671</v>
+        <f t="shared" si="32"/>
+        <v>527.38584691598055</v>
       </c>
       <c r="DE23" s="2">
-        <f t="shared" si="34"/>
-        <v>462.20727660646446</v>
+        <f t="shared" si="32"/>
+        <v>522.11198844682076</v>
       </c>
       <c r="DF23" s="2">
-        <f t="shared" si="34"/>
-        <v>457.5852038403998</v>
+        <f t="shared" si="32"/>
+        <v>516.89086856235258</v>
       </c>
       <c r="DG23" s="2">
-        <f t="shared" si="34"/>
-        <v>453.00935180199582</v>
+        <f t="shared" si="32"/>
+        <v>511.72195987672904</v>
       </c>
       <c r="DH23" s="2">
-        <f t="shared" si="34"/>
-        <v>448.47925828397587</v>
+        <f t="shared" si="32"/>
+        <v>506.60474027796175</v>
       </c>
       <c r="DI23" s="2">
-        <f t="shared" si="34"/>
-        <v>443.99446570113611</v>
+        <f t="shared" si="32"/>
+        <v>501.53869287518211</v>
       </c>
       <c r="DJ23" s="2">
-        <f t="shared" si="34"/>
-        <v>439.55452104412473</v>
+        <f t="shared" si="32"/>
+        <v>496.5233059464303</v>
       </c>
       <c r="DK23" s="2">
-        <f t="shared" si="34"/>
-        <v>435.15897583368348</v>
+        <f t="shared" si="32"/>
+        <v>491.55807288696599</v>
       </c>
       <c r="DL23" s="2">
-        <f t="shared" si="34"/>
-        <v>430.80738607534664</v>
+        <f t="shared" si="32"/>
+        <v>486.64249215809633</v>
       </c>
       <c r="DM23" s="2">
-        <f t="shared" si="34"/>
-        <v>426.49931221459315</v>
+        <f t="shared" si="32"/>
+        <v>481.77606723651536</v>
       </c>
       <c r="DN23" s="2">
-        <f t="shared" si="34"/>
-        <v>422.23431909244721</v>
+        <f t="shared" si="32"/>
+        <v>476.95830656415018</v>
       </c>
       <c r="DO23" s="2">
-        <f t="shared" si="34"/>
-        <v>418.01197590152276</v>
+        <f t="shared" si="32"/>
+        <v>472.18872349850869</v>
       </c>
       <c r="DP23" s="2">
-        <f t="shared" si="34"/>
-        <v>413.83185614250755</v>
+        <f t="shared" si="32"/>
+        <v>467.46683626352359</v>
       </c>
       <c r="DQ23" s="2">
-        <f t="shared" si="34"/>
-        <v>409.69353758108247</v>
+        <f t="shared" si="32"/>
+        <v>462.79216790088833</v>
       </c>
       <c r="DR23" s="2">
-        <f t="shared" si="34"/>
-        <v>405.59660220527167</v>
+        <f t="shared" si="32"/>
+        <v>458.16424622187947</v>
       </c>
       <c r="DS23" s="2">
-        <f t="shared" si="34"/>
-        <v>401.54063618321896</v>
+        <f t="shared" si="32"/>
+        <v>453.58260375966069</v>
       </c>
       <c r="DT23" s="2">
-        <f t="shared" si="34"/>
-        <v>397.52522982138674</v>
+        <f t="shared" si="32"/>
+        <v>449.04677772206406</v>
       </c>
       <c r="DU23" s="2">
-        <f t="shared" si="34"/>
-        <v>393.54997752317286</v>
+        <f t="shared" si="32"/>
+        <v>444.55630994484341</v>
       </c>
       <c r="DV23" s="2">
-        <f t="shared" si="34"/>
-        <v>389.61447774794112</v>
+        <f t="shared" si="32"/>
+        <v>440.11074684539494</v>
       </c>
       <c r="DW23" s="2">
-        <f t="shared" si="34"/>
-        <v>385.71833297046169</v>
+        <f t="shared" si="32"/>
+        <v>435.70963937694097</v>
       </c>
       <c r="DX23" s="2">
-        <f t="shared" si="34"/>
-        <v>381.86114964075705</v>
+        <f t="shared" si="32"/>
+        <v>431.35254298317153</v>
       </c>
       <c r="DY23" s="2">
-        <f t="shared" si="34"/>
-        <v>378.04253814434946</v>
+        <f t="shared" si="32"/>
+        <v>427.03901755333982</v>
       </c>
       <c r="DZ23" s="2">
-        <f t="shared" si="34"/>
-        <v>374.26211276290599</v>
+        <f t="shared" si="32"/>
+        <v>422.76862737780641</v>
       </c>
       <c r="EA23" s="2">
-        <f t="shared" si="34"/>
-        <v>370.51949163527695</v>
+        <f t="shared" si="32"/>
+        <v>418.54094110402832</v>
       </c>
       <c r="EB23" s="2">
-        <f t="shared" si="34"/>
-        <v>366.8142967189242</v>
+        <f t="shared" si="32"/>
+        <v>414.35553169298805</v>
       </c>
       <c r="EC23" s="2">
-        <f t="shared" si="34"/>
-        <v>363.14615375173497</v>
+        <f t="shared" si="32"/>
+        <v>410.21197637605815</v>
       </c>
       <c r="ED23" s="2">
-        <f t="shared" si="34"/>
-        <v>359.51469221421763</v>
+        <f t="shared" si="32"/>
+        <v>406.10985661229756</v>
       </c>
       <c r="EE23" s="2">
-        <f t="shared" si="34"/>
-        <v>355.91954529207544</v>
+        <f t="shared" si="32"/>
+        <v>402.04875804617456</v>
       </c>
       <c r="EF23" s="2">
-        <f t="shared" si="34"/>
-        <v>352.36034983915471</v>
+        <f t="shared" si="32"/>
+        <v>398.02827046571281</v>
       </c>
       <c r="EG23" s="2">
-        <f t="shared" si="34"/>
-        <v>348.83674634076317</v>
+        <f t="shared" si="32"/>
+        <v>394.04798776105565</v>
       </c>
       <c r="EH23" s="2">
-        <f t="shared" si="34"/>
-        <v>345.34837887735551</v>
+        <f t="shared" si="32"/>
+        <v>390.10750788344507</v>
       </c>
       <c r="EI23" s="2">
-        <f t="shared" si="34"/>
-        <v>341.89489508858196</v>
+        <f t="shared" si="32"/>
+        <v>386.20643280461059</v>
       </c>
     </row>
     <row r="24" spans="2:139">
@@ -5387,92 +5396,92 @@
         <v>2</v>
       </c>
       <c r="E24" s="6">
-        <f t="shared" ref="E24:L24" si="35">86.8+12.3</f>
+        <f t="shared" ref="E24:L24" si="33">86.8+12.3</f>
         <v>99.1</v>
       </c>
       <c r="F24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="H24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="I24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="J24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="K24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="L24" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>99.1</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" ref="M24:N24" si="36">86.8+12.3</f>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="N24" s="6">
-        <f t="shared" si="36"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="U24" s="6">
         <f>86.8+12.3</f>
         <v>99.1</v>
       </c>
       <c r="V24" s="6">
-        <f>86.8+12.3</f>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="W24" s="6">
-        <f>86.8+12.3</f>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="X24" s="6">
-        <f t="shared" ref="X24:AF24" si="37">86.8+12.3</f>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="Y24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="Z24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="AA24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="AB24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="AC24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="AD24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="AE24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
       <c r="AF24" s="6">
-        <f t="shared" si="37"/>
-        <v>99.1</v>
+        <f>99.2</f>
+        <v>99.2</v>
       </c>
     </row>
     <row r="25" spans="2:139">
@@ -5480,44 +5489,44 @@
         <v>26</v>
       </c>
       <c r="E25" s="14">
-        <f t="shared" ref="E25:L25" si="38">E23/E24</f>
+        <f t="shared" ref="E25:L25" si="34">E23/E24</f>
         <v>-0.37336024217961655</v>
       </c>
       <c r="F25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>2.1695257315842587</v>
       </c>
       <c r="G25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>1.109989909182644</v>
       </c>
       <c r="H25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>0.19172552976791121</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>1.1806256306760847</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>1.2512613521695257</v>
       </c>
       <c r="K25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>0.44399596367305755</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="34"/>
         <v>1.7961654894046419</v>
       </c>
       <c r="M25" s="14">
-        <f t="shared" ref="M25:N25" si="39">M23/M24</f>
-        <v>1.204439959636731</v>
+        <f t="shared" ref="M25:N25" si="35">M23/M24</f>
+        <v>0.53427419354838712</v>
       </c>
       <c r="N25" s="14">
-        <f t="shared" si="39"/>
-        <v>1.6163067608476291</v>
+        <f t="shared" si="35"/>
+        <v>1.6146774193548392</v>
       </c>
       <c r="U25" s="14">
         <f>U23/U24</f>
@@ -5525,47 +5534,47 @@
       </c>
       <c r="V25" s="14">
         <f>V23/V24</f>
-        <v>5.0609081735620638</v>
+        <v>4.3868548387096871</v>
       </c>
       <c r="W25" s="14">
         <f>W23/W24</f>
-        <v>5.8027624117053511</v>
+        <v>6.2339114717741939</v>
       </c>
       <c r="X25" s="14">
-        <f t="shared" ref="X25:AF25" si="40">X23/X24</f>
-        <v>6.7798688118062609</v>
+        <f t="shared" ref="X25:AF25" si="36">X23/X24</f>
+        <v>7.78377013467742</v>
       </c>
       <c r="Y25" s="14">
-        <f t="shared" si="40"/>
-        <v>7.3355895417356294</v>
+        <f t="shared" si="36"/>
+        <v>8.3885906472076606</v>
       </c>
       <c r="Z25" s="14">
-        <f t="shared" si="40"/>
-        <v>7.722074569062066</v>
+        <f t="shared" si="36"/>
+        <v>8.8103857153374037</v>
       </c>
       <c r="AA25" s="14">
-        <f t="shared" si="40"/>
-        <v>8.0771372853815766</v>
+        <f t="shared" si="36"/>
+        <v>9.198580120735631</v>
       </c>
       <c r="AB25" s="14">
-        <f t="shared" si="40"/>
-        <v>8.4476753130125335</v>
+        <f t="shared" si="36"/>
+        <v>9.6030762923027879</v>
       </c>
       <c r="AC25" s="14">
-        <f t="shared" si="40"/>
-        <v>8.8349237223288721</v>
+        <f t="shared" si="36"/>
+        <v>10.025096293164591</v>
       </c>
       <c r="AD25" s="14">
-        <f t="shared" si="40"/>
-        <v>9.2403086045283533</v>
+        <f t="shared" si="36"/>
+        <v>10.466045178951106</v>
       </c>
       <c r="AE25" s="14">
-        <f t="shared" si="40"/>
-        <v>9.6654837115410395</v>
+        <f t="shared" si="36"/>
+        <v>10.927545867674493</v>
       </c>
       <c r="AF25" s="14">
-        <f t="shared" si="40"/>
-        <v>10.112374384625126</v>
+        <f t="shared" si="36"/>
+        <v>11.411480939321839</v>
       </c>
     </row>
     <row r="27" spans="2:139">
@@ -5578,11 +5587,11 @@
       <c r="L27" s="16"/>
       <c r="M27" s="16">
         <f>M3/I3-1</f>
-        <v>9.5238095238095344E-2</v>
+        <v>0.12925170068027203</v>
       </c>
       <c r="N27" s="16">
         <f>N3/J3-1</f>
-        <v>0.11805555555555558</v>
+        <v>0.15277777777777768</v>
       </c>
       <c r="U27" s="16">
         <f>U3/T3-1</f>
@@ -5590,7 +5599,7 @@
       </c>
       <c r="V27" s="16">
         <f>V3/U3-1</f>
-        <v>0.11805555555555558</v>
+        <v>0.15277777777777768</v>
       </c>
     </row>
     <row r="28" spans="2:139">
@@ -5612,72 +5621,72 @@
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
       <c r="I29" s="16">
-        <f t="shared" ref="I29:L32" si="41">I5/E5-1</f>
+        <f t="shared" ref="I29:L32" si="37">I5/E5-1</f>
         <v>6.4200976971388712E-2</v>
       </c>
       <c r="J29" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>1.555814858031912E-3</v>
       </c>
       <c r="K29" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.28553459119496849</v>
       </c>
       <c r="L29" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-0.1513353115727003</v>
       </c>
       <c r="M29" s="16">
-        <f t="shared" ref="M29:M32" si="42">M5/I5-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="M29:M32" si="38">M5/I5-1</f>
+        <v>0.121967213114754</v>
       </c>
       <c r="N29" s="16">
-        <f t="shared" ref="N29:N32" si="43">N5/J5-1</f>
+        <f t="shared" ref="N29:N32" si="39">N5/J5-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="U29" s="16"/>
       <c r="V29" s="16">
         <f>V5/U5-1</f>
-        <v>8.5600303951367751E-2</v>
+        <v>0.10227963525835859</v>
       </c>
       <c r="W29" s="16">
-        <f t="shared" ref="W29:AF32" si="44">W5/V5-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="W29:AF32" si="40">W5/V5-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="X29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="Y29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="Z29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF29" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -5690,72 +5699,72 @@
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
       <c r="I30" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.2753623188405796</v>
       </c>
       <c r="J30" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>8.7136929460580825E-2</v>
       </c>
       <c r="K30" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>3.7735849056603765E-2</v>
       </c>
       <c r="L30" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.16370808678500981</v>
       </c>
       <c r="M30" s="16">
-        <f t="shared" si="42"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="38"/>
+        <v>0.11742424242424243</v>
       </c>
       <c r="N30" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="U30" s="16"/>
       <c r="V30" s="16">
-        <f t="shared" ref="U30:V34" si="45">V6/U6-1</f>
-        <v>9.3457760314342053E-2</v>
+        <f t="shared" ref="V30:V32" si="41">V6/U6-1</f>
+        <v>0.11094302554027502</v>
       </c>
       <c r="W30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="X30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="Y30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Z30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AA30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF30" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -5768,72 +5777,72 @@
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>1.2222222222222223</v>
       </c>
       <c r="J31" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K31" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-0.44444444444444442</v>
       </c>
       <c r="L31" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-0.27272727272727271</v>
       </c>
       <c r="M31" s="16">
-        <f t="shared" si="42"/>
-        <v>-0.55000000000000004</v>
+        <f t="shared" si="38"/>
+        <v>-0.7</v>
       </c>
       <c r="N31" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="U31" s="16"/>
       <c r="V31" s="16">
-        <f t="shared" si="45"/>
-        <v>-0.34693877551020413</v>
+        <f t="shared" si="41"/>
+        <v>-0.40816326530612246</v>
       </c>
       <c r="W31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="X31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="Y31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="Z31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AB31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AC31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AD31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AE31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AF31" s="16">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AH31" s="1" t="s">
@@ -5852,73 +5861,73 @@
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
       <c r="I32" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.1169181034482758</v>
       </c>
       <c r="J32" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>1.5022860875244959E-2</v>
       </c>
       <c r="K32" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>0.1881342701014832</v>
       </c>
       <c r="L32" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>-7.9437131184748044E-2</v>
       </c>
       <c r="M32" s="16">
-        <f t="shared" si="42"/>
-        <v>4.4211287988422665E-2</v>
+        <f t="shared" si="38"/>
+        <v>0.11287988422575967</v>
       </c>
       <c r="N32" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>0.18625482625482626</v>
       </c>
       <c r="U32" s="16"/>
       <c r="V32" s="16">
-        <f t="shared" si="45"/>
-        <v>8.5000577034045177E-2</v>
+        <f t="shared" si="41"/>
+        <v>0.10142873629544158</v>
       </c>
       <c r="W32" s="16">
-        <f t="shared" si="44"/>
-        <v>0.11553630100632573</v>
+        <f t="shared" si="40"/>
+        <v>0.13070239776694592</v>
       </c>
       <c r="X32" s="16">
-        <f t="shared" si="44"/>
-        <v>7.0475983976731715E-2</v>
+        <f t="shared" si="40"/>
+        <v>7.0419227065388279E-2</v>
       </c>
       <c r="Y32" s="16">
-        <f t="shared" si="44"/>
-        <v>4.2990689180072872E-2</v>
+        <f t="shared" si="40"/>
+        <v>4.2883156847113746E-2</v>
       </c>
       <c r="Z32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.3152456972674216E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.3027627938512216E-2</v>
       </c>
       <c r="AA32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.093243779268473E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.082148025403475E-2</v>
       </c>
       <c r="AB32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.1085352744955275E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.0956301671749342E-2</v>
       </c>
       <c r="AC32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.1263157594547453E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.1113104410184889E-2</v>
       </c>
       <c r="AD32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.1469837356540742E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.1295420731740409E-2</v>
       </c>
       <c r="AE32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.1709991668170678E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.1507332280196865E-2</v>
       </c>
       <c r="AF32" s="16">
-        <f t="shared" si="44"/>
-        <v>3.1988921323216957E-2</v>
+        <f t="shared" si="40"/>
+        <v>3.1753549082620847E-2</v>
       </c>
       <c r="AH32" s="1" t="s">
         <v>58</v>
@@ -5932,31 +5941,31 @@
         <v>44</v>
       </c>
       <c r="E33" s="16">
-        <f t="shared" ref="E33:K33" si="46">E10/E8</f>
+        <f t="shared" ref="E33:K33" si="42">E10/E8</f>
         <v>0.20635775862068967</v>
       </c>
       <c r="F33" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.19007184846505551</v>
       </c>
       <c r="G33" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.22248243559718969</v>
       </c>
       <c r="H33" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.20608261461643212</v>
       </c>
       <c r="I33" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.20067534973468404</v>
       </c>
       <c r="J33" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.1998069498069498</v>
       </c>
       <c r="K33" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.18462549277266754</v>
       </c>
       <c r="L33" s="16">
@@ -5964,67 +5973,67 @@
         <v>0.20266272189349113</v>
       </c>
       <c r="M33" s="16">
-        <f t="shared" ref="M33:N33" si="47">M10/M8</f>
+        <f t="shared" ref="M33:N33" si="43">M10/M8</f>
+        <v>0.20112700476809708</v>
+      </c>
+      <c r="N33" s="16">
+        <f t="shared" si="43"/>
         <v>0.2</v>
       </c>
-      <c r="N33" s="16">
-        <f t="shared" si="47"/>
-        <v>0.2</v>
-      </c>
       <c r="U33" s="16">
-        <f t="shared" ref="U33" si="48">U10/U8</f>
+        <f t="shared" ref="U33" si="44">U10/U8</f>
         <v>0.20496249278707443</v>
       </c>
       <c r="V33" s="16">
-        <f t="shared" ref="V33:AF33" si="49">V10/V8</f>
-        <v>0.1980854180117492</v>
+        <f t="shared" ref="V33:AF33" si="45">V10/V8</f>
+        <v>0.19838640049958728</v>
       </c>
       <c r="W33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21000000000000002</v>
       </c>
       <c r="X33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21</v>
       </c>
       <c r="Y33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21</v>
       </c>
       <c r="Z33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21000000000000002</v>
       </c>
       <c r="AA33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21</v>
       </c>
       <c r="AB33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21</v>
       </c>
       <c r="AC33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.20000000000000004</v>
+        <f t="shared" si="45"/>
+        <v>0.20999999999999996</v>
       </c>
       <c r="AD33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.20999999999999996</v>
       </c>
       <c r="AE33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.20000000000000004</v>
+        <f t="shared" si="45"/>
+        <v>0.21</v>
       </c>
       <c r="AF33" s="16">
-        <f t="shared" si="49"/>
-        <v>0.2</v>
+        <f t="shared" si="45"/>
+        <v>0.21</v>
       </c>
       <c r="AH33" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AI33" s="6">
         <f>NPV(AI32,V23:EI23)</f>
-        <v>10070.758342822548</v>
+        <v>11267.766238362408</v>
       </c>
     </row>
     <row r="34" spans="2:35">
@@ -6036,72 +6045,72 @@
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16">
-        <f t="shared" ref="I34:L35" si="50">I11/E11-1</f>
+        <f t="shared" ref="I34:L35" si="46">I11/E11-1</f>
         <v>0.13592233009708732</v>
       </c>
       <c r="J34" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-1.4598540145985384E-2</v>
       </c>
       <c r="K34" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-0.1009174311926605</v>
       </c>
       <c r="L34" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>2.564102564102555E-2</v>
       </c>
       <c r="M34" s="16">
-        <f t="shared" ref="M34:N34" si="51">M11/I11-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="M34:N34" si="47">M11/I11-1</f>
+        <v>5.9829059829059839E-2</v>
       </c>
       <c r="N34" s="16">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="U34" s="16"/>
       <c r="V34" s="16">
         <f>V11/U11-1</f>
-        <v>-9.2050209205019051E-4</v>
+        <v>6.3807531380752902E-3</v>
       </c>
       <c r="W34" s="16">
-        <f t="shared" ref="W34:AF34" si="52">W11/V11-1</f>
+        <f t="shared" ref="W34:AF34" si="48">W11/V11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="X34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Y34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF34" s="16">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH34" s="1" t="s">
@@ -6109,7 +6118,7 @@
       </c>
       <c r="AI34" s="6">
         <f>Main!D8</f>
-        <v>-4448</v>
+        <v>-4321</v>
       </c>
     </row>
     <row r="35" spans="2:35">
@@ -6121,72 +6130,72 @@
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
       <c r="I35" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>9.8765432098765427E-2</v>
       </c>
       <c r="J35" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-0.23417721518987344</v>
       </c>
       <c r="K35" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-1.103448275862069</v>
       </c>
       <c r="L35" s="16">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-0.32743362831858402</v>
       </c>
       <c r="M35" s="16">
-        <f t="shared" ref="M35:N35" si="53">M12/I12-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="M35:N35" si="49">M12/I12-1</f>
+        <v>0.15730337078651679</v>
       </c>
       <c r="N35" s="16">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="U35" s="16"/>
       <c r="V35" s="16">
         <f>V12/U12-1</f>
-        <v>-0.17650568181818183</v>
+        <v>-0.14937499999999992</v>
       </c>
       <c r="W35" s="16">
-        <f t="shared" ref="W35:AF35" si="54">W12/V12-1</f>
+        <f t="shared" ref="W35:AF35" si="50">W12/V12-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Z35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF35" s="16">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH35" s="1" t="s">
@@ -6194,7 +6203,7 @@
       </c>
       <c r="AI35" s="6">
         <f>AI33+AI34</f>
-        <v>5622.758342822548</v>
+        <v>6946.7662383624083</v>
       </c>
     </row>
     <row r="36" spans="2:35">
@@ -6202,31 +6211,31 @@
         <v>50</v>
       </c>
       <c r="E36" s="16">
-        <f t="shared" ref="E36:K36" si="55">E17/E8</f>
+        <f t="shared" ref="E36:K36" si="51">E17/E8</f>
         <v>0.10614224137931035</v>
       </c>
       <c r="F36" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>6.8909209666884394E-2</v>
       </c>
       <c r="G36" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.11241217798594848</v>
       </c>
       <c r="H36" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>8.6699954607353608E-2</v>
       </c>
       <c r="I36" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>9.6960926193921854E-2</v>
       </c>
       <c r="J36" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.11003861003861004</v>
       </c>
       <c r="K36" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.11629434954007885</v>
       </c>
       <c r="L36" s="16">
@@ -6234,67 +6243,67 @@
         <v>0.10108481262327416</v>
       </c>
       <c r="M36" s="16">
-        <f t="shared" ref="M36:N36" si="56">M17/M8</f>
-        <v>9.6537546485575054E-2</v>
+        <f t="shared" ref="M36:N36" si="52">M17/M8</f>
+        <v>9.8396185522323362E-2</v>
       </c>
       <c r="N36" s="16">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.12474124462960554</v>
       </c>
       <c r="U36" s="16">
-        <f t="shared" ref="U36" si="57">U17/U8</f>
+        <f t="shared" ref="U36" si="53">U17/U8</f>
         <v>0.10132717830351991</v>
       </c>
       <c r="V36" s="16">
-        <f t="shared" ref="V36:AF36" si="58">V17/V8</f>
-        <v>0.11177712563806108</v>
+        <f t="shared" ref="V36:AF36" si="54">V17/V8</f>
+        <v>0.11199910309014792</v>
       </c>
       <c r="W36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.12058360860691923</v>
+        <f t="shared" si="54"/>
+        <v>0.13156158745832749</v>
       </c>
       <c r="X36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.12436338657778545</v>
+        <f t="shared" si="54"/>
+        <v>0.13528467400660574</v>
       </c>
       <c r="Y36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.12632240056642327</v>
+        <f t="shared" si="54"/>
+        <v>0.13721063899396863</v>
       </c>
       <c r="Z36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.12754074977298496</v>
+        <f t="shared" si="54"/>
+        <v>0.13840407449774622</v>
       </c>
       <c r="AA36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.12857894665916025</v>
+        <f t="shared" si="54"/>
+        <v>0.13942083417595558</v>
       </c>
       <c r="AB36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.12960610562873573</v>
+        <f t="shared" si="54"/>
+        <v>0.140425810410088</v>
       </c>
       <c r="AC36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.13062380012178135</v>
+        <f t="shared" si="54"/>
+        <v>0.14142041302650443</v>
       </c>
       <c r="AD36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.13163377610648491</v>
+        <f t="shared" si="54"/>
+        <v>0.14240620397126447</v>
       </c>
       <c r="AE36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.13263797464031252</v>
+        <f t="shared" si="54"/>
+        <v>0.14338491785526911</v>
       </c>
       <c r="AF36" s="16">
-        <f t="shared" si="58"/>
-        <v>0.13363855628424812</v>
+        <f t="shared" si="54"/>
+        <v>0.14435848439756699</v>
       </c>
       <c r="AH36" s="1" t="s">
         <v>62</v>
       </c>
       <c r="AI36" s="23">
         <f>AI35/AF24</f>
-        <v>56.738227475505028</v>
+        <v>70.027885467362992</v>
       </c>
     </row>
     <row r="37" spans="2:35">
@@ -6302,31 +6311,31 @@
         <v>24</v>
       </c>
       <c r="E37" s="16">
-        <f t="shared" ref="E37:K37" si="59">E21/E20</f>
+        <f t="shared" ref="E37:K37" si="55">E21/E20</f>
         <v>5.128205128205128E-2</v>
       </c>
       <c r="F37" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>3.1531531531531529E-2</v>
       </c>
       <c r="G37" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>-0.1702127659574468</v>
       </c>
       <c r="H37" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>7.333333333333333</v>
       </c>
       <c r="I37" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>-2.6315789473684209E-2</v>
       </c>
       <c r="J37" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>-1.4313725490196079</v>
       </c>
       <c r="K37" s="16">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="L37" s="16">
@@ -6334,59 +6343,59 @@
         <v>-0.11560693641618497</v>
       </c>
       <c r="M37" s="16">
-        <f t="shared" ref="M37:N37" si="60">M21/M20</f>
+        <f t="shared" ref="M37:N37" si="56">M21/M20</f>
+        <v>-0.14864864864864866</v>
+      </c>
+      <c r="N37" s="16">
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="N37" s="16">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
       <c r="U37" s="16">
-        <f t="shared" ref="U37" si="61">U21/U20</f>
+        <f t="shared" ref="U37" si="57">U21/U20</f>
         <v>-0.4453125</v>
       </c>
       <c r="V37" s="16">
-        <f t="shared" ref="V37:AF37" si="62">V21/V20</f>
-        <v>-3.8188191407254914E-2</v>
+        <f t="shared" ref="V37:AF37" si="58">V21/V20</f>
+        <v>-6.6345847634549232E-2</v>
       </c>
       <c r="W37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="X37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="Y37" s="16">
-        <f t="shared" si="62"/>
-        <v>0.14999999999999997</v>
+        <f t="shared" si="58"/>
+        <v>0.15</v>
       </c>
       <c r="Z37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AA37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AB37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AC37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AD37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AE37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AF37" s="16">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.15</v>
       </c>
       <c r="AH37" s="1" t="s">
@@ -6394,7 +6403,7 @@
       </c>
       <c r="AI37" s="23">
         <f>Main!D3</f>
-        <v>195.91</v>
+        <v>162.50479999999999</v>
       </c>
     </row>
     <row r="38" spans="2:35">
@@ -6402,31 +6411,31 @@
         <v>51</v>
       </c>
       <c r="E38" s="16">
-        <f t="shared" ref="E38:K38" si="63">E23/E8</f>
+        <f t="shared" ref="E38:K38" si="59">E23/E8</f>
         <v>-1.9935344827586209E-2</v>
       </c>
       <c r="F38" s="16">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>7.0215545395166556E-2</v>
       </c>
       <c r="G38" s="16">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>8.5870413739266196E-2</v>
       </c>
       <c r="H38" s="16">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>8.6246028143440769E-3</v>
       </c>
       <c r="I38" s="16">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>5.6439942112879886E-2</v>
       </c>
       <c r="J38" s="16">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>3.9897039897039896E-2</v>
       </c>
       <c r="K38" s="16">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>2.8909329829172142E-2</v>
       </c>
       <c r="L38" s="16">
@@ -6434,67 +6443,67 @@
         <v>8.7771203155818545E-2</v>
       </c>
       <c r="M38" s="16">
-        <f t="shared" ref="M38:N38" si="64">M23/M8</f>
-        <v>5.5140553900168636E-2</v>
+        <f t="shared" ref="M38:N38" si="60">M23/M8</f>
+        <v>2.2973558734286952E-2</v>
       </c>
       <c r="N38" s="16">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>4.3444863950006518E-2</v>
       </c>
       <c r="U38" s="16">
-        <f t="shared" ref="U38" si="65">U23/U8</f>
+        <f t="shared" ref="U38" si="61">U23/U8</f>
         <v>4.2700519330640507E-2</v>
       </c>
       <c r="V38" s="16">
-        <f t="shared" ref="V38:AF38" si="66">V23/V8</f>
-        <v>5.334621066996547E-2</v>
+        <f t="shared" ref="V38:AF38" si="62">V23/V8</f>
+        <v>4.5597388064393202E-2</v>
       </c>
       <c r="W38" s="16">
-        <f t="shared" si="66"/>
-        <v>5.4831004234655541E-2</v>
+        <f t="shared" si="62"/>
+        <v>5.7305858021767193E-2</v>
       </c>
       <c r="X38" s="16">
-        <f t="shared" si="66"/>
-        <v>5.9846088852221688E-2</v>
+        <f t="shared" si="62"/>
+        <v>6.6845856099188902E-2</v>
       </c>
       <c r="Y38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.2082482348569251E-2</v>
+        <f t="shared" si="62"/>
+        <v>6.907769476511548E-2</v>
       </c>
       <c r="Z38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.3256277256410059E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.0231479842168265E-2</v>
       </c>
       <c r="AA38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.417958404572148E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.113350903453268E-2</v>
       </c>
       <c r="AB38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.5100156022380173E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.2031682526016674E-2</v>
       </c>
       <c r="AC38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.6020394899883289E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.2928188579369668E-2</v>
       </c>
       <c r="AD38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.6943013189534592E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.3825498722254523E-2</v>
       </c>
       <c r="AE38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.7871076488419418E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.4726407350762525E-2</v>
       </c>
       <c r="AF38" s="16">
-        <f t="shared" si="66"/>
-        <v>6.8808049808672042E-2</v>
+        <f t="shared" si="62"/>
+        <v>7.5634075485520411E-2</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>64</v>
       </c>
       <c r="AI38" s="22">
         <f>AI36/AI37-1</f>
-        <v>-0.710386261673702</v>
+        <v>-0.56907189530793556</v>
       </c>
     </row>
     <row r="39" spans="2:35">
@@ -6509,27 +6518,35 @@
       <c r="B41" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="L41" s="20">
+      <c r="L41" s="24">
         <f>12864</f>
         <v>12864</v>
+      </c>
+      <c r="M41" s="24">
+        <v>13333</v>
+      </c>
+      <c r="V41" s="24">
+        <v>13333</v>
       </c>
     </row>
     <row r="43" spans="2:35">
       <c r="B43" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L43" s="21">
-        <f>Main!D9/Model!L41</f>
-        <v>1.8549969682835818</v>
+      <c r="L43" s="21"/>
+      <c r="V43" s="21">
+        <f>Main!$D$9/Model!V41</f>
+        <v>1.533149040726018</v>
       </c>
     </row>
     <row r="44" spans="2:35">
       <c r="B44" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L44" s="16">
-        <f>L41/Main!D9-1</f>
-        <v>-0.46091556099668762</v>
+      <c r="L44" s="16"/>
+      <c r="V44" s="16">
+        <f>V41/Main!$D$9-1</f>
+        <v>-0.34774769220971946</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/BBD.A.xlsx
+++ b/Financial Analysis/BBD.A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F30132-8B08-4A88-A40C-462C5902DCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE78F00D-D094-44DC-A112-FE7BBE347B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{346DD61D-C15D-48A0-ADE2-5B9C576CD682}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
   <si>
     <t>BBD</t>
   </si>
@@ -226,13 +226,43 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
-  </si>
-  <si>
-    <t>USD/CAD</t>
-  </si>
-  <si>
     <t>CAD$</t>
+  </si>
+  <si>
+    <t>CAD/USD</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Large aircraft</t>
+  </si>
+  <si>
+    <t>Medium aircraft</t>
+  </si>
+  <si>
+    <t>Total deliveries</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Contractual</t>
+  </si>
+  <si>
+    <t>Total employees</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -258,7 +288,7 @@
     <numFmt numFmtId="177" formatCode="0.0\x"/>
     <numFmt numFmtId="178" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,6 +622,15 @@
     <font>
       <b/>
       <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -1951,7 +1990,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1975,9 +2014,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="648" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1991,6 +2027,15 @@
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="53" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="54" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="649">
     <cellStyle name="_Exec Summary FINAL" xfId="3" xr:uid="{19585BA9-F398-4EDE-A7B7-F00CFAAF7DC7}"/>
@@ -2660,15 +2705,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2684,8 +2729,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8435340" y="7620"/>
-          <a:ext cx="0" cy="9974580"/>
+          <a:off x="9052560" y="7620"/>
+          <a:ext cx="0" cy="11254740"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2710,15 +2755,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3087,17 +3132,17 @@
       </c>
       <c r="D3" s="5">
         <f>D12*D13</f>
-        <v>162.50479999999999</v>
+        <v>178.49960000000002</v>
       </c>
       <c r="E3" s="4">
-        <v>45988</v>
+        <v>46070</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45988</v>
+        <v>46070</v>
       </c>
       <c r="G3" s="4">
-        <v>46065</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -3105,11 +3150,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
+        <f>12.1+88.1</f>
+        <v>100.19999999999999</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -3118,7 +3163,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>16120.47616</v>
+        <v>17885.659919999998</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -3126,11 +3171,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1182</f>
-        <v>1182</v>
+        <f>2175</f>
+        <v>2175</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -3138,11 +3183,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>250+5253</f>
-        <v>5503</v>
+        <f>607+4547</f>
+        <v>5154</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -3151,7 +3196,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-4321</v>
+        <v>-2979</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -3160,15 +3205,15 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>20441.476159999998</v>
+        <v>20864.659919999998</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D12" s="1">
-        <v>228.88</v>
+        <v>244.52</v>
       </c>
     </row>
     <row r="13" spans="2:7">
@@ -3176,7 +3221,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="1">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -3186,18 +3231,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D972C2C-CAC0-4237-B51D-27B3C5E485D0}">
-  <dimension ref="A2:EI44"/>
+  <dimension ref="A2:EM51"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="8.88671875" style="1"/>
-    <col min="34" max="34" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="37" width="8.88671875" style="1"/>
+    <col min="38" max="38" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:36">
       <c r="C2" s="12" t="s">
         <v>27</v>
       </c>
@@ -3234,100 +3279,105 @@
       <c r="N2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="1">
+      <c r="O2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="T2" s="1">
         <v>2019</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="U2" s="1">
         <v>2020</v>
       </c>
-      <c r="R2" s="1">
+      <c r="V2" s="1">
         <v>2021</v>
       </c>
-      <c r="S2" s="1">
+      <c r="W2" s="1">
         <v>2022</v>
       </c>
-      <c r="T2" s="1">
+      <c r="X2" s="1">
         <v>2023</v>
       </c>
-      <c r="U2" s="1">
+      <c r="Y2" s="1">
         <v>2024</v>
       </c>
-      <c r="V2" s="1">
+      <c r="Z2" s="1">
         <v>2025</v>
       </c>
-      <c r="W2" s="1">
+      <c r="AA2" s="1">
         <v>2026</v>
       </c>
-      <c r="X2" s="1">
+      <c r="AB2" s="1">
         <v>2027</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <v>2028</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <v>2029</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <v>2030</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <v>2031</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <v>2032</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <v>2033</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <v>2034</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:32" s="6" customFormat="1">
-      <c r="A3" s="1"/>
+    <row r="3" spans="1:36">
       <c r="B3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18">
-        <v>14200</v>
-      </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18">
-        <v>14700</v>
-      </c>
-      <c r="J3" s="18">
-        <v>14400</v>
-      </c>
-      <c r="K3" s="18">
-        <v>14200</v>
-      </c>
-      <c r="L3" s="18">
-        <v>16100</v>
-      </c>
-      <c r="M3" s="18">
-        <v>16600</v>
-      </c>
-      <c r="N3" s="13">
-        <v>16600</v>
-      </c>
-      <c r="T3" s="18">
-        <v>14200</v>
-      </c>
-      <c r="U3" s="6">
-        <v>14400</v>
-      </c>
-      <c r="V3" s="18">
-        <v>16600</v>
+        <v>73</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12">
+        <v>28</v>
+      </c>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12">
+        <v>25</v>
+      </c>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="Y3" s="12">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:36">
+      <c r="B4" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -3335,3218 +3385,3545 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
+      <c r="J4" s="12">
+        <v>29</v>
+      </c>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
+      <c r="N4" s="12">
+        <v>39</v>
+      </c>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="Y4" s="12">
+        <v>73</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>86</v>
+      </c>
     </row>
-    <row r="5" spans="1:32">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:36" s="2" customFormat="1">
+      <c r="B5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24">
+        <f>SUM(J3:J4)</f>
+        <v>57</v>
+      </c>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24">
+        <f>SUM(N3:N4)</f>
+        <v>64</v>
+      </c>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="Y5" s="24">
+        <f>SUM(Y3:Y4)</f>
+        <v>146</v>
+      </c>
+      <c r="Z5" s="24">
+        <f>SUM(Z3:Z4)</f>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" spans="1:36" s="16" customFormat="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25">
+        <v>14200</v>
+      </c>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25">
+        <v>14700</v>
+      </c>
+      <c r="J7" s="25">
+        <v>14400</v>
+      </c>
+      <c r="K7" s="25">
+        <v>14200</v>
+      </c>
+      <c r="L7" s="25">
+        <v>16100</v>
+      </c>
+      <c r="M7" s="25">
+        <v>16600</v>
+      </c>
+      <c r="N7" s="25">
+        <v>17500</v>
+      </c>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="X7" s="25">
+        <v>14200</v>
+      </c>
+      <c r="Y7" s="16">
+        <v>14400</v>
+      </c>
+      <c r="Z7" s="25">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="1:36">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18">
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17">
         <v>1433</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F9" s="17">
         <v>2571</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G9" s="17">
         <v>795</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H9" s="17">
         <v>1685</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I9" s="17">
         <v>1525</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J9" s="17">
         <v>2575</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K9" s="17">
         <v>1022</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L9" s="17">
         <v>1430</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M9" s="17">
         <v>1711</v>
       </c>
-      <c r="N5" s="18">
-        <f>J5*1.2</f>
-        <v>3090</v>
-      </c>
-      <c r="U5" s="18">
-        <f>SUM(G5:J5)</f>
+      <c r="N9" s="17">
+        <f>Z9-M9-L9-K9</f>
+        <v>3059</v>
+      </c>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="Y9" s="17">
+        <f>SUM(G9:J9)</f>
         <v>6580</v>
       </c>
-      <c r="V5" s="18">
-        <f>SUM(K5:N5)</f>
-        <v>7253</v>
-      </c>
-      <c r="W5" s="6">
-        <f>V5*1.14</f>
-        <v>8268.42</v>
-      </c>
-      <c r="X5" s="6">
-        <f>W5*1.07</f>
-        <v>8847.2093999999997</v>
-      </c>
-      <c r="Y5" s="6">
-        <f>X5*1.04</f>
-        <v>9201.0977760000005</v>
-      </c>
-      <c r="Z5" s="6">
-        <f>Y5*1.03</f>
-        <v>9477.1307092800016</v>
-      </c>
-      <c r="AA5" s="6">
-        <f t="shared" ref="AA5:AF6" si="0">Z5*1.03</f>
-        <v>9761.4446305584024</v>
-      </c>
-      <c r="AB5" s="6">
+      <c r="Z9" s="17">
+        <v>7222</v>
+      </c>
+      <c r="AA9" s="6">
+        <f>Z9*1.05</f>
+        <v>7583.1</v>
+      </c>
+      <c r="AB9" s="6">
+        <f>AA9*1.04</f>
+        <v>7886.4240000000009</v>
+      </c>
+      <c r="AC9" s="6">
+        <f>AB9*1.03</f>
+        <v>8123.0167200000014</v>
+      </c>
+      <c r="AD9" s="6">
+        <f>AC9*1.03</f>
+        <v>8366.7072216000015</v>
+      </c>
+      <c r="AE9" s="6">
+        <f t="shared" ref="AE9:AJ10" si="0">AD9*1.03</f>
+        <v>8617.7084382480025</v>
+      </c>
+      <c r="AF9" s="6">
         <f t="shared" si="0"/>
-        <v>10054.287969475155</v>
-      </c>
-      <c r="AC5" s="6">
+        <v>8876.2396913954435</v>
+      </c>
+      <c r="AG9" s="6">
         <f t="shared" si="0"/>
-        <v>10355.91660855941</v>
-      </c>
-      <c r="AD5" s="6">
+        <v>9142.5268821373065</v>
+      </c>
+      <c r="AH9" s="6">
         <f t="shared" si="0"/>
-        <v>10666.594106816192</v>
-      </c>
-      <c r="AE5" s="6">
+        <v>9416.8026886014268</v>
+      </c>
+      <c r="AI9" s="6">
         <f t="shared" si="0"/>
-        <v>10986.591930020679</v>
-      </c>
-      <c r="AF5" s="6">
+        <v>9699.3067692594705</v>
+      </c>
+      <c r="AJ9" s="6">
         <f t="shared" si="0"/>
-        <v>11316.1896879213</v>
+        <v>9990.2859723372549</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
-      <c r="B6" s="1" t="s">
+    <row r="10" spans="1:36">
+      <c r="B10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17">
         <v>414</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F10" s="17">
         <v>482</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G10" s="17">
         <v>477</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H10" s="17">
         <v>507</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I10" s="17">
         <v>528</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J10" s="17">
         <v>524</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K10" s="17">
         <v>495</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L10" s="17">
         <v>590</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M10" s="17">
         <v>590</v>
       </c>
-      <c r="N6" s="18">
-        <f>J6*1.12</f>
-        <v>586.88000000000011</v>
-      </c>
-      <c r="U6" s="18">
-        <f>SUM(G6:J6)</f>
+      <c r="N10" s="17">
+        <f t="shared" ref="N10:N19" si="1">Z10-M10-L10-K10</f>
+        <v>630</v>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="Y10" s="17">
+        <f>SUM(G10:J10)</f>
         <v>2036</v>
       </c>
-      <c r="V6" s="18">
-        <f t="shared" ref="V6:V7" si="1">SUM(K6:N6)</f>
-        <v>2261.88</v>
-      </c>
-      <c r="W6" s="6">
-        <f>V6*1.1</f>
-        <v>2488.0680000000002</v>
-      </c>
-      <c r="X6" s="6">
-        <f>W6*1.07</f>
-        <v>2662.2327600000003</v>
-      </c>
-      <c r="Y6" s="6">
-        <f>X6*1.05</f>
-        <v>2795.3443980000006</v>
-      </c>
-      <c r="Z6" s="6">
-        <f>Y6*1.04</f>
-        <v>2907.1581739200005</v>
-      </c>
-      <c r="AA6" s="6">
-        <f>Z6*1.03</f>
-        <v>2994.3729191376005</v>
-      </c>
-      <c r="AB6" s="6">
+      <c r="Z10" s="17">
+        <v>2305</v>
+      </c>
+      <c r="AA10" s="6">
+        <f>Z10*1.1</f>
+        <v>2535.5</v>
+      </c>
+      <c r="AB10" s="6">
+        <f>AA10*1.07</f>
+        <v>2712.9850000000001</v>
+      </c>
+      <c r="AC10" s="6">
+        <f>AB10*1.05</f>
+        <v>2848.6342500000001</v>
+      </c>
+      <c r="AD10" s="6">
+        <f>AC10*1.04</f>
+        <v>2962.57962</v>
+      </c>
+      <c r="AE10" s="6">
+        <f>AD10*1.03</f>
+        <v>3051.4570085999999</v>
+      </c>
+      <c r="AF10" s="6">
         <f t="shared" si="0"/>
-        <v>3084.2041067117289</v>
-      </c>
-      <c r="AC6" s="6">
+        <v>3143.0007188579998</v>
+      </c>
+      <c r="AG10" s="6">
         <f t="shared" si="0"/>
-        <v>3176.7302299130806</v>
-      </c>
-      <c r="AD6" s="6">
+        <v>3237.2907404237399</v>
+      </c>
+      <c r="AH10" s="6">
         <f t="shared" si="0"/>
-        <v>3272.0321368104733</v>
-      </c>
-      <c r="AE6" s="6">
+        <v>3334.4094626364522</v>
+      </c>
+      <c r="AI10" s="6">
         <f t="shared" si="0"/>
-        <v>3370.1931009147875</v>
-      </c>
-      <c r="AF6" s="6">
+        <v>3434.4417465155457</v>
+      </c>
+      <c r="AJ10" s="6">
         <f t="shared" si="0"/>
-        <v>3471.2988939422312</v>
+        <v>3537.4749989110123</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
-      <c r="B7" s="1" t="s">
+    <row r="11" spans="1:36">
+      <c r="B11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18">
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17">
         <v>9</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F11" s="17">
         <v>9</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G11" s="17">
         <v>9</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H11" s="17">
         <v>11</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I11" s="17">
         <v>20</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J11" s="17">
         <v>9</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K11" s="17">
         <v>5</v>
       </c>
-      <c r="L7" s="18">
+      <c r="L11" s="17">
         <v>8</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M11" s="12">
         <v>6</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N11" s="17">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O11" s="17">
+        <f>K11*1.01</f>
+        <v>5.05</v>
+      </c>
+      <c r="P11" s="17">
+        <f t="shared" ref="P11:R11" si="2">L11*1.01</f>
+        <v>8.08</v>
+      </c>
+      <c r="Q11" s="17">
+        <f t="shared" si="2"/>
+        <v>6.0600000000000005</v>
+      </c>
+      <c r="R11" s="17">
+        <f t="shared" si="2"/>
+        <v>5.05</v>
+      </c>
+      <c r="Y11" s="17">
+        <f>SUM(G11:J11)</f>
+        <v>49</v>
+      </c>
+      <c r="Z11" s="17">
+        <v>24</v>
+      </c>
+      <c r="AA11" s="6">
+        <f>Z11*1.2</f>
+        <v>28.799999999999997</v>
+      </c>
+      <c r="AB11" s="6">
+        <f t="shared" ref="AB11:AJ11" si="3">AA11*1.2</f>
+        <v>34.559999999999995</v>
+      </c>
+      <c r="AC11" s="6">
+        <f t="shared" si="3"/>
+        <v>41.471999999999994</v>
+      </c>
+      <c r="AD11" s="6">
+        <f t="shared" si="3"/>
+        <v>49.76639999999999</v>
+      </c>
+      <c r="AE11" s="6">
+        <f t="shared" si="3"/>
+        <v>59.719679999999983</v>
+      </c>
+      <c r="AF11" s="6">
+        <f t="shared" si="3"/>
+        <v>71.663615999999976</v>
+      </c>
+      <c r="AG11" s="6">
+        <f t="shared" si="3"/>
+        <v>85.996339199999966</v>
+      </c>
+      <c r="AH11" s="6">
+        <f t="shared" si="3"/>
+        <v>103.19560703999996</v>
+      </c>
+      <c r="AI11" s="6">
+        <f t="shared" si="3"/>
+        <v>123.83472844799994</v>
+      </c>
+      <c r="AJ11" s="6">
+        <f t="shared" si="3"/>
+        <v>148.60167413759993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" s="2" customFormat="1">
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="14">
+        <f t="shared" ref="E12:N12" si="4">SUM(E9:E11)</f>
+        <v>1856</v>
+      </c>
+      <c r="F12" s="14">
+        <f t="shared" si="4"/>
+        <v>3062</v>
+      </c>
+      <c r="G12" s="14">
+        <f t="shared" si="4"/>
+        <v>1281</v>
+      </c>
+      <c r="H12" s="14">
+        <f t="shared" si="4"/>
+        <v>2203</v>
+      </c>
+      <c r="I12" s="14">
+        <f t="shared" si="4"/>
+        <v>2073</v>
+      </c>
+      <c r="J12" s="14">
+        <f t="shared" si="4"/>
+        <v>3108</v>
+      </c>
+      <c r="K12" s="14">
+        <f t="shared" si="4"/>
+        <v>1522</v>
+      </c>
+      <c r="L12" s="14">
+        <f t="shared" si="4"/>
+        <v>2028</v>
+      </c>
+      <c r="M12" s="14">
+        <f>SUM(M9:M11)</f>
+        <v>2307</v>
+      </c>
+      <c r="N12" s="14">
+        <f t="shared" si="4"/>
+        <v>3694</v>
+      </c>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="Y12" s="14">
+        <f>SUM(Y9:Y11)</f>
+        <v>8665</v>
+      </c>
+      <c r="Z12" s="14">
+        <f>SUM(Z9:Z11)</f>
+        <v>9551</v>
+      </c>
+      <c r="AA12" s="14">
+        <f t="shared" ref="AA12:AJ12" si="5">SUM(AA9:AA11)</f>
+        <v>10147.4</v>
+      </c>
+      <c r="AB12" s="14">
+        <f t="shared" si="5"/>
+        <v>10633.969000000001</v>
+      </c>
+      <c r="AC12" s="14">
+        <f t="shared" si="5"/>
+        <v>11013.122970000002</v>
+      </c>
+      <c r="AD12" s="14">
+        <f t="shared" si="5"/>
+        <v>11379.053241600002</v>
+      </c>
+      <c r="AE12" s="14">
+        <f t="shared" si="5"/>
+        <v>11728.885126848003</v>
+      </c>
+      <c r="AF12" s="14">
+        <f t="shared" si="5"/>
+        <v>12090.904026253444</v>
+      </c>
+      <c r="AG12" s="14">
+        <f t="shared" si="5"/>
+        <v>12465.813961761047</v>
+      </c>
+      <c r="AH12" s="14">
+        <f t="shared" si="5"/>
+        <v>12854.407758277879</v>
+      </c>
+      <c r="AI12" s="14">
+        <f t="shared" si="5"/>
+        <v>13257.583244223017</v>
+      </c>
+      <c r="AJ12" s="14">
+        <f t="shared" si="5"/>
+        <v>13676.362645385867</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36">
+      <c r="B13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="18">
+        <v>1473</v>
+      </c>
+      <c r="F13" s="18">
+        <v>2480</v>
+      </c>
+      <c r="G13" s="18">
+        <v>996</v>
+      </c>
+      <c r="H13" s="18">
+        <v>1749</v>
+      </c>
+      <c r="I13" s="18">
+        <v>1657</v>
+      </c>
+      <c r="J13" s="18">
+        <v>2487</v>
+      </c>
+      <c r="K13" s="18">
+        <v>1241</v>
+      </c>
+      <c r="L13" s="18">
+        <v>1617</v>
+      </c>
+      <c r="M13" s="6">
+        <v>1843</v>
+      </c>
+      <c r="N13" s="17">
+        <f t="shared" si="1"/>
+        <v>2939</v>
+      </c>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="Y13" s="17">
+        <f>SUM(G13:J13)</f>
+        <v>6889</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>7640</v>
+      </c>
+      <c r="AA13" s="6">
+        <f>AA12-AA14</f>
+        <v>8016.4459999999999</v>
+      </c>
+      <c r="AB13" s="6">
+        <f t="shared" ref="AB13:AJ13" si="6">AB12-AB14</f>
+        <v>8400.8355100000008</v>
+      </c>
+      <c r="AC13" s="6">
+        <f t="shared" si="6"/>
+        <v>8700.3671463000028</v>
+      </c>
+      <c r="AD13" s="6">
+        <f t="shared" si="6"/>
+        <v>8989.4520608640014</v>
+      </c>
+      <c r="AE13" s="6">
+        <f t="shared" si="6"/>
+        <v>9265.8192502099228</v>
+      </c>
+      <c r="AF13" s="6">
+        <f t="shared" si="6"/>
+        <v>9551.8141807402208</v>
+      </c>
+      <c r="AG13" s="6">
+        <f t="shared" si="6"/>
+        <v>9847.9930297912269</v>
+      </c>
+      <c r="AH13" s="6">
+        <f t="shared" si="6"/>
+        <v>10154.982129039525</v>
+      </c>
+      <c r="AI13" s="6">
+        <f t="shared" si="6"/>
+        <v>10473.490762936184</v>
+      </c>
+      <c r="AJ13" s="6">
+        <f t="shared" si="6"/>
+        <v>10804.326489854835</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1">
+      <c r="B14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" ref="E14:M14" si="7">E12-E13</f>
+        <v>383</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="7"/>
+        <v>582</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="7"/>
+        <v>285</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="7"/>
+        <v>454</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="7"/>
+        <v>416</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="7"/>
+        <v>621</v>
+      </c>
+      <c r="K14" s="14">
+        <f t="shared" si="7"/>
+        <v>281</v>
+      </c>
+      <c r="L14" s="14">
+        <f t="shared" si="7"/>
+        <v>411</v>
+      </c>
+      <c r="M14" s="14">
+        <f t="shared" si="7"/>
+        <v>464</v>
+      </c>
+      <c r="N14" s="16">
+        <f>N12*0.2</f>
+        <v>738.80000000000007</v>
+      </c>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="Y14" s="14">
+        <f>Y12-Y13</f>
+        <v>1776</v>
+      </c>
+      <c r="Z14" s="14">
+        <f>Z12-Z13</f>
+        <v>1911</v>
+      </c>
+      <c r="AA14" s="16">
+        <f>AA12*0.21</f>
+        <v>2130.9539999999997</v>
+      </c>
+      <c r="AB14" s="16">
+        <f t="shared" ref="AB14:AJ14" si="8">AB12*0.21</f>
+        <v>2233.1334900000002</v>
+      </c>
+      <c r="AC14" s="16">
+        <f t="shared" si="8"/>
+        <v>2312.7558237000003</v>
+      </c>
+      <c r="AD14" s="16">
+        <f t="shared" si="8"/>
+        <v>2389.6011807360005</v>
+      </c>
+      <c r="AE14" s="16">
+        <f t="shared" si="8"/>
+        <v>2463.0658766380807</v>
+      </c>
+      <c r="AF14" s="16">
+        <f t="shared" si="8"/>
+        <v>2539.0898455132233</v>
+      </c>
+      <c r="AG14" s="16">
+        <f t="shared" si="8"/>
+        <v>2617.8209319698199</v>
+      </c>
+      <c r="AH14" s="16">
+        <f t="shared" si="8"/>
+        <v>2699.4256292383543</v>
+      </c>
+      <c r="AI14" s="16">
+        <f t="shared" si="8"/>
+        <v>2784.0924812868334</v>
+      </c>
+      <c r="AJ14" s="16">
+        <f t="shared" si="8"/>
+        <v>2872.0361555310319</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36">
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="18">
+        <v>103</v>
+      </c>
+      <c r="F15" s="18">
+        <v>137</v>
+      </c>
+      <c r="G15" s="18">
+        <v>109</v>
+      </c>
+      <c r="H15" s="18">
+        <v>117</v>
+      </c>
+      <c r="I15" s="18">
+        <v>117</v>
+      </c>
+      <c r="J15" s="18">
+        <v>135</v>
+      </c>
+      <c r="K15" s="18">
+        <v>98</v>
+      </c>
+      <c r="L15" s="18">
+        <v>120</v>
+      </c>
+      <c r="M15" s="6">
+        <v>124</v>
+      </c>
+      <c r="N15" s="17">
+        <f t="shared" si="1"/>
+        <v>164</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="Y15" s="17">
+        <f t="shared" ref="Y15:Y19" si="9">SUM(G15:J15)</f>
+        <v>478</v>
+      </c>
+      <c r="Z15" s="17">
+        <v>506</v>
+      </c>
+      <c r="AA15" s="6">
+        <f>Z15*1.04</f>
+        <v>526.24</v>
+      </c>
+      <c r="AB15" s="6">
+        <f>AA15*1.03</f>
+        <v>542.02719999999999</v>
+      </c>
+      <c r="AC15" s="6">
+        <f>AB15*1.02</f>
+        <v>552.86774400000002</v>
+      </c>
+      <c r="AD15" s="6">
+        <f t="shared" ref="AD15:AJ15" si="10">AC15*1.01</f>
+        <v>558.39642144000004</v>
+      </c>
+      <c r="AE15" s="6">
+        <f t="shared" si="10"/>
+        <v>563.98038565440004</v>
+      </c>
+      <c r="AF15" s="6">
+        <f t="shared" si="10"/>
+        <v>569.62018951094399</v>
+      </c>
+      <c r="AG15" s="6">
+        <f t="shared" si="10"/>
+        <v>575.31639140605341</v>
+      </c>
+      <c r="AH15" s="6">
+        <f t="shared" si="10"/>
+        <v>581.06955532011398</v>
+      </c>
+      <c r="AI15" s="6">
+        <f t="shared" si="10"/>
+        <v>586.88025087331516</v>
+      </c>
+      <c r="AJ15" s="6">
+        <f t="shared" si="10"/>
+        <v>592.74905338204837</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="B16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="18">
+        <v>81</v>
+      </c>
+      <c r="F16" s="18">
+        <v>158</v>
+      </c>
+      <c r="G16" s="18">
+        <v>29</v>
+      </c>
+      <c r="H16" s="18">
+        <v>113</v>
+      </c>
+      <c r="I16" s="18">
+        <v>89</v>
+      </c>
+      <c r="J16" s="18">
+        <v>121</v>
+      </c>
+      <c r="K16" s="18">
+        <v>-3</v>
+      </c>
+      <c r="L16" s="18">
+        <v>76</v>
+      </c>
+      <c r="M16" s="6">
+        <v>103</v>
+      </c>
+      <c r="N16" s="17">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="Y16" s="17">
+        <f t="shared" si="9"/>
+        <v>352</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>271</v>
+      </c>
+      <c r="AA16" s="6">
+        <f>Z16*1.05</f>
+        <v>284.55</v>
+      </c>
+      <c r="AB16" s="6">
+        <f>AA16*1.03</f>
+        <v>293.0865</v>
+      </c>
+      <c r="AC16" s="6">
+        <f>AB16*1.02</f>
+        <v>298.94823000000002</v>
+      </c>
+      <c r="AD16" s="6">
+        <f t="shared" ref="AD16:AJ16" si="11">AC16*1.02</f>
+        <v>304.92719460000001</v>
+      </c>
+      <c r="AE16" s="6">
+        <f t="shared" si="11"/>
+        <v>311.02573849200002</v>
+      </c>
+      <c r="AF16" s="6">
+        <f t="shared" si="11"/>
+        <v>317.24625326184002</v>
+      </c>
+      <c r="AG16" s="6">
+        <f t="shared" si="11"/>
+        <v>323.59117832707682</v>
+      </c>
+      <c r="AH16" s="6">
+        <f t="shared" si="11"/>
+        <v>330.06300189361838</v>
+      </c>
+      <c r="AI16" s="6">
+        <f t="shared" si="11"/>
+        <v>336.66426193149073</v>
+      </c>
+      <c r="AJ16" s="6">
+        <f t="shared" si="11"/>
+        <v>343.39754717012056</v>
+      </c>
+    </row>
+    <row r="17" spans="2:143">
+      <c r="B17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="18">
+        <v>6</v>
+      </c>
+      <c r="F17" s="18">
+        <v>12</v>
+      </c>
+      <c r="G17" s="18">
+        <v>5</v>
+      </c>
+      <c r="H17" s="18">
+        <v>33</v>
+      </c>
+      <c r="I17" s="18">
+        <v>9</v>
+      </c>
+      <c r="J17" s="18">
+        <v>16</v>
+      </c>
+      <c r="K17" s="18">
+        <v>9</v>
+      </c>
+      <c r="L17" s="18">
         <v>10</v>
       </c>
-      <c r="U7" s="18">
-        <f>SUM(G7:J7)</f>
-        <v>49</v>
-      </c>
-      <c r="V7" s="18">
+      <c r="M17" s="6">
+        <v>10</v>
+      </c>
+      <c r="N17" s="17">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="W7" s="6">
-        <f>V7*1.2</f>
-        <v>34.799999999999997</v>
-      </c>
-      <c r="X7" s="6">
-        <f t="shared" ref="X7:AF7" si="2">W7*1.2</f>
-        <v>41.76</v>
-      </c>
-      <c r="Y7" s="6">
-        <f t="shared" si="2"/>
-        <v>50.111999999999995</v>
-      </c>
-      <c r="Z7" s="6">
-        <f t="shared" si="2"/>
-        <v>60.134399999999992</v>
-      </c>
-      <c r="AA7" s="6">
-        <f t="shared" si="2"/>
-        <v>72.161279999999991</v>
-      </c>
-      <c r="AB7" s="6">
-        <f t="shared" si="2"/>
-        <v>86.593535999999986</v>
-      </c>
-      <c r="AC7" s="6">
-        <f t="shared" si="2"/>
-        <v>103.91224319999998</v>
-      </c>
-      <c r="AD7" s="6">
-        <f t="shared" si="2"/>
-        <v>124.69469183999996</v>
-      </c>
-      <c r="AE7" s="6">
-        <f t="shared" si="2"/>
-        <v>149.63363020799994</v>
-      </c>
-      <c r="AF7" s="6">
-        <f t="shared" si="2"/>
-        <v>179.56035624959992</v>
+        <v>10</v>
+      </c>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="Y17" s="17">
+        <f t="shared" si="9"/>
+        <v>63</v>
+      </c>
+      <c r="Z17" s="17">
+        <v>39</v>
+      </c>
+      <c r="AA17" s="6">
+        <f>Z17*1.05</f>
+        <v>40.950000000000003</v>
+      </c>
+      <c r="AB17" s="6">
+        <f t="shared" ref="AB17:AJ17" si="12">AA17*1.05</f>
+        <v>42.997500000000002</v>
+      </c>
+      <c r="AC17" s="6">
+        <f t="shared" si="12"/>
+        <v>45.147375000000004</v>
+      </c>
+      <c r="AD17" s="6">
+        <f t="shared" si="12"/>
+        <v>47.404743750000009</v>
+      </c>
+      <c r="AE17" s="6">
+        <f t="shared" si="12"/>
+        <v>49.774980937500011</v>
+      </c>
+      <c r="AF17" s="6">
+        <f t="shared" si="12"/>
+        <v>52.263729984375011</v>
+      </c>
+      <c r="AG17" s="6">
+        <f t="shared" si="12"/>
+        <v>54.876916483593767</v>
+      </c>
+      <c r="AH17" s="6">
+        <f t="shared" si="12"/>
+        <v>57.620762307773461</v>
+      </c>
+      <c r="AI17" s="6">
+        <f t="shared" si="12"/>
+        <v>60.501800423162138</v>
+      </c>
+      <c r="AJ17" s="6">
+        <f t="shared" si="12"/>
+        <v>63.526890444320244</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="2" customFormat="1">
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="15">
-        <f t="shared" ref="E8:N8" si="3">SUM(E5:E7)</f>
-        <v>1856</v>
-      </c>
-      <c r="F8" s="15">
-        <f t="shared" si="3"/>
-        <v>3062</v>
-      </c>
-      <c r="G8" s="15">
-        <f t="shared" si="3"/>
-        <v>1281</v>
-      </c>
-      <c r="H8" s="15">
-        <f t="shared" si="3"/>
-        <v>2203</v>
-      </c>
-      <c r="I8" s="15">
-        <f t="shared" si="3"/>
-        <v>2073</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" si="3"/>
-        <v>3108</v>
-      </c>
-      <c r="K8" s="15">
-        <f t="shared" si="3"/>
-        <v>1522</v>
-      </c>
-      <c r="L8" s="15">
-        <f t="shared" si="3"/>
-        <v>2028</v>
-      </c>
-      <c r="M8" s="15">
-        <f>SUM(M5:M7)</f>
-        <v>2307</v>
-      </c>
-      <c r="N8" s="15">
-        <f t="shared" si="3"/>
-        <v>3686.88</v>
-      </c>
-      <c r="U8" s="15">
-        <f>SUM(U5:U7)</f>
-        <v>8665</v>
-      </c>
-      <c r="V8" s="15">
-        <f>SUM(V5:V7)</f>
-        <v>9543.880000000001</v>
-      </c>
-      <c r="W8" s="15">
-        <f t="shared" ref="W8:AF8" si="4">SUM(W5:W7)</f>
-        <v>10791.288</v>
-      </c>
-      <c r="X8" s="15">
-        <f t="shared" si="4"/>
-        <v>11551.202160000001</v>
-      </c>
-      <c r="Y8" s="15">
-        <f t="shared" si="4"/>
-        <v>12046.554174000001</v>
-      </c>
-      <c r="Z8" s="15">
-        <f t="shared" si="4"/>
-        <v>12444.423283200003</v>
-      </c>
-      <c r="AA8" s="15">
-        <f t="shared" si="4"/>
-        <v>12827.978829696003</v>
-      </c>
-      <c r="AB8" s="15">
-        <f t="shared" si="4"/>
-        <v>13225.085612186886</v>
-      </c>
-      <c r="AC8" s="15">
-        <f t="shared" si="4"/>
-        <v>13636.559081672491</v>
-      </c>
-      <c r="AD8" s="15">
-        <f t="shared" si="4"/>
-        <v>14063.320935466667</v>
-      </c>
-      <c r="AE8" s="15">
-        <f t="shared" si="4"/>
-        <v>14506.418661143465</v>
-      </c>
-      <c r="AF8" s="15">
-        <f t="shared" si="4"/>
-        <v>14967.04893811313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32">
-      <c r="B9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="19">
-        <v>1473</v>
-      </c>
-      <c r="F9" s="19">
-        <v>2480</v>
-      </c>
-      <c r="G9" s="19">
-        <v>996</v>
-      </c>
-      <c r="H9" s="19">
-        <v>1749</v>
-      </c>
-      <c r="I9" s="19">
-        <v>1657</v>
-      </c>
-      <c r="J9" s="19">
-        <v>2487</v>
-      </c>
-      <c r="K9" s="19">
-        <v>1241</v>
-      </c>
-      <c r="L9" s="19">
-        <v>1617</v>
-      </c>
-      <c r="M9" s="6">
-        <v>1843</v>
-      </c>
-      <c r="N9" s="6">
-        <f>N8-N10</f>
-        <v>2949.5039999999999</v>
-      </c>
-      <c r="U9" s="18">
-        <f>SUM(G9:J9)</f>
-        <v>6889</v>
-      </c>
-      <c r="V9" s="18">
-        <f>SUM(K9:N9)</f>
-        <v>7650.5039999999999</v>
-      </c>
-      <c r="W9" s="6">
-        <f>W8-W10</f>
-        <v>8525.1175199999998</v>
-      </c>
-      <c r="X9" s="6">
-        <f t="shared" ref="X9:AF9" si="5">X8-X10</f>
-        <v>9125.4497064000007</v>
-      </c>
-      <c r="Y9" s="6">
-        <f t="shared" si="5"/>
-        <v>9516.7777974600012</v>
-      </c>
-      <c r="Z9" s="6">
-        <f t="shared" si="5"/>
-        <v>9831.0943937280026</v>
-      </c>
-      <c r="AA9" s="6">
-        <f t="shared" si="5"/>
-        <v>10134.103275459842</v>
-      </c>
-      <c r="AB9" s="6">
-        <f t="shared" si="5"/>
-        <v>10447.817633627639</v>
-      </c>
-      <c r="AC9" s="6">
-        <f t="shared" si="5"/>
-        <v>10772.881674521268</v>
-      </c>
-      <c r="AD9" s="6">
-        <f t="shared" si="5"/>
-        <v>11110.023539018668</v>
-      </c>
-      <c r="AE9" s="6">
-        <f t="shared" si="5"/>
-        <v>11460.070742303338</v>
-      </c>
-      <c r="AF9" s="6">
-        <f t="shared" si="5"/>
-        <v>11823.968661109373</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" s="2" customFormat="1">
-      <c r="B10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="15">
-        <f t="shared" ref="E10:M10" si="6">E8-E9</f>
-        <v>383</v>
-      </c>
-      <c r="F10" s="15">
-        <f t="shared" si="6"/>
-        <v>582</v>
-      </c>
-      <c r="G10" s="15">
-        <f t="shared" si="6"/>
-        <v>285</v>
-      </c>
-      <c r="H10" s="15">
-        <f t="shared" si="6"/>
-        <v>454</v>
-      </c>
-      <c r="I10" s="15">
-        <f t="shared" si="6"/>
-        <v>416</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" si="6"/>
-        <v>621</v>
-      </c>
-      <c r="K10" s="15">
-        <f t="shared" si="6"/>
-        <v>281</v>
-      </c>
-      <c r="L10" s="15">
-        <f t="shared" si="6"/>
-        <v>411</v>
-      </c>
-      <c r="M10" s="15">
-        <f t="shared" si="6"/>
-        <v>464</v>
-      </c>
-      <c r="N10" s="17">
-        <f>N8*0.2</f>
-        <v>737.37600000000009</v>
-      </c>
-      <c r="U10" s="15">
-        <f>U8-U9</f>
-        <v>1776</v>
-      </c>
-      <c r="V10" s="15">
-        <f>V8-V9</f>
-        <v>1893.3760000000011</v>
-      </c>
-      <c r="W10" s="17">
-        <f>W8*0.21</f>
-        <v>2266.1704800000002</v>
-      </c>
-      <c r="X10" s="17">
-        <f t="shared" ref="X10:AF10" si="7">X8*0.21</f>
-        <v>2425.7524536000001</v>
-      </c>
-      <c r="Y10" s="17">
-        <f t="shared" si="7"/>
-        <v>2529.77637654</v>
-      </c>
-      <c r="Z10" s="17">
-        <f t="shared" si="7"/>
-        <v>2613.3288894720008</v>
-      </c>
-      <c r="AA10" s="17">
-        <f t="shared" si="7"/>
-        <v>2693.8755542361605</v>
-      </c>
-      <c r="AB10" s="17">
-        <f t="shared" si="7"/>
-        <v>2777.2679785592459</v>
-      </c>
-      <c r="AC10" s="17">
-        <f t="shared" si="7"/>
-        <v>2863.6774071512227</v>
-      </c>
-      <c r="AD10" s="17">
-        <f t="shared" si="7"/>
-        <v>2953.2973964479997</v>
-      </c>
-      <c r="AE10" s="17">
-        <f t="shared" si="7"/>
-        <v>3046.3479188401275</v>
-      </c>
-      <c r="AF10" s="17">
-        <f t="shared" si="7"/>
-        <v>3143.0802770037571</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32">
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="19">
-        <v>103</v>
-      </c>
-      <c r="F11" s="19">
-        <v>137</v>
-      </c>
-      <c r="G11" s="19">
-        <v>109</v>
-      </c>
-      <c r="H11" s="19">
-        <v>117</v>
-      </c>
-      <c r="I11" s="19">
-        <v>117</v>
-      </c>
-      <c r="J11" s="19">
-        <v>135</v>
-      </c>
-      <c r="K11" s="19">
-        <v>98</v>
-      </c>
-      <c r="L11" s="19">
-        <v>120</v>
-      </c>
-      <c r="M11" s="6">
-        <v>124</v>
-      </c>
-      <c r="N11" s="6">
-        <f>J11*1.03</f>
-        <v>139.05000000000001</v>
-      </c>
-      <c r="U11" s="18">
-        <f t="shared" ref="U11:U15" si="8">SUM(G11:J11)</f>
-        <v>478</v>
-      </c>
-      <c r="V11" s="18">
-        <f t="shared" ref="V11:V15" si="9">SUM(K11:N11)</f>
-        <v>481.05</v>
-      </c>
-      <c r="W11" s="6">
-        <f>V11*1.01</f>
-        <v>485.8605</v>
-      </c>
-      <c r="X11" s="6">
-        <f t="shared" ref="X11:Y11" si="10">W11*1.01</f>
-        <v>490.71910500000001</v>
-      </c>
-      <c r="Y11" s="6">
-        <f t="shared" si="10"/>
-        <v>495.62629605000001</v>
-      </c>
-      <c r="Z11" s="6">
-        <f t="shared" ref="Z11:AF11" si="11">Y11*1.01</f>
-        <v>500.58255901050001</v>
-      </c>
-      <c r="AA11" s="6">
-        <f t="shared" si="11"/>
-        <v>505.58838460060502</v>
-      </c>
-      <c r="AB11" s="6">
-        <f t="shared" si="11"/>
-        <v>510.64426844661108</v>
-      </c>
-      <c r="AC11" s="6">
-        <f t="shared" si="11"/>
-        <v>515.7507111310772</v>
-      </c>
-      <c r="AD11" s="6">
-        <f t="shared" si="11"/>
-        <v>520.90821824238799</v>
-      </c>
-      <c r="AE11" s="6">
-        <f t="shared" si="11"/>
-        <v>526.1173004248119</v>
-      </c>
-      <c r="AF11" s="6">
-        <f t="shared" si="11"/>
-        <v>531.37847342906002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32">
-      <c r="B12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="19">
-        <v>81</v>
-      </c>
-      <c r="F12" s="19">
-        <v>158</v>
-      </c>
-      <c r="G12" s="19">
-        <v>29</v>
-      </c>
-      <c r="H12" s="19">
-        <v>113</v>
-      </c>
-      <c r="I12" s="19">
-        <v>89</v>
-      </c>
-      <c r="J12" s="19">
-        <v>121</v>
-      </c>
-      <c r="K12" s="19">
+    <row r="18" spans="2:143">
+      <c r="B18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="18">
         <v>-3</v>
       </c>
-      <c r="L12" s="19">
-        <v>76</v>
-      </c>
-      <c r="M12" s="6">
-        <v>103</v>
-      </c>
-      <c r="N12" s="6">
-        <f>J12*1.02</f>
-        <v>123.42</v>
-      </c>
-      <c r="U12" s="18">
-        <f t="shared" si="8"/>
-        <v>352</v>
-      </c>
-      <c r="V12" s="18">
-        <f t="shared" si="9"/>
-        <v>299.42</v>
-      </c>
-      <c r="W12" s="6">
-        <f>V12*1.05</f>
-        <v>314.39100000000002</v>
-      </c>
-      <c r="X12" s="6">
-        <f>W12*1.03</f>
-        <v>323.82273000000004</v>
-      </c>
-      <c r="Y12" s="6">
-        <f>X12*1.02</f>
-        <v>330.29918460000005</v>
-      </c>
-      <c r="Z12" s="6">
-        <f t="shared" ref="Z12:AF12" si="12">Y12*1.02</f>
-        <v>336.90516829200004</v>
-      </c>
-      <c r="AA12" s="6">
-        <f t="shared" si="12"/>
-        <v>343.64327165784005</v>
-      </c>
-      <c r="AB12" s="6">
-        <f t="shared" si="12"/>
-        <v>350.51613709099684</v>
-      </c>
-      <c r="AC12" s="6">
-        <f t="shared" si="12"/>
-        <v>357.52645983281678</v>
-      </c>
-      <c r="AD12" s="6">
-        <f t="shared" si="12"/>
-        <v>364.67698902947313</v>
-      </c>
-      <c r="AE12" s="6">
-        <f t="shared" si="12"/>
-        <v>371.9705288100626</v>
-      </c>
-      <c r="AF12" s="6">
-        <f t="shared" si="12"/>
-        <v>379.40993938626389</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32">
-      <c r="B13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="19">
-        <v>6</v>
-      </c>
-      <c r="F13" s="19">
-        <v>12</v>
-      </c>
-      <c r="G13" s="19">
-        <v>5</v>
-      </c>
-      <c r="H13" s="19">
-        <v>33</v>
-      </c>
-      <c r="I13" s="19">
-        <v>9</v>
-      </c>
-      <c r="J13" s="19">
-        <v>16</v>
-      </c>
-      <c r="K13" s="19">
-        <v>9</v>
-      </c>
-      <c r="L13" s="19">
-        <v>10</v>
-      </c>
-      <c r="M13" s="6">
-        <v>10</v>
-      </c>
-      <c r="N13" s="6">
-        <v>15</v>
-      </c>
-      <c r="U13" s="18">
-        <f t="shared" si="8"/>
-        <v>63</v>
-      </c>
-      <c r="V13" s="18">
-        <f t="shared" si="9"/>
-        <v>44</v>
-      </c>
-      <c r="W13" s="6">
-        <f>V13*1.05</f>
-        <v>46.2</v>
-      </c>
-      <c r="X13" s="6">
-        <f t="shared" ref="X13:AF13" si="13">W13*1.05</f>
-        <v>48.510000000000005</v>
-      </c>
-      <c r="Y13" s="6">
-        <f t="shared" si="13"/>
-        <v>50.935500000000005</v>
-      </c>
-      <c r="Z13" s="6">
-        <f t="shared" si="13"/>
-        <v>53.482275000000008</v>
-      </c>
-      <c r="AA13" s="6">
-        <f t="shared" si="13"/>
-        <v>56.156388750000012</v>
-      </c>
-      <c r="AB13" s="6">
-        <f t="shared" si="13"/>
-        <v>58.964208187500013</v>
-      </c>
-      <c r="AC13" s="6">
-        <f t="shared" si="13"/>
-        <v>61.912418596875014</v>
-      </c>
-      <c r="AD13" s="6">
-        <f t="shared" si="13"/>
-        <v>65.008039526718761</v>
-      </c>
-      <c r="AE13" s="6">
-        <f t="shared" si="13"/>
-        <v>68.258441503054698</v>
-      </c>
-      <c r="AF13" s="6">
-        <f t="shared" si="13"/>
-        <v>71.671363578207433</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32">
-      <c r="B14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="19">
-        <v>-3</v>
-      </c>
-      <c r="F14" s="19">
+      <c r="F18" s="18">
         <f>1-19</f>
         <v>-18</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G18" s="18">
         <v>-1</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H18" s="18">
         <v>0</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I18" s="18">
         <v>0</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J18" s="18">
         <v>4</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K18" s="18">
         <v>0</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L18" s="18">
         <v>0</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M18" s="6">
         <v>0</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N18" s="17">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="Y18" s="17">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="Z18" s="17">
+        <v>-13</v>
+      </c>
+      <c r="AA18" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="18">
-        <f t="shared" si="8"/>
+      <c r="AB18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:143">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="18">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="18">
+        <v>82</v>
+      </c>
+      <c r="G19" s="18">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="18">
+        <v>0</v>
+      </c>
+      <c r="I19" s="18">
+        <v>0</v>
+      </c>
+      <c r="J19" s="18">
         <v>3</v>
       </c>
-      <c r="V14" s="18">
+      <c r="K19" s="18">
+        <v>0</v>
+      </c>
+      <c r="L19" s="18">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0</v>
+      </c>
+      <c r="N19" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="Y19" s="17">
         <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="Z19" s="17">
+        <f>1-1</f>
         <v>0</v>
       </c>
-      <c r="W14" s="6">
+      <c r="AA19" s="6">
         <v>0</v>
       </c>
-      <c r="X14" s="6">
+      <c r="AB19" s="6">
         <v>0</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="AC19" s="6">
         <v>0</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="AD19" s="6">
         <v>0</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AE19" s="6">
         <v>0</v>
       </c>
-      <c r="AB14" s="6">
+      <c r="AF19" s="6">
         <v>0</v>
       </c>
-      <c r="AC14" s="6">
+      <c r="AG19" s="6">
         <v>0</v>
       </c>
-      <c r="AD14" s="6">
+      <c r="AH19" s="6">
         <v>0</v>
       </c>
-      <c r="AE14" s="6">
+      <c r="AI19" s="6">
         <v>0</v>
       </c>
-      <c r="AF14" s="6">
+      <c r="AJ19" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
-      <c r="B15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="19">
-        <v>-1</v>
-      </c>
-      <c r="F15" s="19">
-        <v>82</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-1</v>
-      </c>
-      <c r="H15" s="19">
-        <v>0</v>
-      </c>
-      <c r="I15" s="19">
-        <v>0</v>
-      </c>
-      <c r="J15" s="19">
-        <v>3</v>
-      </c>
-      <c r="K15" s="19">
-        <v>0</v>
-      </c>
-      <c r="L15" s="19">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="18">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="V15" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="6">
-        <v>0</v>
+    <row r="20" spans="2:143">
+      <c r="B20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="18">
+        <f t="shared" ref="E20:N20" si="13">SUM(E15:E19)</f>
+        <v>186</v>
+      </c>
+      <c r="F20" s="18">
+        <f t="shared" si="13"/>
+        <v>371</v>
+      </c>
+      <c r="G20" s="18">
+        <f t="shared" si="13"/>
+        <v>141</v>
+      </c>
+      <c r="H20" s="18">
+        <f t="shared" si="13"/>
+        <v>263</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="13"/>
+        <v>215</v>
+      </c>
+      <c r="J20" s="18">
+        <f t="shared" si="13"/>
+        <v>279</v>
+      </c>
+      <c r="K20" s="18">
+        <f t="shared" si="13"/>
+        <v>104</v>
+      </c>
+      <c r="L20" s="18">
+        <f t="shared" si="13"/>
+        <v>206</v>
+      </c>
+      <c r="M20" s="18">
+        <f t="shared" si="13"/>
+        <v>237</v>
+      </c>
+      <c r="N20" s="18">
+        <f t="shared" si="13"/>
+        <v>256</v>
+      </c>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="Y20" s="18">
+        <f>SUM(Y15:Y19)</f>
+        <v>898</v>
+      </c>
+      <c r="Z20" s="18">
+        <f>SUM(Z15:Z19)</f>
+        <v>803</v>
+      </c>
+      <c r="AA20" s="18">
+        <f>SUM(AA15:AA19)</f>
+        <v>851.74</v>
+      </c>
+      <c r="AB20" s="18">
+        <f t="shared" ref="AB20:AJ20" si="14">SUM(AB15:AB19)</f>
+        <v>878.11120000000005</v>
+      </c>
+      <c r="AC20" s="18">
+        <f t="shared" si="14"/>
+        <v>896.96334900000011</v>
+      </c>
+      <c r="AD20" s="18">
+        <f t="shared" si="14"/>
+        <v>910.72835979000001</v>
+      </c>
+      <c r="AE20" s="18">
+        <f t="shared" si="14"/>
+        <v>924.7811050839</v>
+      </c>
+      <c r="AF20" s="18">
+        <f t="shared" si="14"/>
+        <v>939.13017275715902</v>
+      </c>
+      <c r="AG20" s="18">
+        <f t="shared" si="14"/>
+        <v>953.78448621672396</v>
+      </c>
+      <c r="AH20" s="18">
+        <f t="shared" si="14"/>
+        <v>968.75331952150577</v>
+      </c>
+      <c r="AI20" s="18">
+        <f t="shared" si="14"/>
+        <v>984.04631322796808</v>
+      </c>
+      <c r="AJ20" s="18">
+        <f t="shared" si="14"/>
+        <v>999.67349099648914</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
-      <c r="B16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="19">
-        <f t="shared" ref="E16:N16" si="14">SUM(E11:E15)</f>
-        <v>186</v>
-      </c>
-      <c r="F16" s="19">
-        <f t="shared" si="14"/>
-        <v>371</v>
-      </c>
-      <c r="G16" s="19">
-        <f t="shared" si="14"/>
-        <v>141</v>
-      </c>
-      <c r="H16" s="19">
-        <f t="shared" si="14"/>
-        <v>263</v>
-      </c>
-      <c r="I16" s="19">
-        <f t="shared" si="14"/>
-        <v>215</v>
-      </c>
-      <c r="J16" s="19">
-        <f t="shared" si="14"/>
-        <v>279</v>
-      </c>
-      <c r="K16" s="19">
-        <f t="shared" si="14"/>
-        <v>104</v>
-      </c>
-      <c r="L16" s="19">
-        <f t="shared" si="14"/>
-        <v>206</v>
-      </c>
-      <c r="M16" s="19">
-        <f t="shared" si="14"/>
-        <v>237</v>
-      </c>
-      <c r="N16" s="19">
-        <f t="shared" si="14"/>
-        <v>277.47000000000003</v>
-      </c>
-      <c r="U16" s="19">
-        <f>SUM(U11:U15)</f>
-        <v>898</v>
-      </c>
-      <c r="V16" s="19">
-        <f>SUM(V11:V15)</f>
-        <v>824.47</v>
-      </c>
-      <c r="W16" s="19">
-        <f>SUM(W11:W15)</f>
-        <v>846.45150000000012</v>
-      </c>
-      <c r="X16" s="19">
-        <f t="shared" ref="X16:AF16" si="15">SUM(X11:X15)</f>
-        <v>863.05183499999998</v>
-      </c>
-      <c r="Y16" s="19">
+    <row r="21" spans="2:143" s="2" customFormat="1">
+      <c r="B21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="14">
+        <f t="shared" ref="E21:N21" si="15">E14-E20</f>
+        <v>197</v>
+      </c>
+      <c r="F21" s="14">
         <f t="shared" si="15"/>
-        <v>876.8609806500001</v>
-      </c>
-      <c r="Z16" s="19">
+        <v>211</v>
+      </c>
+      <c r="G21" s="14">
         <f t="shared" si="15"/>
-        <v>890.97000230250001</v>
-      </c>
-      <c r="AA16" s="19">
+        <v>144</v>
+      </c>
+      <c r="H21" s="14">
         <f t="shared" si="15"/>
-        <v>905.38804500844515</v>
-      </c>
-      <c r="AB16" s="19">
+        <v>191</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="15"/>
-        <v>920.12461372510791</v>
-      </c>
-      <c r="AC16" s="19">
+        <v>201</v>
+      </c>
+      <c r="J21" s="14">
         <f t="shared" si="15"/>
-        <v>935.18958956076892</v>
-      </c>
-      <c r="AD16" s="19">
+        <v>342</v>
+      </c>
+      <c r="K21" s="14">
         <f t="shared" si="15"/>
-        <v>950.59324679857991</v>
-      </c>
-      <c r="AE16" s="19">
+        <v>177</v>
+      </c>
+      <c r="L21" s="14">
         <f t="shared" si="15"/>
-        <v>966.34627073792922</v>
-      </c>
-      <c r="AF16" s="19">
+        <v>205</v>
+      </c>
+      <c r="M21" s="14">
         <f t="shared" si="15"/>
-        <v>982.45977639353134</v>
+        <v>227</v>
+      </c>
+      <c r="N21" s="14">
+        <f t="shared" si="15"/>
+        <v>482.80000000000007</v>
+      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="Y21" s="14">
+        <f>Y14-Y20</f>
+        <v>878</v>
+      </c>
+      <c r="Z21" s="14">
+        <f>Z14-Z20</f>
+        <v>1108</v>
+      </c>
+      <c r="AA21" s="14">
+        <f>AA14-AA20</f>
+        <v>1279.2139999999997</v>
+      </c>
+      <c r="AB21" s="14">
+        <f t="shared" ref="AB21:AJ21" si="16">AB14-AB20</f>
+        <v>1355.0222900000001</v>
+      </c>
+      <c r="AC21" s="14">
+        <f t="shared" si="16"/>
+        <v>1415.7924747000002</v>
+      </c>
+      <c r="AD21" s="14">
+        <f t="shared" si="16"/>
+        <v>1478.8728209460005</v>
+      </c>
+      <c r="AE21" s="14">
+        <f t="shared" si="16"/>
+        <v>1538.2847715541807</v>
+      </c>
+      <c r="AF21" s="14">
+        <f t="shared" si="16"/>
+        <v>1599.9596727560643</v>
+      </c>
+      <c r="AG21" s="14">
+        <f t="shared" si="16"/>
+        <v>1664.0364457530959</v>
+      </c>
+      <c r="AH21" s="14">
+        <f t="shared" si="16"/>
+        <v>1730.6723097168485</v>
+      </c>
+      <c r="AI21" s="14">
+        <f t="shared" si="16"/>
+        <v>1800.0461680588653</v>
+      </c>
+      <c r="AJ21" s="14">
+        <f t="shared" si="16"/>
+        <v>1872.3626645345428</v>
       </c>
     </row>
-    <row r="17" spans="2:139" s="2" customFormat="1">
-      <c r="B17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="15">
-        <f t="shared" ref="E17:N17" si="16">E10-E16</f>
-        <v>197</v>
-      </c>
-      <c r="F17" s="15">
-        <f t="shared" si="16"/>
-        <v>211</v>
-      </c>
-      <c r="G17" s="15">
-        <f t="shared" si="16"/>
+    <row r="22" spans="2:143">
+      <c r="B22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="18">
+        <v>240</v>
+      </c>
+      <c r="F22" s="18">
+        <v>159</v>
+      </c>
+      <c r="G22" s="18">
+        <v>136</v>
+      </c>
+      <c r="H22" s="18">
+        <v>271</v>
+      </c>
+      <c r="I22" s="18">
+        <v>138</v>
+      </c>
+      <c r="J22" s="18">
+        <v>297</v>
+      </c>
+      <c r="K22" s="18">
         <v>144</v>
       </c>
-      <c r="H17" s="15">
-        <f t="shared" si="16"/>
-        <v>191</v>
-      </c>
-      <c r="I17" s="15">
-        <f t="shared" si="16"/>
-        <v>201</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" si="16"/>
-        <v>342</v>
-      </c>
-      <c r="K17" s="15">
-        <f t="shared" si="16"/>
-        <v>177</v>
-      </c>
-      <c r="L17" s="15">
-        <f t="shared" si="16"/>
-        <v>205</v>
-      </c>
-      <c r="M17" s="15">
-        <f t="shared" si="16"/>
-        <v>227</v>
-      </c>
-      <c r="N17" s="15">
-        <f t="shared" si="16"/>
-        <v>459.90600000000006</v>
-      </c>
-      <c r="U17" s="15">
-        <f>U10-U16</f>
-        <v>878</v>
-      </c>
-      <c r="V17" s="15">
-        <f>V10-V16</f>
-        <v>1068.9060000000011</v>
-      </c>
-      <c r="W17" s="15">
-        <f>W10-W16</f>
-        <v>1419.7189800000001</v>
-      </c>
-      <c r="X17" s="15">
-        <f t="shared" ref="X17:AF17" si="17">X10-X16</f>
-        <v>1562.7006186000001</v>
-      </c>
-      <c r="Y17" s="15">
+      <c r="L22" s="18">
+        <v>166</v>
+      </c>
+      <c r="M22" s="6">
+        <v>159</v>
+      </c>
+      <c r="N22" s="17">
+        <f t="shared" ref="N22:N23" si="17">Z22-M22-L22-K22</f>
+        <v>95</v>
+      </c>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="Y22" s="17">
+        <f t="shared" ref="Y22:Y23" si="18">SUM(G22:J22)</f>
+        <v>842</v>
+      </c>
+      <c r="Z22" s="17">
+        <v>564</v>
+      </c>
+      <c r="AA22" s="6">
+        <f>Z22*1.03</f>
+        <v>580.91999999999996</v>
+      </c>
+      <c r="AB22" s="6">
+        <f t="shared" ref="AB22:AJ22" si="19">AA22*1.03</f>
+        <v>598.34759999999994</v>
+      </c>
+      <c r="AC22" s="6">
+        <f t="shared" si="19"/>
+        <v>616.29802799999993</v>
+      </c>
+      <c r="AD22" s="6">
+        <f t="shared" si="19"/>
+        <v>634.78696883999999</v>
+      </c>
+      <c r="AE22" s="6">
+        <f t="shared" si="19"/>
+        <v>653.83057790520002</v>
+      </c>
+      <c r="AF22" s="6">
+        <f t="shared" si="19"/>
+        <v>673.44549524235606</v>
+      </c>
+      <c r="AG22" s="6">
+        <f t="shared" si="19"/>
+        <v>693.64886009962675</v>
+      </c>
+      <c r="AH22" s="6">
+        <f t="shared" si="19"/>
+        <v>714.45832590261557</v>
+      </c>
+      <c r="AI22" s="6">
+        <f t="shared" si="19"/>
+        <v>735.89207567969402</v>
+      </c>
+      <c r="AJ22" s="6">
+        <f t="shared" si="19"/>
+        <v>757.96883795008489</v>
+      </c>
+    </row>
+    <row r="23" spans="2:143">
+      <c r="B23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="18">
+        <v>-4</v>
+      </c>
+      <c r="F23" s="18">
+        <v>-170</v>
+      </c>
+      <c r="G23" s="18">
+        <v>-86</v>
+      </c>
+      <c r="H23" s="18">
+        <v>-77</v>
+      </c>
+      <c r="I23" s="18">
+        <v>-51</v>
+      </c>
+      <c r="J23" s="18">
+        <v>-6</v>
+      </c>
+      <c r="K23" s="18">
+        <v>-12</v>
+      </c>
+      <c r="L23" s="18">
+        <v>-134</v>
+      </c>
+      <c r="M23" s="6">
+        <v>-6</v>
+      </c>
+      <c r="N23" s="17">
         <f t="shared" si="17"/>
-        <v>1652.9153958899999</v>
-      </c>
-      <c r="Z17" s="15">
-        <f t="shared" si="17"/>
-        <v>1722.3588871695008</v>
-      </c>
-      <c r="AA17" s="15">
-        <f t="shared" si="17"/>
-        <v>1788.4875092277152</v>
-      </c>
-      <c r="AB17" s="15">
-        <f t="shared" si="17"/>
-        <v>1857.1433648341381</v>
-      </c>
-      <c r="AC17" s="15">
-        <f t="shared" si="17"/>
-        <v>1928.4878175904537</v>
-      </c>
-      <c r="AD17" s="15">
-        <f t="shared" si="17"/>
-        <v>2002.7041496494198</v>
-      </c>
-      <c r="AE17" s="15">
-        <f t="shared" si="17"/>
-        <v>2080.0016481021985</v>
-      </c>
-      <c r="AF17" s="15">
-        <f t="shared" si="17"/>
-        <v>2160.6205006102259</v>
-      </c>
-    </row>
-    <row r="18" spans="2:139">
-      <c r="B18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="19">
-        <v>240</v>
-      </c>
-      <c r="F18" s="19">
-        <v>159</v>
-      </c>
-      <c r="G18" s="19">
-        <v>136</v>
-      </c>
-      <c r="H18" s="19">
-        <v>271</v>
-      </c>
-      <c r="I18" s="19">
-        <v>138</v>
-      </c>
-      <c r="J18" s="19">
-        <v>297</v>
-      </c>
-      <c r="K18" s="19">
-        <v>144</v>
-      </c>
-      <c r="L18" s="19">
-        <v>166</v>
-      </c>
-      <c r="M18" s="6">
-        <v>159</v>
-      </c>
-      <c r="N18" s="6">
-        <f>J18*1.03</f>
-        <v>305.91000000000003</v>
-      </c>
-      <c r="U18" s="18">
-        <f t="shared" ref="U18:U19" si="18">SUM(G18:J18)</f>
-        <v>842</v>
-      </c>
-      <c r="V18" s="18">
-        <f t="shared" ref="V18:V19" si="19">SUM(K18:N18)</f>
-        <v>774.91000000000008</v>
-      </c>
-      <c r="W18" s="6">
-        <f>V18*1.03</f>
-        <v>798.15730000000008</v>
-      </c>
-      <c r="X18" s="6">
-        <f t="shared" ref="X18:AF18" si="20">W18*1.03</f>
-        <v>822.10201900000015</v>
-      </c>
-      <c r="Y18" s="6">
-        <f t="shared" si="20"/>
-        <v>846.76507957000013</v>
-      </c>
-      <c r="Z18" s="6">
-        <f t="shared" si="20"/>
-        <v>872.1680319571002</v>
-      </c>
-      <c r="AA18" s="6">
-        <f t="shared" si="20"/>
-        <v>898.3330729158132</v>
-      </c>
-      <c r="AB18" s="6">
-        <f t="shared" si="20"/>
-        <v>925.28306510328764</v>
-      </c>
-      <c r="AC18" s="6">
-        <f t="shared" si="20"/>
-        <v>953.0415570563863</v>
-      </c>
-      <c r="AD18" s="6">
-        <f t="shared" si="20"/>
-        <v>981.63280376807791</v>
-      </c>
-      <c r="AE18" s="6">
-        <f t="shared" si="20"/>
-        <v>1011.0817878811202</v>
-      </c>
-      <c r="AF18" s="6">
-        <f t="shared" si="20"/>
-        <v>1041.4142415175538</v>
-      </c>
-    </row>
-    <row r="19" spans="2:139">
-      <c r="B19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="19">
-        <v>-4</v>
-      </c>
-      <c r="F19" s="19">
-        <v>-170</v>
-      </c>
-      <c r="G19" s="19">
-        <v>-86</v>
-      </c>
-      <c r="H19" s="19">
-        <v>-77</v>
-      </c>
-      <c r="I19" s="19">
-        <v>-51</v>
-      </c>
-      <c r="J19" s="19">
-        <v>-6</v>
-      </c>
-      <c r="K19" s="19">
-        <v>-12</v>
-      </c>
-      <c r="L19" s="19">
-        <v>-134</v>
-      </c>
-      <c r="M19" s="6">
-        <v>-6</v>
-      </c>
-      <c r="N19" s="6">
-        <f t="shared" ref="M19:N19" si="21">J19*1.03</f>
-        <v>-6.18</v>
-      </c>
-      <c r="U19" s="18">
+        <v>-139</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="Y23" s="17">
         <f t="shared" si="18"/>
         <v>-220</v>
       </c>
-      <c r="V19" s="18">
-        <f t="shared" si="19"/>
-        <v>-158.18</v>
-      </c>
-      <c r="W19" s="6">
-        <f>V19*1.03</f>
-        <v>-162.92540000000002</v>
-      </c>
-      <c r="X19" s="6">
-        <f t="shared" ref="X19:AF19" si="22">W19*1.03</f>
-        <v>-167.81316200000003</v>
-      </c>
-      <c r="Y19" s="6">
+      <c r="Z23" s="17">
+        <v>-291</v>
+      </c>
+      <c r="AA23" s="6">
+        <f>Z23*1.03</f>
+        <v>-299.73</v>
+      </c>
+      <c r="AB23" s="6">
+        <f t="shared" ref="AB23:AJ23" si="20">AA23*1.03</f>
+        <v>-308.72190000000001</v>
+      </c>
+      <c r="AC23" s="6">
+        <f t="shared" si="20"/>
+        <v>-317.98355700000002</v>
+      </c>
+      <c r="AD23" s="6">
+        <f t="shared" si="20"/>
+        <v>-327.52306371000003</v>
+      </c>
+      <c r="AE23" s="6">
+        <f t="shared" si="20"/>
+        <v>-337.34875562130003</v>
+      </c>
+      <c r="AF23" s="6">
+        <f t="shared" si="20"/>
+        <v>-347.46921828993902</v>
+      </c>
+      <c r="AG23" s="6">
+        <f t="shared" si="20"/>
+        <v>-357.89329483863719</v>
+      </c>
+      <c r="AH23" s="6">
+        <f t="shared" si="20"/>
+        <v>-368.6300936837963</v>
+      </c>
+      <c r="AI23" s="6">
+        <f t="shared" si="20"/>
+        <v>-379.68899649431017</v>
+      </c>
+      <c r="AJ23" s="6">
+        <f t="shared" si="20"/>
+        <v>-391.0796663891395</v>
+      </c>
+    </row>
+    <row r="24" spans="2:143" s="2" customFormat="1">
+      <c r="B24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="14">
+        <f t="shared" ref="E24:N24" si="21">E21-E22-E23</f>
+        <v>-39</v>
+      </c>
+      <c r="F24" s="14">
+        <f t="shared" si="21"/>
+        <v>222</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" si="21"/>
+        <v>94</v>
+      </c>
+      <c r="H24" s="14">
+        <f t="shared" si="21"/>
+        <v>-3</v>
+      </c>
+      <c r="I24" s="14">
+        <f t="shared" si="21"/>
+        <v>114</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" si="21"/>
+        <v>51</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" si="21"/>
+        <v>45</v>
+      </c>
+      <c r="L24" s="14">
+        <f t="shared" si="21"/>
+        <v>173</v>
+      </c>
+      <c r="M24" s="14">
+        <f t="shared" si="21"/>
+        <v>74</v>
+      </c>
+      <c r="N24" s="14">
+        <f t="shared" si="21"/>
+        <v>526.80000000000007</v>
+      </c>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="Y24" s="14">
+        <f>Y21-Y22-Y23</f>
+        <v>256</v>
+      </c>
+      <c r="Z24" s="14">
+        <f>Z21-Z22-Z23</f>
+        <v>835</v>
+      </c>
+      <c r="AA24" s="14">
+        <f>AA21-AA22-AA23</f>
+        <v>998.02399999999977</v>
+      </c>
+      <c r="AB24" s="14">
+        <f t="shared" ref="AB24:AJ24" si="22">AB21-AB22-AB23</f>
+        <v>1065.3965900000003</v>
+      </c>
+      <c r="AC24" s="14">
         <f t="shared" si="22"/>
-        <v>-172.84755686000003</v>
-      </c>
-      <c r="Z19" s="6">
+        <v>1117.4780037000003</v>
+      </c>
+      <c r="AD24" s="14">
         <f t="shared" si="22"/>
-        <v>-178.03298356580004</v>
-      </c>
-      <c r="AA19" s="6">
+        <v>1171.6089158160005</v>
+      </c>
+      <c r="AE24" s="14">
         <f t="shared" si="22"/>
-        <v>-183.37397307277405</v>
-      </c>
-      <c r="AB19" s="6">
+        <v>1221.8029492702808</v>
+      </c>
+      <c r="AF24" s="14">
         <f t="shared" si="22"/>
-        <v>-188.87519226495726</v>
-      </c>
-      <c r="AC19" s="6">
+        <v>1273.9833958036472</v>
+      </c>
+      <c r="AG24" s="14">
         <f t="shared" si="22"/>
-        <v>-194.54144803290598</v>
-      </c>
-      <c r="AD19" s="6">
+        <v>1328.2808804921065</v>
+      </c>
+      <c r="AH24" s="14">
         <f t="shared" si="22"/>
-        <v>-200.37769147389315</v>
-      </c>
-      <c r="AE19" s="6">
+        <v>1384.8440774980293</v>
+      </c>
+      <c r="AI24" s="14">
         <f t="shared" si="22"/>
-        <v>-206.38902221810994</v>
-      </c>
-      <c r="AF19" s="6">
+        <v>1443.8430888734815</v>
+      </c>
+      <c r="AJ24" s="14">
         <f t="shared" si="22"/>
-        <v>-212.58069288465325</v>
+        <v>1505.4734929735973</v>
       </c>
     </row>
-    <row r="20" spans="2:139" s="2" customFormat="1">
-      <c r="B20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="15">
-        <f t="shared" ref="E20:N20" si="23">E17-E18-E19</f>
-        <v>-39</v>
-      </c>
-      <c r="F20" s="15">
+    <row r="25" spans="2:143">
+      <c r="B25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="18">
+        <v>-2</v>
+      </c>
+      <c r="F25" s="18">
+        <v>7</v>
+      </c>
+      <c r="G25" s="18">
+        <v>-16</v>
+      </c>
+      <c r="H25" s="18">
+        <v>-22</v>
+      </c>
+      <c r="I25" s="18">
+        <v>-3</v>
+      </c>
+      <c r="J25" s="18">
+        <v>-73</v>
+      </c>
+      <c r="K25" s="18">
+        <v>1</v>
+      </c>
+      <c r="L25" s="18">
+        <v>-20</v>
+      </c>
+      <c r="M25" s="6">
+        <v>-11</v>
+      </c>
+      <c r="N25" s="17">
+        <f t="shared" ref="N25:N26" si="23">Z25-M25-L25-K25</f>
+        <v>-110</v>
+      </c>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="Y25" s="17">
+        <f t="shared" ref="Y25:Y26" si="24">SUM(G25:J25)</f>
+        <v>-114</v>
+      </c>
+      <c r="Z25" s="17">
+        <v>-140</v>
+      </c>
+      <c r="AA25" s="6">
+        <f>AA24*0.15</f>
+        <v>149.70359999999997</v>
+      </c>
+      <c r="AB25" s="6">
+        <f t="shared" ref="AB25:AJ25" si="25">AB24*0.15</f>
+        <v>159.80948850000004</v>
+      </c>
+      <c r="AC25" s="6">
+        <f t="shared" si="25"/>
+        <v>167.62170055500005</v>
+      </c>
+      <c r="AD25" s="6">
+        <f t="shared" si="25"/>
+        <v>175.74133737240007</v>
+      </c>
+      <c r="AE25" s="6">
+        <f t="shared" si="25"/>
+        <v>183.27044239054212</v>
+      </c>
+      <c r="AF25" s="6">
+        <f t="shared" si="25"/>
+        <v>191.09750937054707</v>
+      </c>
+      <c r="AG25" s="6">
+        <f t="shared" si="25"/>
+        <v>199.24213207381595</v>
+      </c>
+      <c r="AH25" s="6">
+        <f t="shared" si="25"/>
+        <v>207.72661162470439</v>
+      </c>
+      <c r="AI25" s="6">
+        <f t="shared" si="25"/>
+        <v>216.57646333102221</v>
+      </c>
+      <c r="AJ25" s="6">
+        <f t="shared" si="25"/>
+        <v>225.82102394603959</v>
+      </c>
+    </row>
+    <row r="26" spans="2:143">
+      <c r="B26" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="18">
+        <v>0</v>
+      </c>
+      <c r="F26" s="18">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18">
+        <v>0</v>
+      </c>
+      <c r="H26" s="18">
+        <v>0</v>
+      </c>
+      <c r="I26" s="18">
+        <v>0</v>
+      </c>
+      <c r="J26" s="18">
+        <v>0</v>
+      </c>
+      <c r="K26" s="18">
+        <v>0</v>
+      </c>
+      <c r="L26" s="18">
+        <v>15</v>
+      </c>
+      <c r="M26" s="6">
+        <v>32</v>
+      </c>
+      <c r="N26" s="17">
         <f t="shared" si="23"/>
-        <v>222</v>
-      </c>
-      <c r="G20" s="15">
-        <f t="shared" si="23"/>
-        <v>94</v>
-      </c>
-      <c r="H20" s="15">
-        <f t="shared" si="23"/>
-        <v>-3</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="23"/>
-        <v>114</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="23"/>
-        <v>51</v>
-      </c>
-      <c r="K20" s="15">
-        <f t="shared" si="23"/>
-        <v>45</v>
-      </c>
-      <c r="L20" s="15">
-        <f t="shared" si="23"/>
-        <v>173</v>
-      </c>
-      <c r="M20" s="15">
-        <f t="shared" si="23"/>
-        <v>74</v>
-      </c>
-      <c r="N20" s="15">
-        <f t="shared" si="23"/>
-        <v>160.17600000000004</v>
-      </c>
-      <c r="U20" s="15">
-        <f>U17-U18-U19</f>
-        <v>256</v>
-      </c>
-      <c r="V20" s="15">
-        <f>V17-V18-V19</f>
-        <v>452.17600000000101</v>
-      </c>
-      <c r="W20" s="15">
-        <f>W17-W18-W19</f>
-        <v>784.48708000000011</v>
-      </c>
-      <c r="X20" s="15">
-        <f t="shared" ref="X20:AF20" si="24">X17-X18-X19</f>
-        <v>908.41176159999998</v>
-      </c>
-      <c r="Y20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="Y26" s="17">
         <f t="shared" si="24"/>
-        <v>978.99787317999983</v>
-      </c>
-      <c r="Z20" s="15">
-        <f t="shared" si="24"/>
-        <v>1028.2238387782006</v>
-      </c>
-      <c r="AA20" s="15">
-        <f t="shared" si="24"/>
-        <v>1073.528409384676</v>
-      </c>
-      <c r="AB20" s="15">
-        <f t="shared" si="24"/>
-        <v>1120.7354919958077</v>
-      </c>
-      <c r="AC20" s="15">
-        <f t="shared" si="24"/>
-        <v>1169.9877085669734</v>
-      </c>
-      <c r="AD20" s="15">
-        <f t="shared" si="24"/>
-        <v>1221.4490373552351</v>
-      </c>
-      <c r="AE20" s="15">
-        <f t="shared" si="24"/>
-        <v>1275.308882439188</v>
-      </c>
-      <c r="AF20" s="15">
-        <f t="shared" si="24"/>
-        <v>1331.7869519773253</v>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="17">
+        <v>47</v>
+      </c>
+      <c r="AA26" s="6">
+        <f>Z26*1.03</f>
+        <v>48.410000000000004</v>
+      </c>
+      <c r="AB26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:139">
-      <c r="B21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="19">
-        <v>-2</v>
-      </c>
-      <c r="F21" s="19">
-        <v>7</v>
-      </c>
-      <c r="G21" s="19">
-        <v>-16</v>
-      </c>
-      <c r="H21" s="19">
-        <v>-22</v>
-      </c>
-      <c r="I21" s="19">
-        <v>-3</v>
-      </c>
-      <c r="J21" s="19">
-        <v>-73</v>
-      </c>
-      <c r="K21" s="19">
-        <v>1</v>
-      </c>
-      <c r="L21" s="19">
-        <v>-20</v>
-      </c>
-      <c r="M21" s="6">
-        <v>-11</v>
-      </c>
-      <c r="N21" s="6">
-        <v>0</v>
-      </c>
-      <c r="U21" s="18">
-        <f t="shared" ref="U21:U22" si="25">SUM(G21:J21)</f>
-        <v>-114</v>
-      </c>
-      <c r="V21" s="18">
-        <f t="shared" ref="V21:V22" si="26">SUM(K21:N21)</f>
-        <v>-30</v>
-      </c>
-      <c r="W21" s="6">
-        <f>W20*0.15</f>
-        <v>117.67306200000002</v>
-      </c>
-      <c r="X21" s="6">
-        <f t="shared" ref="X21:AF21" si="27">X20*0.15</f>
-        <v>136.26176423999999</v>
-      </c>
-      <c r="Y21" s="6">
+    <row r="27" spans="2:143" s="2" customFormat="1">
+      <c r="B27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="14">
+        <f t="shared" ref="E27:L27" si="26">E24-E25-E26</f>
+        <v>-37</v>
+      </c>
+      <c r="F27" s="14">
+        <f t="shared" si="26"/>
+        <v>215</v>
+      </c>
+      <c r="G27" s="14">
+        <f t="shared" si="26"/>
+        <v>110</v>
+      </c>
+      <c r="H27" s="14">
+        <f t="shared" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="I27" s="14">
+        <f t="shared" si="26"/>
+        <v>117</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" si="26"/>
+        <v>124</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="26"/>
+        <v>44</v>
+      </c>
+      <c r="L27" s="14">
+        <f t="shared" si="26"/>
+        <v>178</v>
+      </c>
+      <c r="M27" s="14">
+        <f t="shared" ref="M27:N27" si="27">M24-M25-M26</f>
+        <v>53</v>
+      </c>
+      <c r="N27" s="14">
         <f t="shared" si="27"/>
-        <v>146.84968097699996</v>
-      </c>
-      <c r="Z21" s="6">
-        <f t="shared" si="27"/>
-        <v>154.23357581673008</v>
-      </c>
-      <c r="AA21" s="6">
-        <f t="shared" si="27"/>
-        <v>161.0292614077014</v>
-      </c>
-      <c r="AB21" s="6">
-        <f t="shared" si="27"/>
-        <v>168.11032379937114</v>
-      </c>
-      <c r="AC21" s="6">
-        <f t="shared" si="27"/>
-        <v>175.49815628504601</v>
-      </c>
-      <c r="AD21" s="6">
-        <f t="shared" si="27"/>
-        <v>183.21735560328526</v>
-      </c>
-      <c r="AE21" s="6">
-        <f t="shared" si="27"/>
-        <v>191.29633236587819</v>
-      </c>
-      <c r="AF21" s="6">
-        <f t="shared" si="27"/>
-        <v>199.76804279659879</v>
+        <v>636.80000000000007</v>
+      </c>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="Y27" s="14">
+        <f>Y24-Y25-Y26</f>
+        <v>370</v>
+      </c>
+      <c r="Z27" s="14">
+        <f>Z24-Z25-Z26</f>
+        <v>928</v>
+      </c>
+      <c r="AA27" s="14">
+        <f>AA24-AA25-AA26</f>
+        <v>799.91039999999987</v>
+      </c>
+      <c r="AB27" s="14">
+        <f t="shared" ref="AB27:AJ27" si="28">AB24-AB25-AB26</f>
+        <v>905.58710150000024</v>
+      </c>
+      <c r="AC27" s="14">
+        <f t="shared" si="28"/>
+        <v>949.8563031450002</v>
+      </c>
+      <c r="AD27" s="14">
+        <f t="shared" si="28"/>
+        <v>995.86757844360045</v>
+      </c>
+      <c r="AE27" s="14">
+        <f t="shared" si="28"/>
+        <v>1038.5325068797388</v>
+      </c>
+      <c r="AF27" s="14">
+        <f t="shared" si="28"/>
+        <v>1082.8858864331</v>
+      </c>
+      <c r="AG27" s="14">
+        <f t="shared" si="28"/>
+        <v>1129.0387484182904</v>
+      </c>
+      <c r="AH27" s="14">
+        <f t="shared" si="28"/>
+        <v>1177.1174658733248</v>
+      </c>
+      <c r="AI27" s="14">
+        <f t="shared" si="28"/>
+        <v>1227.2666255424592</v>
+      </c>
+      <c r="AJ27" s="14">
+        <f t="shared" si="28"/>
+        <v>1279.6524690275578</v>
+      </c>
+      <c r="AK27" s="2">
+        <f>AJ27*(1+$AM$35)</f>
+        <v>1266.8559443372822</v>
+      </c>
+      <c r="AL27" s="2">
+        <f t="shared" ref="AL27:CW27" si="29">AK27*(1+$AM$35)</f>
+        <v>1254.1873848939092</v>
+      </c>
+      <c r="AM27" s="2">
+        <f t="shared" si="29"/>
+        <v>1241.6455110449701</v>
+      </c>
+      <c r="AN27" s="2">
+        <f t="shared" si="29"/>
+        <v>1229.2290559345204</v>
+      </c>
+      <c r="AO27" s="2">
+        <f t="shared" si="29"/>
+        <v>1216.9367653751751</v>
+      </c>
+      <c r="AP27" s="2">
+        <f t="shared" si="29"/>
+        <v>1204.7673977214233</v>
+      </c>
+      <c r="AQ27" s="2">
+        <f t="shared" si="29"/>
+        <v>1192.719723744209</v>
+      </c>
+      <c r="AR27" s="2">
+        <f t="shared" si="29"/>
+        <v>1180.792526506767</v>
+      </c>
+      <c r="AS27" s="2">
+        <f t="shared" si="29"/>
+        <v>1168.9846012416992</v>
+      </c>
+      <c r="AT27" s="2">
+        <f t="shared" si="29"/>
+        <v>1157.2947552292821</v>
+      </c>
+      <c r="AU27" s="2">
+        <f t="shared" si="29"/>
+        <v>1145.7218076769893</v>
+      </c>
+      <c r="AV27" s="2">
+        <f t="shared" si="29"/>
+        <v>1134.2645896002193</v>
+      </c>
+      <c r="AW27" s="2">
+        <f t="shared" si="29"/>
+        <v>1122.921943704217</v>
+      </c>
+      <c r="AX27" s="2">
+        <f t="shared" si="29"/>
+        <v>1111.6927242671748</v>
+      </c>
+      <c r="AY27" s="2">
+        <f t="shared" si="29"/>
+        <v>1100.5757970245029</v>
+      </c>
+      <c r="AZ27" s="2">
+        <f t="shared" si="29"/>
+        <v>1089.5700390542579</v>
+      </c>
+      <c r="BA27" s="2">
+        <f t="shared" si="29"/>
+        <v>1078.6743386637154</v>
+      </c>
+      <c r="BB27" s="2">
+        <f t="shared" si="29"/>
+        <v>1067.8875952770782</v>
+      </c>
+      <c r="BC27" s="2">
+        <f t="shared" si="29"/>
+        <v>1057.2087193243074</v>
+      </c>
+      <c r="BD27" s="2">
+        <f t="shared" si="29"/>
+        <v>1046.6366321310643</v>
+      </c>
+      <c r="BE27" s="2">
+        <f t="shared" si="29"/>
+        <v>1036.1702658097536</v>
+      </c>
+      <c r="BF27" s="2">
+        <f t="shared" si="29"/>
+        <v>1025.808563151656</v>
+      </c>
+      <c r="BG27" s="2">
+        <f t="shared" si="29"/>
+        <v>1015.5504775201395</v>
+      </c>
+      <c r="BH27" s="2">
+        <f t="shared" si="29"/>
+        <v>1005.3949727449381</v>
+      </c>
+      <c r="BI27" s="2">
+        <f t="shared" si="29"/>
+        <v>995.34102301748862</v>
+      </c>
+      <c r="BJ27" s="2">
+        <f t="shared" si="29"/>
+        <v>985.38761278731374</v>
+      </c>
+      <c r="BK27" s="2">
+        <f t="shared" si="29"/>
+        <v>975.53373665944059</v>
+      </c>
+      <c r="BL27" s="2">
+        <f t="shared" si="29"/>
+        <v>965.77839929284619</v>
+      </c>
+      <c r="BM27" s="2">
+        <f t="shared" si="29"/>
+        <v>956.12061529991774</v>
+      </c>
+      <c r="BN27" s="2">
+        <f t="shared" si="29"/>
+        <v>946.5594091469186</v>
+      </c>
+      <c r="BO27" s="2">
+        <f t="shared" si="29"/>
+        <v>937.09381505544945</v>
+      </c>
+      <c r="BP27" s="2">
+        <f t="shared" si="29"/>
+        <v>927.72287690489497</v>
+      </c>
+      <c r="BQ27" s="2">
+        <f t="shared" si="29"/>
+        <v>918.445648135846</v>
+      </c>
+      <c r="BR27" s="2">
+        <f t="shared" si="29"/>
+        <v>909.26119165448756</v>
+      </c>
+      <c r="BS27" s="2">
+        <f t="shared" si="29"/>
+        <v>900.16857973794265</v>
+      </c>
+      <c r="BT27" s="2">
+        <f t="shared" si="29"/>
+        <v>891.16689394056323</v>
+      </c>
+      <c r="BU27" s="2">
+        <f t="shared" si="29"/>
+        <v>882.25522500115756</v>
+      </c>
+      <c r="BV27" s="2">
+        <f t="shared" si="29"/>
+        <v>873.43267275114601</v>
+      </c>
+      <c r="BW27" s="2">
+        <f t="shared" si="29"/>
+        <v>864.6983460236346</v>
+      </c>
+      <c r="BX27" s="2">
+        <f t="shared" si="29"/>
+        <v>856.05136256339824</v>
+      </c>
+      <c r="BY27" s="2">
+        <f t="shared" si="29"/>
+        <v>847.49084893776421</v>
+      </c>
+      <c r="BZ27" s="2">
+        <f t="shared" si="29"/>
+        <v>839.01594044838657</v>
+      </c>
+      <c r="CA27" s="2">
+        <f t="shared" si="29"/>
+        <v>830.62578104390275</v>
+      </c>
+      <c r="CB27" s="2">
+        <f t="shared" si="29"/>
+        <v>822.31952323346377</v>
+      </c>
+      <c r="CC27" s="2">
+        <f t="shared" si="29"/>
+        <v>814.09632800112911</v>
+      </c>
+      <c r="CD27" s="2">
+        <f t="shared" si="29"/>
+        <v>805.9553647211178</v>
+      </c>
+      <c r="CE27" s="2">
+        <f t="shared" si="29"/>
+        <v>797.89581107390666</v>
+      </c>
+      <c r="CF27" s="2">
+        <f t="shared" si="29"/>
+        <v>789.91685296316757</v>
+      </c>
+      <c r="CG27" s="2">
+        <f t="shared" si="29"/>
+        <v>782.01768443353592</v>
+      </c>
+      <c r="CH27" s="2">
+        <f t="shared" si="29"/>
+        <v>774.19750758920054</v>
+      </c>
+      <c r="CI27" s="2">
+        <f t="shared" si="29"/>
+        <v>766.45553251330853</v>
+      </c>
+      <c r="CJ27" s="2">
+        <f t="shared" si="29"/>
+        <v>758.79097718817548</v>
+      </c>
+      <c r="CK27" s="2">
+        <f t="shared" si="29"/>
+        <v>751.20306741629372</v>
+      </c>
+      <c r="CL27" s="2">
+        <f t="shared" si="29"/>
+        <v>743.69103674213079</v>
+      </c>
+      <c r="CM27" s="2">
+        <f t="shared" si="29"/>
+        <v>736.25412637470947</v>
+      </c>
+      <c r="CN27" s="2">
+        <f t="shared" si="29"/>
+        <v>728.89158511096241</v>
+      </c>
+      <c r="CO27" s="2">
+        <f t="shared" si="29"/>
+        <v>721.60266925985275</v>
+      </c>
+      <c r="CP27" s="2">
+        <f t="shared" si="29"/>
+        <v>714.38664256725417</v>
+      </c>
+      <c r="CQ27" s="2">
+        <f t="shared" si="29"/>
+        <v>707.24277614158166</v>
+      </c>
+      <c r="CR27" s="2">
+        <f t="shared" si="29"/>
+        <v>700.17034838016582</v>
+      </c>
+      <c r="CS27" s="2">
+        <f t="shared" si="29"/>
+        <v>693.16864489636419</v>
+      </c>
+      <c r="CT27" s="2">
+        <f t="shared" si="29"/>
+        <v>686.23695844740053</v>
+      </c>
+      <c r="CU27" s="2">
+        <f t="shared" si="29"/>
+        <v>679.37458886292654</v>
+      </c>
+      <c r="CV27" s="2">
+        <f t="shared" si="29"/>
+        <v>672.5808429742973</v>
+      </c>
+      <c r="CW27" s="2">
+        <f t="shared" si="29"/>
+        <v>665.85503454455431</v>
+      </c>
+      <c r="CX27" s="2">
+        <f t="shared" ref="CX27:EM27" si="30">CW27*(1+$AM$35)</f>
+        <v>659.1964841991088</v>
+      </c>
+      <c r="CY27" s="2">
+        <f t="shared" si="30"/>
+        <v>652.60451935711774</v>
+      </c>
+      <c r="CZ27" s="2">
+        <f t="shared" si="30"/>
+        <v>646.0784741635465</v>
+      </c>
+      <c r="DA27" s="2">
+        <f t="shared" si="30"/>
+        <v>639.617689421911</v>
+      </c>
+      <c r="DB27" s="2">
+        <f t="shared" si="30"/>
+        <v>633.22151252769186</v>
+      </c>
+      <c r="DC27" s="2">
+        <f t="shared" si="30"/>
+        <v>626.88929740241497</v>
+      </c>
+      <c r="DD27" s="2">
+        <f t="shared" si="30"/>
+        <v>620.62040442839077</v>
+      </c>
+      <c r="DE27" s="2">
+        <f t="shared" si="30"/>
+        <v>614.41420038410683</v>
+      </c>
+      <c r="DF27" s="2">
+        <f t="shared" si="30"/>
+        <v>608.27005838026571</v>
+      </c>
+      <c r="DG27" s="2">
+        <f t="shared" si="30"/>
+        <v>602.18735779646306</v>
+      </c>
+      <c r="DH27" s="2">
+        <f t="shared" si="30"/>
+        <v>596.16548421849848</v>
+      </c>
+      <c r="DI27" s="2">
+        <f t="shared" si="30"/>
+        <v>590.20382937631348</v>
+      </c>
+      <c r="DJ27" s="2">
+        <f t="shared" si="30"/>
+        <v>584.30179108255038</v>
+      </c>
+      <c r="DK27" s="2">
+        <f t="shared" si="30"/>
+        <v>578.45877317172483</v>
+      </c>
+      <c r="DL27" s="2">
+        <f t="shared" si="30"/>
+        <v>572.67418544000759</v>
+      </c>
+      <c r="DM27" s="2">
+        <f t="shared" si="30"/>
+        <v>566.94744358560752</v>
+      </c>
+      <c r="DN27" s="2">
+        <f t="shared" si="30"/>
+        <v>561.27796914975147</v>
+      </c>
+      <c r="DO27" s="2">
+        <f t="shared" si="30"/>
+        <v>555.66518945825396</v>
+      </c>
+      <c r="DP27" s="2">
+        <f t="shared" si="30"/>
+        <v>550.10853756367146</v>
+      </c>
+      <c r="DQ27" s="2">
+        <f t="shared" si="30"/>
+        <v>544.6074521880347</v>
+      </c>
+      <c r="DR27" s="2">
+        <f t="shared" si="30"/>
+        <v>539.16137766615429</v>
+      </c>
+      <c r="DS27" s="2">
+        <f t="shared" si="30"/>
+        <v>533.76976388949276</v>
+      </c>
+      <c r="DT27" s="2">
+        <f t="shared" si="30"/>
+        <v>528.43206625059781</v>
+      </c>
+      <c r="DU27" s="2">
+        <f t="shared" si="30"/>
+        <v>523.14774558809188</v>
+      </c>
+      <c r="DV27" s="2">
+        <f t="shared" si="30"/>
+        <v>517.91626813221092</v>
+      </c>
+      <c r="DW27" s="2">
+        <f t="shared" si="30"/>
+        <v>512.73710545088875</v>
+      </c>
+      <c r="DX27" s="2">
+        <f t="shared" si="30"/>
+        <v>507.60973439637985</v>
+      </c>
+      <c r="DY27" s="2">
+        <f t="shared" si="30"/>
+        <v>502.53363705241605</v>
+      </c>
+      <c r="DZ27" s="2">
+        <f t="shared" si="30"/>
+        <v>497.50830068189191</v>
+      </c>
+      <c r="EA27" s="2">
+        <f t="shared" si="30"/>
+        <v>492.53321767507299</v>
+      </c>
+      <c r="EB27" s="2">
+        <f t="shared" si="30"/>
+        <v>487.60788549832228</v>
+      </c>
+      <c r="EC27" s="2">
+        <f t="shared" si="30"/>
+        <v>482.73180664333904</v>
+      </c>
+      <c r="ED27" s="2">
+        <f t="shared" si="30"/>
+        <v>477.90448857690564</v>
+      </c>
+      <c r="EE27" s="2">
+        <f t="shared" si="30"/>
+        <v>473.12544369113658</v>
+      </c>
+      <c r="EF27" s="2">
+        <f t="shared" si="30"/>
+        <v>468.39418925422524</v>
+      </c>
+      <c r="EG27" s="2">
+        <f t="shared" si="30"/>
+        <v>463.710247361683</v>
+      </c>
+      <c r="EH27" s="2">
+        <f t="shared" si="30"/>
+        <v>459.07314488806617</v>
+      </c>
+      <c r="EI27" s="2">
+        <f t="shared" si="30"/>
+        <v>454.48241343918551</v>
+      </c>
+      <c r="EJ27" s="2">
+        <f t="shared" si="30"/>
+        <v>449.93758930479368</v>
+      </c>
+      <c r="EK27" s="2">
+        <f t="shared" si="30"/>
+        <v>445.43821341174572</v>
+      </c>
+      <c r="EL27" s="2">
+        <f t="shared" si="30"/>
+        <v>440.98383127762827</v>
+      </c>
+      <c r="EM27" s="2">
+        <f t="shared" si="30"/>
+        <v>436.57399296485198</v>
       </c>
     </row>
-    <row r="22" spans="2:139">
-      <c r="B22" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="19">
-        <v>0</v>
-      </c>
-      <c r="F22" s="19">
-        <v>0</v>
-      </c>
-      <c r="G22" s="19">
-        <v>0</v>
-      </c>
-      <c r="H22" s="19">
-        <v>0</v>
-      </c>
-      <c r="I22" s="19">
-        <v>0</v>
-      </c>
-      <c r="J22" s="19">
-        <v>0</v>
-      </c>
-      <c r="K22" s="19">
-        <v>0</v>
-      </c>
-      <c r="L22" s="19">
-        <v>15</v>
-      </c>
-      <c r="M22" s="6">
-        <v>32</v>
-      </c>
-      <c r="N22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="18">
-        <f t="shared" si="26"/>
-        <v>47</v>
-      </c>
-      <c r="W22" s="6">
-        <f>V22*1.03</f>
-        <v>48.410000000000004</v>
-      </c>
-      <c r="X22" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:139" s="2" customFormat="1">
-      <c r="B23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" ref="E23:L23" si="28">E20-E21-E22</f>
-        <v>-37</v>
-      </c>
-      <c r="F23" s="15">
-        <f t="shared" si="28"/>
-        <v>215</v>
-      </c>
-      <c r="G23" s="15">
-        <f t="shared" si="28"/>
-        <v>110</v>
-      </c>
-      <c r="H23" s="15">
-        <f t="shared" si="28"/>
-        <v>19</v>
-      </c>
-      <c r="I23" s="15">
-        <f t="shared" si="28"/>
-        <v>117</v>
-      </c>
-      <c r="J23" s="15">
-        <f t="shared" si="28"/>
-        <v>124</v>
-      </c>
-      <c r="K23" s="15">
-        <f t="shared" si="28"/>
-        <v>44</v>
-      </c>
-      <c r="L23" s="15">
-        <f t="shared" si="28"/>
-        <v>178</v>
-      </c>
-      <c r="M23" s="15">
-        <f t="shared" ref="M23:N23" si="29">M20-M21-M22</f>
-        <v>53</v>
-      </c>
-      <c r="N23" s="15">
-        <f t="shared" si="29"/>
-        <v>160.17600000000004</v>
-      </c>
-      <c r="U23" s="15">
-        <f>U20-U21-U22</f>
-        <v>370</v>
-      </c>
-      <c r="V23" s="15">
-        <f>V20-V21-V22</f>
-        <v>435.17600000000101</v>
-      </c>
-      <c r="W23" s="15">
-        <f>W20-W21-W22</f>
-        <v>618.40401800000006</v>
-      </c>
-      <c r="X23" s="15">
-        <f t="shared" ref="X23:AF23" si="30">X20-X21-X22</f>
-        <v>772.14999736000004</v>
-      </c>
-      <c r="Y23" s="15">
-        <f t="shared" si="30"/>
-        <v>832.14819220299989</v>
-      </c>
-      <c r="Z23" s="15">
-        <f t="shared" si="30"/>
-        <v>873.99026296147053</v>
-      </c>
-      <c r="AA23" s="15">
-        <f t="shared" si="30"/>
-        <v>912.49914797697465</v>
-      </c>
-      <c r="AB23" s="15">
-        <f t="shared" si="30"/>
-        <v>952.62516819643656</v>
-      </c>
-      <c r="AC23" s="15">
-        <f t="shared" si="30"/>
-        <v>994.48955228192744</v>
-      </c>
-      <c r="AD23" s="15">
-        <f t="shared" si="30"/>
-        <v>1038.2316817519497</v>
-      </c>
-      <c r="AE23" s="15">
-        <f t="shared" si="30"/>
-        <v>1084.0125500733097</v>
-      </c>
-      <c r="AF23" s="15">
-        <f t="shared" si="30"/>
-        <v>1132.0189091807265</v>
-      </c>
-      <c r="AG23" s="2">
-        <f>AF23*(1+$AI$31)</f>
-        <v>1120.6987200889191</v>
-      </c>
-      <c r="AH23" s="2">
-        <f t="shared" ref="AH23:CS23" si="31">AG23*(1+$AI$31)</f>
-        <v>1109.4917328880299</v>
-      </c>
-      <c r="AI23" s="2">
+    <row r="28" spans="2:143">
+      <c r="B28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" ref="E28:L28" si="31">86.8+12.3</f>
+        <v>99.1</v>
+      </c>
+      <c r="F28" s="6">
         <f t="shared" si="31"/>
-        <v>1098.3968155591497</v>
-      </c>
-      <c r="AJ23" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="G28" s="6">
         <f t="shared" si="31"/>
-        <v>1087.4128474035581</v>
-      </c>
-      <c r="AK23" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="H28" s="6">
         <f t="shared" si="31"/>
-        <v>1076.5387189295225</v>
-      </c>
-      <c r="AL23" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="I28" s="6">
         <f t="shared" si="31"/>
-        <v>1065.7733317402271</v>
-      </c>
-      <c r="AM23" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="J28" s="6">
         <f t="shared" si="31"/>
-        <v>1055.1155984228249</v>
-      </c>
-      <c r="AN23" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="K28" s="6">
         <f t="shared" si="31"/>
-        <v>1044.5644424385966</v>
-      </c>
-      <c r="AO23" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="L28" s="6">
         <f t="shared" si="31"/>
-        <v>1034.1187980142106</v>
-      </c>
-      <c r="AP23" s="2">
-        <f t="shared" si="31"/>
-        <v>1023.7776100340685</v>
-      </c>
-      <c r="AQ23" s="2">
-        <f t="shared" si="31"/>
-        <v>1013.5398339337278</v>
-      </c>
-      <c r="AR23" s="2">
-        <f t="shared" si="31"/>
-        <v>1003.4044355943905</v>
-      </c>
-      <c r="AS23" s="2">
-        <f t="shared" si="31"/>
-        <v>993.37039123844659</v>
-      </c>
-      <c r="AT23" s="2">
-        <f t="shared" si="31"/>
-        <v>983.43668732606216</v>
-      </c>
-      <c r="AU23" s="2">
-        <f t="shared" si="31"/>
-        <v>973.60232045280156</v>
-      </c>
-      <c r="AV23" s="2">
-        <f t="shared" si="31"/>
-        <v>963.86629724827355</v>
-      </c>
-      <c r="AW23" s="2">
-        <f t="shared" si="31"/>
-        <v>954.22763427579082</v>
-      </c>
-      <c r="AX23" s="2">
-        <f t="shared" si="31"/>
-        <v>944.68535793303295</v>
-      </c>
-      <c r="AY23" s="2">
-        <f t="shared" si="31"/>
-        <v>935.23850435370264</v>
-      </c>
-      <c r="AZ23" s="2">
-        <f t="shared" si="31"/>
-        <v>925.88611931016555</v>
-      </c>
-      <c r="BA23" s="2">
-        <f t="shared" si="31"/>
-        <v>916.62725811706389</v>
-      </c>
-      <c r="BB23" s="2">
-        <f t="shared" si="31"/>
-        <v>907.4609855358932</v>
-      </c>
-      <c r="BC23" s="2">
-        <f t="shared" si="31"/>
-        <v>898.38637568053423</v>
-      </c>
-      <c r="BD23" s="2">
-        <f t="shared" si="31"/>
-        <v>889.40251192372887</v>
-      </c>
-      <c r="BE23" s="2">
-        <f t="shared" si="31"/>
-        <v>880.50848680449155</v>
-      </c>
-      <c r="BF23" s="2">
-        <f t="shared" si="31"/>
-        <v>871.70340193644665</v>
-      </c>
-      <c r="BG23" s="2">
-        <f t="shared" si="31"/>
-        <v>862.98636791708213</v>
-      </c>
-      <c r="BH23" s="2">
-        <f t="shared" si="31"/>
-        <v>854.35650423791128</v>
-      </c>
-      <c r="BI23" s="2">
-        <f t="shared" si="31"/>
-        <v>845.81293919553218</v>
-      </c>
-      <c r="BJ23" s="2">
-        <f t="shared" si="31"/>
-        <v>837.35480980357681</v>
-      </c>
-      <c r="BK23" s="2">
-        <f t="shared" si="31"/>
-        <v>828.98126170554099</v>
-      </c>
-      <c r="BL23" s="2">
-        <f t="shared" si="31"/>
-        <v>820.69144908848557</v>
-      </c>
-      <c r="BM23" s="2">
-        <f t="shared" si="31"/>
-        <v>812.48453459760071</v>
-      </c>
-      <c r="BN23" s="2">
-        <f t="shared" si="31"/>
-        <v>804.35968925162467</v>
-      </c>
-      <c r="BO23" s="2">
-        <f t="shared" si="31"/>
-        <v>796.31609235910844</v>
-      </c>
-      <c r="BP23" s="2">
-        <f t="shared" si="31"/>
-        <v>788.35293143551735</v>
-      </c>
-      <c r="BQ23" s="2">
-        <f t="shared" si="31"/>
-        <v>780.46940212116215</v>
-      </c>
-      <c r="BR23" s="2">
-        <f t="shared" si="31"/>
-        <v>772.66470809995053</v>
-      </c>
-      <c r="BS23" s="2">
-        <f t="shared" si="31"/>
-        <v>764.93806101895098</v>
-      </c>
-      <c r="BT23" s="2">
-        <f t="shared" si="31"/>
-        <v>757.28868040876148</v>
-      </c>
-      <c r="BU23" s="2">
-        <f t="shared" si="31"/>
-        <v>749.71579360467388</v>
-      </c>
-      <c r="BV23" s="2">
-        <f t="shared" si="31"/>
-        <v>742.21863566862714</v>
-      </c>
-      <c r="BW23" s="2">
-        <f t="shared" si="31"/>
-        <v>734.79644931194082</v>
-      </c>
-      <c r="BX23" s="2">
-        <f t="shared" si="31"/>
-        <v>727.44848481882138</v>
-      </c>
-      <c r="BY23" s="2">
-        <f t="shared" si="31"/>
-        <v>720.17399997063319</v>
-      </c>
-      <c r="BZ23" s="2">
-        <f t="shared" si="31"/>
-        <v>712.97225997092687</v>
-      </c>
-      <c r="CA23" s="2">
-        <f t="shared" si="31"/>
-        <v>705.84253737121765</v>
-      </c>
-      <c r="CB23" s="2">
-        <f t="shared" si="31"/>
-        <v>698.78411199750542</v>
-      </c>
-      <c r="CC23" s="2">
-        <f t="shared" si="31"/>
-        <v>691.79627087753033</v>
-      </c>
-      <c r="CD23" s="2">
-        <f t="shared" si="31"/>
-        <v>684.87830816875498</v>
-      </c>
-      <c r="CE23" s="2">
-        <f t="shared" si="31"/>
-        <v>678.02952508706744</v>
-      </c>
-      <c r="CF23" s="2">
-        <f t="shared" si="31"/>
-        <v>671.24922983619672</v>
-      </c>
-      <c r="CG23" s="2">
-        <f t="shared" si="31"/>
-        <v>664.53673753783471</v>
-      </c>
-      <c r="CH23" s="2">
-        <f t="shared" si="31"/>
-        <v>657.89137016245638</v>
-      </c>
-      <c r="CI23" s="2">
-        <f t="shared" si="31"/>
-        <v>651.31245646083187</v>
-      </c>
-      <c r="CJ23" s="2">
-        <f t="shared" si="31"/>
-        <v>644.79933189622352</v>
-      </c>
-      <c r="CK23" s="2">
-        <f t="shared" si="31"/>
-        <v>638.35133857726123</v>
-      </c>
-      <c r="CL23" s="2">
-        <f t="shared" si="31"/>
-        <v>631.9678251914886</v>
-      </c>
-      <c r="CM23" s="2">
-        <f t="shared" si="31"/>
-        <v>625.64814693957373</v>
-      </c>
-      <c r="CN23" s="2">
-        <f t="shared" si="31"/>
-        <v>619.39166547017794</v>
-      </c>
-      <c r="CO23" s="2">
-        <f t="shared" si="31"/>
-        <v>613.19774881547619</v>
-      </c>
-      <c r="CP23" s="2">
-        <f t="shared" si="31"/>
-        <v>607.06577132732139</v>
-      </c>
-      <c r="CQ23" s="2">
-        <f t="shared" si="31"/>
-        <v>600.99511361404814</v>
-      </c>
-      <c r="CR23" s="2">
-        <f t="shared" si="31"/>
-        <v>594.98516247790769</v>
-      </c>
-      <c r="CS23" s="2">
-        <f t="shared" si="31"/>
-        <v>589.03531085312864</v>
-      </c>
-      <c r="CT23" s="2">
-        <f t="shared" ref="CT23:EI23" si="32">CS23*(1+$AI$31)</f>
-        <v>583.14495774459738</v>
-      </c>
-      <c r="CU23" s="2">
-        <f t="shared" si="32"/>
-        <v>577.31350816715144</v>
-      </c>
-      <c r="CV23" s="2">
-        <f t="shared" si="32"/>
-        <v>571.54037308547993</v>
-      </c>
-      <c r="CW23" s="2">
-        <f t="shared" si="32"/>
-        <v>565.82496935462507</v>
-      </c>
-      <c r="CX23" s="2">
-        <f t="shared" si="32"/>
-        <v>560.16671966107879</v>
-      </c>
-      <c r="CY23" s="2">
-        <f t="shared" si="32"/>
-        <v>554.56505246446795</v>
-      </c>
-      <c r="CZ23" s="2">
-        <f t="shared" si="32"/>
-        <v>549.0194019398233</v>
-      </c>
-      <c r="DA23" s="2">
-        <f t="shared" si="32"/>
-        <v>543.52920792042505</v>
-      </c>
-      <c r="DB23" s="2">
-        <f t="shared" si="32"/>
-        <v>538.09391584122079</v>
-      </c>
-      <c r="DC23" s="2">
-        <f t="shared" si="32"/>
-        <v>532.71297668280863</v>
-      </c>
-      <c r="DD23" s="2">
-        <f t="shared" si="32"/>
-        <v>527.38584691598055</v>
-      </c>
-      <c r="DE23" s="2">
-        <f t="shared" si="32"/>
-        <v>522.11198844682076</v>
-      </c>
-      <c r="DF23" s="2">
-        <f t="shared" si="32"/>
-        <v>516.89086856235258</v>
-      </c>
-      <c r="DG23" s="2">
-        <f t="shared" si="32"/>
-        <v>511.72195987672904</v>
-      </c>
-      <c r="DH23" s="2">
-        <f t="shared" si="32"/>
-        <v>506.60474027796175</v>
-      </c>
-      <c r="DI23" s="2">
-        <f t="shared" si="32"/>
-        <v>501.53869287518211</v>
-      </c>
-      <c r="DJ23" s="2">
-        <f t="shared" si="32"/>
-        <v>496.5233059464303</v>
-      </c>
-      <c r="DK23" s="2">
-        <f t="shared" si="32"/>
-        <v>491.55807288696599</v>
-      </c>
-      <c r="DL23" s="2">
-        <f t="shared" si="32"/>
-        <v>486.64249215809633</v>
-      </c>
-      <c r="DM23" s="2">
-        <f t="shared" si="32"/>
-        <v>481.77606723651536</v>
-      </c>
-      <c r="DN23" s="2">
-        <f t="shared" si="32"/>
-        <v>476.95830656415018</v>
-      </c>
-      <c r="DO23" s="2">
-        <f t="shared" si="32"/>
-        <v>472.18872349850869</v>
-      </c>
-      <c r="DP23" s="2">
-        <f t="shared" si="32"/>
-        <v>467.46683626352359</v>
-      </c>
-      <c r="DQ23" s="2">
-        <f t="shared" si="32"/>
-        <v>462.79216790088833</v>
-      </c>
-      <c r="DR23" s="2">
-        <f t="shared" si="32"/>
-        <v>458.16424622187947</v>
-      </c>
-      <c r="DS23" s="2">
-        <f t="shared" si="32"/>
-        <v>453.58260375966069</v>
-      </c>
-      <c r="DT23" s="2">
-        <f t="shared" si="32"/>
-        <v>449.04677772206406</v>
-      </c>
-      <c r="DU23" s="2">
-        <f t="shared" si="32"/>
-        <v>444.55630994484341</v>
-      </c>
-      <c r="DV23" s="2">
-        <f t="shared" si="32"/>
-        <v>440.11074684539494</v>
-      </c>
-      <c r="DW23" s="2">
-        <f t="shared" si="32"/>
-        <v>435.70963937694097</v>
-      </c>
-      <c r="DX23" s="2">
-        <f t="shared" si="32"/>
-        <v>431.35254298317153</v>
-      </c>
-      <c r="DY23" s="2">
-        <f t="shared" si="32"/>
-        <v>427.03901755333982</v>
-      </c>
-      <c r="DZ23" s="2">
-        <f t="shared" si="32"/>
-        <v>422.76862737780641</v>
-      </c>
-      <c r="EA23" s="2">
-        <f t="shared" si="32"/>
-        <v>418.54094110402832</v>
-      </c>
-      <c r="EB23" s="2">
-        <f t="shared" si="32"/>
-        <v>414.35553169298805</v>
-      </c>
-      <c r="EC23" s="2">
-        <f t="shared" si="32"/>
-        <v>410.21197637605815</v>
-      </c>
-      <c r="ED23" s="2">
-        <f t="shared" si="32"/>
-        <v>406.10985661229756</v>
-      </c>
-      <c r="EE23" s="2">
-        <f t="shared" si="32"/>
-        <v>402.04875804617456</v>
-      </c>
-      <c r="EF23" s="2">
-        <f t="shared" si="32"/>
-        <v>398.02827046571281</v>
-      </c>
-      <c r="EG23" s="2">
-        <f t="shared" si="32"/>
-        <v>394.04798776105565</v>
-      </c>
-      <c r="EH23" s="2">
-        <f t="shared" si="32"/>
-        <v>390.10750788344507</v>
-      </c>
-      <c r="EI23" s="2">
-        <f t="shared" si="32"/>
-        <v>386.20643280461059</v>
-      </c>
-    </row>
-    <row r="24" spans="2:139">
-      <c r="B24" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="6">
-        <f t="shared" ref="E24:L24" si="33">86.8+12.3</f>
         <v>99.1</v>
       </c>
-      <c r="F24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="G24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="H24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="I24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="K24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="L24" s="6">
-        <f t="shared" si="33"/>
-        <v>99.1</v>
-      </c>
-      <c r="M24" s="6">
+      <c r="M28" s="6">
         <f>99.2</f>
         <v>99.2</v>
       </c>
-      <c r="N24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="U24" s="6">
+      <c r="N28" s="6">
+        <f>12.1+88.1</f>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="Y28" s="6">
         <f>86.8+12.3</f>
         <v>99.1</v>
       </c>
-      <c r="V24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="W24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="X24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="Y24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="Z24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="AA24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="AB24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="AC24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="AD24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="AE24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
-      </c>
-      <c r="AF24" s="6">
-        <f>99.2</f>
-        <v>99.2</v>
+      <c r="Z28" s="6">
+        <f t="shared" ref="Z28:AJ28" si="32">12.1+88.1</f>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AA28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AB28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AC28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AD28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AE28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AF28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AG28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AH28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AI28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="AJ28" s="6">
+        <f t="shared" si="32"/>
+        <v>100.19999999999999</v>
       </c>
     </row>
-    <row r="25" spans="2:139">
-      <c r="B25" s="7" t="s">
+    <row r="29" spans="2:143">
+      <c r="B29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="14">
-        <f t="shared" ref="E25:L25" si="34">E23/E24</f>
+      <c r="E29" s="13">
+        <f t="shared" ref="E29:L29" si="33">E27/E28</f>
         <v>-0.37336024217961655</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F29" s="13">
+        <f t="shared" si="33"/>
+        <v>2.1695257315842587</v>
+      </c>
+      <c r="G29" s="13">
+        <f t="shared" si="33"/>
+        <v>1.109989909182644</v>
+      </c>
+      <c r="H29" s="13">
+        <f t="shared" si="33"/>
+        <v>0.19172552976791121</v>
+      </c>
+      <c r="I29" s="13">
+        <f t="shared" si="33"/>
+        <v>1.1806256306760847</v>
+      </c>
+      <c r="J29" s="13">
+        <f t="shared" si="33"/>
+        <v>1.2512613521695257</v>
+      </c>
+      <c r="K29" s="13">
+        <f t="shared" si="33"/>
+        <v>0.44399596367305755</v>
+      </c>
+      <c r="L29" s="13">
+        <f t="shared" si="33"/>
+        <v>1.7961654894046419</v>
+      </c>
+      <c r="M29" s="13">
+        <f t="shared" ref="M29:N29" si="34">M27/M28</f>
+        <v>0.53427419354838712</v>
+      </c>
+      <c r="N29" s="13">
         <f t="shared" si="34"/>
-        <v>2.1695257315842587</v>
-      </c>
-      <c r="G25" s="14">
-        <f t="shared" si="34"/>
-        <v>1.109989909182644</v>
-      </c>
-      <c r="H25" s="14">
-        <f t="shared" si="34"/>
-        <v>0.19172552976791121</v>
-      </c>
-      <c r="I25" s="14">
-        <f t="shared" si="34"/>
-        <v>1.1806256306760847</v>
-      </c>
-      <c r="J25" s="14">
-        <f t="shared" si="34"/>
-        <v>1.2512613521695257</v>
-      </c>
-      <c r="K25" s="14">
-        <f t="shared" si="34"/>
-        <v>0.44399596367305755</v>
-      </c>
-      <c r="L25" s="14">
-        <f t="shared" si="34"/>
-        <v>1.7961654894046419</v>
-      </c>
-      <c r="M25" s="14">
-        <f t="shared" ref="M25:N25" si="35">M23/M24</f>
-        <v>0.53427419354838712</v>
-      </c>
-      <c r="N25" s="14">
+        <v>6.3552894211576865</v>
+      </c>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="Y29" s="13">
+        <f>Y27/Y28</f>
+        <v>3.7336024217961659</v>
+      </c>
+      <c r="Z29" s="13">
+        <f>Z27/Z28</f>
+        <v>9.261477045908185</v>
+      </c>
+      <c r="AA29" s="13">
+        <f>AA27/AA28</f>
+        <v>7.9831377245508977</v>
+      </c>
+      <c r="AB29" s="13">
+        <f t="shared" ref="AB29:AJ29" si="35">AB27/AB28</f>
+        <v>9.0377954241516996</v>
+      </c>
+      <c r="AC29" s="13">
         <f t="shared" si="35"/>
-        <v>1.6146774193548392</v>
-      </c>
-      <c r="U25" s="14">
-        <f>U23/U24</f>
-        <v>3.7336024217961659</v>
-      </c>
-      <c r="V25" s="14">
-        <f>V23/V24</f>
-        <v>4.3868548387096871</v>
-      </c>
-      <c r="W25" s="14">
-        <f>W23/W24</f>
-        <v>6.2339114717741939</v>
-      </c>
-      <c r="X25" s="14">
-        <f t="shared" ref="X25:AF25" si="36">X23/X24</f>
-        <v>7.78377013467742</v>
-      </c>
-      <c r="Y25" s="14">
+        <v>9.4796038238023979</v>
+      </c>
+      <c r="AD29" s="13">
+        <f t="shared" si="35"/>
+        <v>9.9387981880598861</v>
+      </c>
+      <c r="AE29" s="13">
+        <f t="shared" si="35"/>
+        <v>10.364595877043302</v>
+      </c>
+      <c r="AF29" s="13">
+        <f t="shared" si="35"/>
+        <v>10.807244375579842</v>
+      </c>
+      <c r="AG29" s="13">
+        <f t="shared" si="35"/>
+        <v>11.267851780621662</v>
+      </c>
+      <c r="AH29" s="13">
+        <f t="shared" si="35"/>
+        <v>11.747679300132983</v>
+      </c>
+      <c r="AI29" s="13">
+        <f t="shared" si="35"/>
+        <v>12.248169915593406</v>
+      </c>
+      <c r="AJ29" s="13">
+        <f t="shared" si="35"/>
+        <v>12.770982724825927</v>
+      </c>
+    </row>
+    <row r="31" spans="2:143">
+      <c r="B31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15">
+        <f>M7/I7-1</f>
+        <v>0.12925170068027203</v>
+      </c>
+      <c r="N31" s="15">
+        <f>N7/J7-1</f>
+        <v>0.21527777777777768</v>
+      </c>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="Y31" s="15">
+        <f>Y7/X7-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="Z31" s="15">
+        <f>Z7/Y7-1</f>
+        <v>0.21527777777777768</v>
+      </c>
+    </row>
+    <row r="32" spans="2:143">
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="Y32" s="15"/>
+      <c r="Z32" s="15"/>
+    </row>
+    <row r="33" spans="2:39">
+      <c r="B33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15">
+        <f t="shared" ref="I33:L36" si="36">I9/E9-1</f>
+        <v>6.4200976971388712E-2</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="36"/>
-        <v>8.3885906472076606</v>
-      </c>
-      <c r="Z25" s="14">
+        <v>1.555814858031912E-3</v>
+      </c>
+      <c r="K33" s="15">
         <f t="shared" si="36"/>
-        <v>8.8103857153374037</v>
-      </c>
-      <c r="AA25" s="14">
+        <v>0.28553459119496849</v>
+      </c>
+      <c r="L33" s="15">
         <f t="shared" si="36"/>
-        <v>9.198580120735631</v>
-      </c>
-      <c r="AB25" s="14">
+        <v>-0.1513353115727003</v>
+      </c>
+      <c r="M33" s="15">
+        <f t="shared" ref="M33:M36" si="37">M9/I9-1</f>
+        <v>0.121967213114754</v>
+      </c>
+      <c r="N33" s="15">
+        <f t="shared" ref="N33:N36" si="38">N9/J9-1</f>
+        <v>0.18796116504854377</v>
+      </c>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15">
+        <f>Z9/Y9-1</f>
+        <v>9.7568389057750782E-2</v>
+      </c>
+      <c r="AA33" s="15">
+        <f t="shared" ref="AA33:AJ36" si="39">AA9/Z9-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AB33" s="15">
+        <f t="shared" si="39"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AC33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AJ33" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:39">
+      <c r="B34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15">
         <f t="shared" si="36"/>
-        <v>9.6030762923027879</v>
-      </c>
-      <c r="AC25" s="14">
+        <v>0.2753623188405796</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="36"/>
-        <v>10.025096293164591</v>
-      </c>
-      <c r="AD25" s="14">
+        <v>8.7136929460580825E-2</v>
+      </c>
+      <c r="K34" s="15">
         <f t="shared" si="36"/>
-        <v>10.466045178951106</v>
-      </c>
-      <c r="AE25" s="14">
+        <v>3.7735849056603765E-2</v>
+      </c>
+      <c r="L34" s="15">
         <f t="shared" si="36"/>
-        <v>10.927545867674493</v>
-      </c>
-      <c r="AF25" s="14">
+        <v>0.16370808678500981</v>
+      </c>
+      <c r="M34" s="15">
+        <f t="shared" si="37"/>
+        <v>0.11742424242424243</v>
+      </c>
+      <c r="N34" s="15">
+        <f t="shared" si="38"/>
+        <v>0.20229007633587792</v>
+      </c>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="Y34" s="15"/>
+      <c r="Z34" s="15">
+        <f t="shared" ref="Z34:Z36" si="40">Z10/Y10-1</f>
+        <v>0.13212180746561897</v>
+      </c>
+      <c r="AA34" s="15">
+        <f t="shared" si="39"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AB34" s="15">
+        <f t="shared" si="39"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AC34" s="15">
+        <f t="shared" si="39"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AD34" s="15">
+        <f t="shared" si="39"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AE34" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF34" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG34" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH34" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI34" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AJ34" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:39">
+      <c r="B35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15">
         <f t="shared" si="36"/>
-        <v>11.411480939321839</v>
+        <v>1.2222222222222223</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="15">
+        <f t="shared" si="36"/>
+        <v>-0.44444444444444442</v>
+      </c>
+      <c r="L35" s="15">
+        <f t="shared" si="36"/>
+        <v>-0.27272727272727271</v>
+      </c>
+      <c r="M35" s="15">
+        <f t="shared" si="37"/>
+        <v>-0.7</v>
+      </c>
+      <c r="N35" s="15">
+        <f t="shared" si="38"/>
+        <v>-0.44444444444444442</v>
+      </c>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="Y35" s="15"/>
+      <c r="Z35" s="15">
+        <f t="shared" si="40"/>
+        <v>-0.51020408163265307</v>
+      </c>
+      <c r="AA35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AB35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AC35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AD35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AE35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AF35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AG35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AH35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AI35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AJ35" s="15">
+        <f t="shared" si="39"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AL35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM35" s="15">
+        <v>-0.01</v>
       </c>
     </row>
-    <row r="27" spans="2:139">
-      <c r="B27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16">
-        <f>M3/I3-1</f>
-        <v>0.12925170068027203</v>
-      </c>
-      <c r="N27" s="16">
-        <f>N3/J3-1</f>
-        <v>0.15277777777777768</v>
-      </c>
-      <c r="U27" s="16">
-        <f>U3/T3-1</f>
-        <v>1.4084507042253502E-2</v>
-      </c>
-      <c r="V27" s="16">
-        <f>V3/U3-1</f>
-        <v>0.15277777777777768</v>
+    <row r="36" spans="2:39">
+      <c r="B36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15">
+        <f t="shared" si="36"/>
+        <v>0.1169181034482758</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" si="36"/>
+        <v>1.5022860875244959E-2</v>
+      </c>
+      <c r="K36" s="15">
+        <f t="shared" si="36"/>
+        <v>0.1881342701014832</v>
+      </c>
+      <c r="L36" s="15">
+        <f t="shared" si="36"/>
+        <v>-7.9437131184748044E-2</v>
+      </c>
+      <c r="M36" s="15">
+        <f t="shared" si="37"/>
+        <v>0.11287988422575967</v>
+      </c>
+      <c r="N36" s="15">
+        <f t="shared" si="38"/>
+        <v>0.18854568854568865</v>
+      </c>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="Y36" s="15"/>
+      <c r="Z36" s="15">
+        <f t="shared" si="40"/>
+        <v>0.10225043277553381</v>
+      </c>
+      <c r="AA36" s="15">
+        <f t="shared" si="39"/>
+        <v>6.244372317034852E-2</v>
+      </c>
+      <c r="AB36" s="15">
+        <f t="shared" si="39"/>
+        <v>4.7950115300471108E-2</v>
+      </c>
+      <c r="AC36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.5654981691219945E-2</v>
+      </c>
+      <c r="AD36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.3226748906445724E-2</v>
+      </c>
+      <c r="AE36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0743496653049318E-2</v>
+      </c>
+      <c r="AF36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.0865584877863839E-2</v>
+      </c>
+      <c r="AG36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.1007601639509108E-2</v>
+      </c>
+      <c r="AH36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.1172757567925036E-2</v>
+      </c>
+      <c r="AI36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.1364765575100373E-2</v>
+      </c>
+      <c r="AJ36" s="15">
+        <f t="shared" si="39"/>
+        <v>3.1587914135506878E-2</v>
+      </c>
+      <c r="AL36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM36" s="15">
+        <v>0.08</v>
       </c>
     </row>
-    <row r="28" spans="2:139">
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
+    <row r="37" spans="2:39">
+      <c r="B37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="15">
+        <f t="shared" ref="E37:K37" si="41">E14/E12</f>
+        <v>0.20635775862068967</v>
+      </c>
+      <c r="F37" s="15">
+        <f t="shared" si="41"/>
+        <v>0.19007184846505551</v>
+      </c>
+      <c r="G37" s="15">
+        <f t="shared" si="41"/>
+        <v>0.22248243559718969</v>
+      </c>
+      <c r="H37" s="15">
+        <f t="shared" si="41"/>
+        <v>0.20608261461643212</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="41"/>
+        <v>0.20067534973468404</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="41"/>
+        <v>0.1998069498069498</v>
+      </c>
+      <c r="K37" s="15">
+        <f t="shared" si="41"/>
+        <v>0.18462549277266754</v>
+      </c>
+      <c r="L37" s="15">
+        <f>L14/L12</f>
+        <v>0.20266272189349113</v>
+      </c>
+      <c r="M37" s="15">
+        <f t="shared" ref="M37:N37" si="42">M14/M12</f>
+        <v>0.20112700476809708</v>
+      </c>
+      <c r="N37" s="15">
+        <f t="shared" si="42"/>
+        <v>0.2</v>
+      </c>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="Y37" s="15">
+        <f t="shared" ref="Y37" si="43">Y14/Y12</f>
+        <v>0.20496249278707443</v>
+      </c>
+      <c r="Z37" s="15">
+        <f t="shared" ref="Z37:AJ37" si="44">Z14/Z12</f>
+        <v>0.20008376086273688</v>
+      </c>
+      <c r="AA37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AB37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AC37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AD37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AE37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AF37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="AG37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AH37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.20999999999999996</v>
+      </c>
+      <c r="AI37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AJ37" s="15">
+        <f t="shared" si="44"/>
+        <v>0.21</v>
+      </c>
+      <c r="AL37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM37" s="6">
+        <f>NPV(AM36,Z27:EM27)</f>
+        <v>13278.790380350476</v>
+      </c>
     </row>
-    <row r="29" spans="2:139">
-      <c r="B29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16">
-        <f t="shared" ref="I29:L32" si="37">I5/E5-1</f>
-        <v>6.4200976971388712E-2</v>
-      </c>
-      <c r="J29" s="16">
-        <f t="shared" si="37"/>
-        <v>1.555814858031912E-3</v>
-      </c>
-      <c r="K29" s="16">
-        <f t="shared" si="37"/>
-        <v>0.28553459119496849</v>
-      </c>
-      <c r="L29" s="16">
-        <f t="shared" si="37"/>
-        <v>-0.1513353115727003</v>
-      </c>
-      <c r="M29" s="16">
-        <f t="shared" ref="M29:M32" si="38">M5/I5-1</f>
-        <v>0.121967213114754</v>
-      </c>
-      <c r="N29" s="16">
-        <f t="shared" ref="N29:N32" si="39">N5/J5-1</f>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16">
-        <f>V5/U5-1</f>
-        <v>0.10227963525835859</v>
-      </c>
-      <c r="W29" s="16">
-        <f t="shared" ref="W29:AF32" si="40">W5/V5-1</f>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="X29" s="16">
-        <f t="shared" si="40"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="Y29" s="16">
-        <f t="shared" si="40"/>
+    <row r="38" spans="2:39">
+      <c r="B38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15">
+        <f t="shared" ref="I38:L39" si="45">I15/E15-1</f>
+        <v>0.13592233009708732</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="45"/>
+        <v>-1.4598540145985384E-2</v>
+      </c>
+      <c r="K38" s="15">
+        <f t="shared" si="45"/>
+        <v>-0.1009174311926605</v>
+      </c>
+      <c r="L38" s="15">
+        <f t="shared" si="45"/>
+        <v>2.564102564102555E-2</v>
+      </c>
+      <c r="M38" s="15">
+        <f t="shared" ref="M38:N38" si="46">M15/I15-1</f>
+        <v>5.9829059829059839E-2</v>
+      </c>
+      <c r="N38" s="15">
+        <f t="shared" si="46"/>
+        <v>0.21481481481481479</v>
+      </c>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="Y38" s="15"/>
+      <c r="Z38" s="15">
+        <f>Z15/Y15-1</f>
+        <v>5.8577405857740628E-2</v>
+      </c>
+      <c r="AA38" s="15">
+        <f t="shared" ref="AA38:AJ38" si="47">AA15/Z15-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="Z29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AA29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AB29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AD29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AE29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AF29" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:139">
-      <c r="B30" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16">
-        <f t="shared" si="37"/>
-        <v>0.2753623188405796</v>
-      </c>
-      <c r="J30" s="16">
-        <f t="shared" si="37"/>
-        <v>8.7136929460580825E-2</v>
-      </c>
-      <c r="K30" s="16">
-        <f t="shared" si="37"/>
-        <v>3.7735849056603765E-2</v>
-      </c>
-      <c r="L30" s="16">
-        <f t="shared" si="37"/>
-        <v>0.16370808678500981</v>
-      </c>
-      <c r="M30" s="16">
-        <f t="shared" si="38"/>
-        <v>0.11742424242424243</v>
-      </c>
-      <c r="N30" s="16">
-        <f t="shared" si="39"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16">
-        <f t="shared" ref="V30:V32" si="41">V6/U6-1</f>
-        <v>0.11094302554027502</v>
-      </c>
-      <c r="W30" s="16">
-        <f t="shared" si="40"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="X30" s="16">
-        <f t="shared" si="40"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="Y30" s="16">
-        <f t="shared" si="40"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="Z30" s="16">
-        <f t="shared" si="40"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AA30" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AB30" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC30" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AD30" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AE30" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AF30" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:139">
-      <c r="B31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16">
-        <f t="shared" si="37"/>
-        <v>1.2222222222222223</v>
-      </c>
-      <c r="J31" s="16">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="16">
-        <f t="shared" si="37"/>
-        <v>-0.44444444444444442</v>
-      </c>
-      <c r="L31" s="16">
-        <f t="shared" si="37"/>
-        <v>-0.27272727272727271</v>
-      </c>
-      <c r="M31" s="16">
-        <f t="shared" si="38"/>
-        <v>-0.7</v>
-      </c>
-      <c r="N31" s="16">
-        <f t="shared" si="39"/>
-        <v>0.11111111111111116</v>
-      </c>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16">
-        <f t="shared" si="41"/>
-        <v>-0.40816326530612246</v>
-      </c>
-      <c r="W31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="X31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="Y31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="Z31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AA31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AB31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AC31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AD31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AE31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AF31" s="16">
-        <f t="shared" si="40"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AH31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI31" s="16">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="32" spans="2:139">
-      <c r="B32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16">
-        <f t="shared" si="37"/>
-        <v>0.1169181034482758</v>
-      </c>
-      <c r="J32" s="16">
-        <f t="shared" si="37"/>
-        <v>1.5022860875244959E-2</v>
-      </c>
-      <c r="K32" s="16">
-        <f t="shared" si="37"/>
-        <v>0.1881342701014832</v>
-      </c>
-      <c r="L32" s="16">
-        <f t="shared" si="37"/>
-        <v>-7.9437131184748044E-2</v>
-      </c>
-      <c r="M32" s="16">
-        <f t="shared" si="38"/>
-        <v>0.11287988422575967</v>
-      </c>
-      <c r="N32" s="16">
-        <f t="shared" si="39"/>
-        <v>0.18625482625482626</v>
-      </c>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16">
-        <f t="shared" si="41"/>
-        <v>0.10142873629544158</v>
-      </c>
-      <c r="W32" s="16">
-        <f t="shared" si="40"/>
-        <v>0.13070239776694592</v>
-      </c>
-      <c r="X32" s="16">
-        <f t="shared" si="40"/>
-        <v>7.0419227065388279E-2</v>
-      </c>
-      <c r="Y32" s="16">
-        <f t="shared" si="40"/>
-        <v>4.2883156847113746E-2</v>
-      </c>
-      <c r="Z32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.3027627938512216E-2</v>
-      </c>
-      <c r="AA32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.082148025403475E-2</v>
-      </c>
-      <c r="AB32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.0956301671749342E-2</v>
-      </c>
-      <c r="AC32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.1113104410184889E-2</v>
-      </c>
-      <c r="AD32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.1295420731740409E-2</v>
-      </c>
-      <c r="AE32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.1507332280196865E-2</v>
-      </c>
-      <c r="AF32" s="16">
-        <f t="shared" si="40"/>
-        <v>3.1753549082620847E-2</v>
-      </c>
-      <c r="AH32" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI32" s="16">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="33" spans="2:35">
-      <c r="B33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="16">
-        <f t="shared" ref="E33:K33" si="42">E10/E8</f>
-        <v>0.20635775862068967</v>
-      </c>
-      <c r="F33" s="16">
-        <f t="shared" si="42"/>
-        <v>0.19007184846505551</v>
-      </c>
-      <c r="G33" s="16">
-        <f t="shared" si="42"/>
-        <v>0.22248243559718969</v>
-      </c>
-      <c r="H33" s="16">
-        <f t="shared" si="42"/>
-        <v>0.20608261461643212</v>
-      </c>
-      <c r="I33" s="16">
-        <f t="shared" si="42"/>
-        <v>0.20067534973468404</v>
-      </c>
-      <c r="J33" s="16">
-        <f t="shared" si="42"/>
-        <v>0.1998069498069498</v>
-      </c>
-      <c r="K33" s="16">
-        <f t="shared" si="42"/>
-        <v>0.18462549277266754</v>
-      </c>
-      <c r="L33" s="16">
-        <f>L10/L8</f>
-        <v>0.20266272189349113</v>
-      </c>
-      <c r="M33" s="16">
-        <f t="shared" ref="M33:N33" si="43">M10/M8</f>
-        <v>0.20112700476809708</v>
-      </c>
-      <c r="N33" s="16">
-        <f t="shared" si="43"/>
-        <v>0.2</v>
-      </c>
-      <c r="U33" s="16">
-        <f t="shared" ref="U33" si="44">U10/U8</f>
-        <v>0.20496249278707443</v>
-      </c>
-      <c r="V33" s="16">
-        <f t="shared" ref="V33:AF33" si="45">V10/V8</f>
-        <v>0.19838640049958728</v>
-      </c>
-      <c r="W33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="X33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
-      </c>
-      <c r="Y33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
-      </c>
-      <c r="Z33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21000000000000002</v>
-      </c>
-      <c r="AA33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
-      </c>
-      <c r="AB33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
-      </c>
-      <c r="AC33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.20999999999999996</v>
-      </c>
-      <c r="AD33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.20999999999999996</v>
-      </c>
-      <c r="AE33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
-      </c>
-      <c r="AF33" s="16">
-        <f t="shared" si="45"/>
-        <v>0.21</v>
-      </c>
-      <c r="AH33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI33" s="6">
-        <f>NPV(AI32,V23:EI23)</f>
-        <v>11267.766238362408</v>
-      </c>
-    </row>
-    <row r="34" spans="2:35">
-      <c r="B34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16">
-        <f t="shared" ref="I34:L35" si="46">I11/E11-1</f>
-        <v>0.13592233009708732</v>
-      </c>
-      <c r="J34" s="16">
-        <f t="shared" si="46"/>
-        <v>-1.4598540145985384E-2</v>
-      </c>
-      <c r="K34" s="16">
-        <f t="shared" si="46"/>
-        <v>-0.1009174311926605</v>
-      </c>
-      <c r="L34" s="16">
-        <f t="shared" si="46"/>
-        <v>2.564102564102555E-2</v>
-      </c>
-      <c r="M34" s="16">
-        <f t="shared" ref="M34:N34" si="47">M11/I11-1</f>
-        <v>5.9829059829059839E-2</v>
-      </c>
-      <c r="N34" s="16">
+      <c r="AB38" s="15">
         <f t="shared" si="47"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16">
-        <f>V11/U11-1</f>
-        <v>6.3807531380752902E-3</v>
-      </c>
-      <c r="W34" s="16">
-        <f t="shared" ref="W34:AF34" si="48">W11/V11-1</f>
+      <c r="AC38" s="15">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD38" s="15">
+        <f t="shared" si="47"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="X34" s="16">
+      <c r="AE38" s="15">
+        <f t="shared" si="47"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF38" s="15">
+        <f t="shared" si="47"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG38" s="15">
+        <f t="shared" si="47"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH38" s="15">
+        <f t="shared" si="47"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI38" s="15">
+        <f t="shared" si="47"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AJ38" s="15">
+        <f t="shared" si="47"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AL38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM38" s="6">
+        <f>Main!D8</f>
+        <v>-2979</v>
+      </c>
+    </row>
+    <row r="39" spans="2:39">
+      <c r="B39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15">
+        <f t="shared" si="45"/>
+        <v>9.8765432098765427E-2</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="45"/>
+        <v>-0.23417721518987344</v>
+      </c>
+      <c r="K39" s="15">
+        <f t="shared" si="45"/>
+        <v>-1.103448275862069</v>
+      </c>
+      <c r="L39" s="15">
+        <f t="shared" si="45"/>
+        <v>-0.32743362831858402</v>
+      </c>
+      <c r="M39" s="15">
+        <f t="shared" ref="M39:N39" si="48">M16/I16-1</f>
+        <v>0.15730337078651679</v>
+      </c>
+      <c r="N39" s="15">
         <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Y34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="Z34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AA34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AB34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AC34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AD34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AE34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AF34" s="16">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AH34" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI34" s="6">
-        <f>Main!D8</f>
-        <v>-4321</v>
-      </c>
-    </row>
-    <row r="35" spans="2:35">
-      <c r="B35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16">
-        <f t="shared" si="46"/>
-        <v>9.8765432098765427E-2</v>
-      </c>
-      <c r="J35" s="16">
-        <f t="shared" si="46"/>
-        <v>-0.23417721518987344</v>
-      </c>
-      <c r="K35" s="16">
-        <f t="shared" si="46"/>
-        <v>-1.103448275862069</v>
-      </c>
-      <c r="L35" s="16">
-        <f t="shared" si="46"/>
-        <v>-0.32743362831858402</v>
-      </c>
-      <c r="M35" s="16">
-        <f t="shared" ref="M35:N35" si="49">M12/I12-1</f>
-        <v>0.15730337078651679</v>
-      </c>
-      <c r="N35" s="16">
+        <v>-0.21487603305785119</v>
+      </c>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="Y39" s="15"/>
+      <c r="Z39" s="15">
+        <f>Z16/Y16-1</f>
+        <v>-0.23011363636363635</v>
+      </c>
+      <c r="AA39" s="15">
+        <f t="shared" ref="AA39:AJ39" si="49">AA16/Z16-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AB39" s="15">
+        <f t="shared" si="49"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC39" s="15">
         <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16">
-        <f>V12/U12-1</f>
-        <v>-0.14937499999999992</v>
-      </c>
-      <c r="W35" s="16">
-        <f t="shared" ref="W35:AF35" si="50">W12/V12-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="X35" s="16">
+      <c r="AD39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AG39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AJ39" s="15">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AL39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM39" s="6">
+        <f>AM37+AM38</f>
+        <v>10299.790380350476</v>
+      </c>
+    </row>
+    <row r="40" spans="2:39">
+      <c r="B40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="15">
+        <f t="shared" ref="E40:K40" si="50">E21/E12</f>
+        <v>0.10614224137931035</v>
+      </c>
+      <c r="F40" s="15">
         <f t="shared" si="50"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="Y35" s="16">
+        <v>6.8909209666884394E-2</v>
+      </c>
+      <c r="G40" s="15">
         <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="Z35" s="16">
+        <v>0.11241217798594848</v>
+      </c>
+      <c r="H40" s="15">
         <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AA35" s="16">
+        <v>8.6699954607353608E-2</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AB35" s="16">
+        <v>9.6960926193921854E-2</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AC35" s="16">
+        <v>0.11003861003861004</v>
+      </c>
+      <c r="K40" s="15">
         <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AD35" s="16">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AE35" s="16">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AF35" s="16">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH35" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI35" s="6">
-        <f>AI33+AI34</f>
-        <v>6946.7662383624083</v>
+        <v>0.11629434954007885</v>
+      </c>
+      <c r="L40" s="15">
+        <f>L21/L12</f>
+        <v>0.10108481262327416</v>
+      </c>
+      <c r="M40" s="15">
+        <f t="shared" ref="M40:N40" si="51">M21/M12</f>
+        <v>9.8396185522323362E-2</v>
+      </c>
+      <c r="N40" s="15">
+        <f t="shared" si="51"/>
+        <v>0.13069842988630212</v>
+      </c>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="Y40" s="15">
+        <f t="shared" ref="Y40" si="52">Y21/Y12</f>
+        <v>0.10132717830351991</v>
+      </c>
+      <c r="Z40" s="15">
+        <f t="shared" ref="Z40:AJ40" si="53">Z21/Z12</f>
+        <v>0.11600879489058737</v>
+      </c>
+      <c r="AA40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.12606322801899991</v>
+      </c>
+      <c r="AB40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.12742394584750058</v>
+      </c>
+      <c r="AC40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.12855504097762743</v>
+      </c>
+      <c r="AD40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.12996448733884797</v>
+      </c>
+      <c r="AE40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.13115353717916209</v>
+      </c>
+      <c r="AF40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.13232754716123876</v>
+      </c>
+      <c r="AG40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.13348798970187883</v>
+      </c>
+      <c r="AH40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.13463648751941482</v>
+      </c>
+      <c r="AI40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.13577483428914047</v>
+      </c>
+      <c r="AJ40" s="15">
+        <f t="shared" si="53"/>
+        <v>0.13690501729758101</v>
+      </c>
+      <c r="AL40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM40" s="22">
+        <f>AM39/AJ28</f>
+        <v>102.79231916517442</v>
       </c>
     </row>
-    <row r="36" spans="2:35">
-      <c r="B36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="16">
-        <f t="shared" ref="E36:K36" si="51">E17/E8</f>
-        <v>0.10614224137931035</v>
-      </c>
-      <c r="F36" s="16">
-        <f t="shared" si="51"/>
-        <v>6.8909209666884394E-2</v>
-      </c>
-      <c r="G36" s="16">
-        <f t="shared" si="51"/>
-        <v>0.11241217798594848</v>
-      </c>
-      <c r="H36" s="16">
-        <f t="shared" si="51"/>
-        <v>8.6699954607353608E-2</v>
-      </c>
-      <c r="I36" s="16">
-        <f t="shared" si="51"/>
-        <v>9.6960926193921854E-2</v>
-      </c>
-      <c r="J36" s="16">
-        <f t="shared" si="51"/>
-        <v>0.11003861003861004</v>
-      </c>
-      <c r="K36" s="16">
-        <f t="shared" si="51"/>
-        <v>0.11629434954007885</v>
-      </c>
-      <c r="L36" s="16">
-        <f>L17/L8</f>
-        <v>0.10108481262327416</v>
-      </c>
-      <c r="M36" s="16">
-        <f t="shared" ref="M36:N36" si="52">M17/M8</f>
-        <v>9.8396185522323362E-2</v>
-      </c>
-      <c r="N36" s="16">
-        <f t="shared" si="52"/>
-        <v>0.12474124462960554</v>
-      </c>
-      <c r="U36" s="16">
-        <f t="shared" ref="U36" si="53">U17/U8</f>
-        <v>0.10132717830351991</v>
-      </c>
-      <c r="V36" s="16">
-        <f t="shared" ref="V36:AF36" si="54">V17/V8</f>
-        <v>0.11199910309014792</v>
-      </c>
-      <c r="W36" s="16">
+    <row r="41" spans="2:39">
+      <c r="B41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="15">
+        <f t="shared" ref="E41:K41" si="54">E25/E24</f>
+        <v>5.128205128205128E-2</v>
+      </c>
+      <c r="F41" s="15">
         <f t="shared" si="54"/>
-        <v>0.13156158745832749</v>
-      </c>
-      <c r="X36" s="16">
+        <v>3.1531531531531529E-2</v>
+      </c>
+      <c r="G41" s="15">
         <f t="shared" si="54"/>
-        <v>0.13528467400660574</v>
-      </c>
-      <c r="Y36" s="16">
+        <v>-0.1702127659574468</v>
+      </c>
+      <c r="H41" s="15">
         <f t="shared" si="54"/>
-        <v>0.13721063899396863</v>
-      </c>
-      <c r="Z36" s="16">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="54"/>
-        <v>0.13840407449774622</v>
-      </c>
-      <c r="AA36" s="16">
+        <v>-2.6315789473684209E-2</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="54"/>
-        <v>0.13942083417595558</v>
-      </c>
-      <c r="AB36" s="16">
+        <v>-1.4313725490196079</v>
+      </c>
+      <c r="K41" s="15">
         <f t="shared" si="54"/>
-        <v>0.140425810410088</v>
-      </c>
-      <c r="AC36" s="16">
-        <f t="shared" si="54"/>
-        <v>0.14142041302650443</v>
-      </c>
-      <c r="AD36" s="16">
-        <f t="shared" si="54"/>
-        <v>0.14240620397126447</v>
-      </c>
-      <c r="AE36" s="16">
-        <f t="shared" si="54"/>
-        <v>0.14338491785526911</v>
-      </c>
-      <c r="AF36" s="16">
-        <f t="shared" si="54"/>
-        <v>0.14435848439756699</v>
-      </c>
-      <c r="AH36" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI36" s="23">
-        <f>AI35/AF24</f>
-        <v>70.027885467362992</v>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="L41" s="15">
+        <f>L25/L24</f>
+        <v>-0.11560693641618497</v>
+      </c>
+      <c r="M41" s="15">
+        <f t="shared" ref="M41:N41" si="55">M25/M24</f>
+        <v>-0.14864864864864866</v>
+      </c>
+      <c r="N41" s="15">
+        <f t="shared" si="55"/>
+        <v>-0.20880789673500377</v>
+      </c>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="Y41" s="15">
+        <f t="shared" ref="Y41" si="56">Y25/Y24</f>
+        <v>-0.4453125</v>
+      </c>
+      <c r="Z41" s="15">
+        <f t="shared" ref="Z41:AJ41" si="57">Z25/Z24</f>
+        <v>-0.16766467065868262</v>
+      </c>
+      <c r="AA41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AB41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AC41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AD41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AE41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AF41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AG41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AI41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AJ41" s="15">
+        <f t="shared" si="57"/>
+        <v>0.15</v>
+      </c>
+      <c r="AL41" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM41" s="22">
+        <f>Main!D3</f>
+        <v>178.49960000000002</v>
       </c>
     </row>
-    <row r="37" spans="2:35">
-      <c r="B37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="16">
-        <f t="shared" ref="E37:K37" si="55">E21/E20</f>
-        <v>5.128205128205128E-2</v>
-      </c>
-      <c r="F37" s="16">
-        <f t="shared" si="55"/>
-        <v>3.1531531531531529E-2</v>
-      </c>
-      <c r="G37" s="16">
-        <f t="shared" si="55"/>
-        <v>-0.1702127659574468</v>
-      </c>
-      <c r="H37" s="16">
-        <f t="shared" si="55"/>
-        <v>7.333333333333333</v>
-      </c>
-      <c r="I37" s="16">
-        <f t="shared" si="55"/>
-        <v>-2.6315789473684209E-2</v>
-      </c>
-      <c r="J37" s="16">
-        <f t="shared" si="55"/>
-        <v>-1.4313725490196079</v>
-      </c>
-      <c r="K37" s="16">
-        <f t="shared" si="55"/>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="L37" s="16">
-        <f>L21/L20</f>
-        <v>-0.11560693641618497</v>
-      </c>
-      <c r="M37" s="16">
-        <f t="shared" ref="M37:N37" si="56">M21/M20</f>
-        <v>-0.14864864864864866</v>
-      </c>
-      <c r="N37" s="16">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="16">
-        <f t="shared" ref="U37" si="57">U21/U20</f>
-        <v>-0.4453125</v>
-      </c>
-      <c r="V37" s="16">
-        <f t="shared" ref="V37:AF37" si="58">V21/V20</f>
-        <v>-6.6345847634549232E-2</v>
-      </c>
-      <c r="W37" s="16">
+    <row r="42" spans="2:39">
+      <c r="B42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="15">
+        <f t="shared" ref="E42:K42" si="58">E27/E12</f>
+        <v>-1.9935344827586209E-2</v>
+      </c>
+      <c r="F42" s="15">
         <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="X37" s="16">
+        <v>7.0215545395166556E-2</v>
+      </c>
+      <c r="G42" s="15">
         <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="Y37" s="16">
+        <v>8.5870413739266196E-2</v>
+      </c>
+      <c r="H42" s="15">
         <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="Z37" s="16">
+        <v>8.6246028143440769E-3</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AA37" s="16">
+        <v>5.6439942112879886E-2</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AB37" s="16">
+        <v>3.9897039897039896E-2</v>
+      </c>
+      <c r="K42" s="15">
         <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AC37" s="16">
-        <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AD37" s="16">
-        <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AE37" s="16">
-        <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AF37" s="16">
-        <f t="shared" si="58"/>
-        <v>0.15</v>
-      </c>
-      <c r="AH37" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI37" s="23">
-        <f>Main!D3</f>
-        <v>162.50479999999999</v>
+        <v>2.8909329829172142E-2</v>
+      </c>
+      <c r="L42" s="15">
+        <f>L27/L12</f>
+        <v>8.7771203155818545E-2</v>
+      </c>
+      <c r="M42" s="15">
+        <f t="shared" ref="M42:N42" si="59">M27/M12</f>
+        <v>2.2973558734286952E-2</v>
+      </c>
+      <c r="N42" s="15">
+        <f t="shared" si="59"/>
+        <v>0.17238765565782352</v>
+      </c>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="Y42" s="15">
+        <f t="shared" ref="Y42" si="60">Y27/Y12</f>
+        <v>4.2700519330640507E-2</v>
+      </c>
+      <c r="Z42" s="15">
+        <f t="shared" ref="Z42:AJ42" si="61">Z27/Z12</f>
+        <v>9.7162600774787986E-2</v>
+      </c>
+      <c r="AA42" s="15">
+        <f t="shared" si="61"/>
+        <v>7.8829099079567172E-2</v>
+      </c>
+      <c r="AB42" s="15">
+        <f t="shared" si="61"/>
+        <v>8.5159840272244561E-2</v>
+      </c>
+      <c r="AC42" s="15">
+        <f t="shared" si="61"/>
+        <v>8.6247679766441404E-2</v>
+      </c>
+      <c r="AD42" s="15">
+        <f t="shared" si="61"/>
+        <v>8.7517613047355072E-2</v>
+      </c>
+      <c r="AE42" s="15">
+        <f t="shared" si="61"/>
+        <v>8.8544861310175679E-2</v>
+      </c>
+      <c r="AF42" s="15">
+        <f t="shared" si="61"/>
+        <v>8.9562028123107124E-2</v>
+      </c>
+      <c r="AG42" s="15">
+        <f t="shared" si="61"/>
+        <v>9.0570800421185732E-2</v>
+      </c>
+      <c r="AH42" s="15">
+        <f t="shared" si="61"/>
+        <v>9.157306100822063E-2</v>
+      </c>
+      <c r="AI42" s="15">
+        <f t="shared" si="61"/>
+        <v>9.2570916051176969E-2</v>
+      </c>
+      <c r="AJ42" s="15">
+        <f t="shared" si="61"/>
+        <v>9.3566725466971076E-2</v>
+      </c>
+      <c r="AL42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM42" s="21">
+        <f>AM40/AM41-1</f>
+        <v>-0.42413137527941569</v>
       </c>
     </row>
-    <row r="38" spans="2:35">
-      <c r="B38" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="16">
-        <f t="shared" ref="E38:K38" si="59">E23/E8</f>
-        <v>-1.9935344827586209E-2</v>
-      </c>
-      <c r="F38" s="16">
-        <f t="shared" si="59"/>
-        <v>7.0215545395166556E-2</v>
-      </c>
-      <c r="G38" s="16">
-        <f t="shared" si="59"/>
-        <v>8.5870413739266196E-2</v>
-      </c>
-      <c r="H38" s="16">
-        <f t="shared" si="59"/>
-        <v>8.6246028143440769E-3</v>
-      </c>
-      <c r="I38" s="16">
-        <f t="shared" si="59"/>
-        <v>5.6439942112879886E-2</v>
-      </c>
-      <c r="J38" s="16">
-        <f t="shared" si="59"/>
-        <v>3.9897039897039896E-2</v>
-      </c>
-      <c r="K38" s="16">
-        <f t="shared" si="59"/>
-        <v>2.8909329829172142E-2</v>
-      </c>
-      <c r="L38" s="16">
-        <f>L23/L8</f>
-        <v>8.7771203155818545E-2</v>
-      </c>
-      <c r="M38" s="16">
-        <f t="shared" ref="M38:N38" si="60">M23/M8</f>
-        <v>2.2973558734286952E-2</v>
-      </c>
-      <c r="N38" s="16">
-        <f t="shared" si="60"/>
-        <v>4.3444863950006518E-2</v>
-      </c>
-      <c r="U38" s="16">
-        <f t="shared" ref="U38" si="61">U23/U8</f>
-        <v>4.2700519330640507E-2</v>
-      </c>
-      <c r="V38" s="16">
-        <f t="shared" ref="V38:AF38" si="62">V23/V8</f>
-        <v>4.5597388064393202E-2</v>
-      </c>
-      <c r="W38" s="16">
-        <f t="shared" si="62"/>
-        <v>5.7305858021767193E-2</v>
-      </c>
-      <c r="X38" s="16">
-        <f t="shared" si="62"/>
-        <v>6.6845856099188902E-2</v>
-      </c>
-      <c r="Y38" s="16">
-        <f t="shared" si="62"/>
-        <v>6.907769476511548E-2</v>
-      </c>
-      <c r="Z38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.0231479842168265E-2</v>
-      </c>
-      <c r="AA38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.113350903453268E-2</v>
-      </c>
-      <c r="AB38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.2031682526016674E-2</v>
-      </c>
-      <c r="AC38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.2928188579369668E-2</v>
-      </c>
-      <c r="AD38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.3825498722254523E-2</v>
-      </c>
-      <c r="AE38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.4726407350762525E-2</v>
-      </c>
-      <c r="AF38" s="16">
-        <f t="shared" si="62"/>
-        <v>7.5634075485520411E-2</v>
-      </c>
-      <c r="AH38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI38" s="22">
-        <f>AI36/AI37-1</f>
-        <v>-0.56907189530793556</v>
+    <row r="43" spans="2:39">
+      <c r="AL43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM43" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="39" spans="2:35">
-      <c r="AH39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI39" s="12" t="s">
-        <v>66</v>
-      </c>
+    <row r="44" spans="2:39">
+      <c r="B44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J44" s="6">
+        <v>17900</v>
+      </c>
+      <c r="N44" s="6">
+        <v>18000</v>
+      </c>
+      <c r="Y44" s="6">
+        <v>17900</v>
+      </c>
+      <c r="Z44" s="6">
+        <v>18000</v>
+      </c>
+      <c r="AM44" s="12"/>
     </row>
-    <row r="41" spans="2:35" s="20" customFormat="1">
-      <c r="B41" s="20" t="s">
+    <row r="45" spans="2:39">
+      <c r="B45" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J45" s="6">
+        <v>900</v>
+      </c>
+      <c r="N45" s="6">
+        <v>900</v>
+      </c>
+      <c r="Y45" s="6">
+        <v>900</v>
+      </c>
+      <c r="Z45" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="46" spans="2:39" s="2" customFormat="1">
+      <c r="B46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J46" s="16">
+        <f>SUM(J44:J45)</f>
+        <v>18800</v>
+      </c>
+      <c r="N46" s="16">
+        <f>SUM(N44:N45)</f>
+        <v>18900</v>
+      </c>
+      <c r="Y46" s="16">
+        <f>SUM(Y44:Y45)</f>
+        <v>18800</v>
+      </c>
+      <c r="Z46" s="16">
+        <f>SUM(Z44:Z45)</f>
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="48" spans="2:39" s="19" customFormat="1">
+      <c r="B48" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L48" s="23">
         <f>12864</f>
         <v>12864</v>
       </c>
-      <c r="M41" s="24">
+      <c r="M48" s="23">
         <v>13333</v>
       </c>
-      <c r="V41" s="24">
+      <c r="N48" s="23">
         <v>13333</v>
       </c>
+      <c r="Z48" s="23">
+        <v>13333</v>
+      </c>
     </row>
-    <row r="43" spans="2:35">
-      <c r="B43" s="1" t="s">
+    <row r="50" spans="2:26">
+      <c r="B50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L43" s="21"/>
-      <c r="V43" s="21">
-        <f>Main!$D$9/Model!V41</f>
-        <v>1.533149040726018</v>
+      <c r="L50" s="20"/>
+      <c r="Z50" s="20">
+        <f>Main!$D$9/Model!Z48</f>
+        <v>1.5648886162154052</v>
       </c>
     </row>
-    <row r="44" spans="2:35">
-      <c r="B44" s="1" t="s">
+    <row r="51" spans="2:26">
+      <c r="B51" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L44" s="16"/>
-      <c r="V44" s="16">
-        <f>V41/Main!$D$9-1</f>
-        <v>-0.34774769220971946</v>
+      <c r="L51" s="15"/>
+      <c r="Z51" s="15">
+        <f>Z48/Main!$D$9-1</f>
+        <v>-0.36097688382548043</v>
       </c>
     </row>
   </sheetData>
